--- a/sortari.xlsx
+++ b/sortari.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1AE9CE-563D-455F-82A4-B7D19E57FB77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD99119E-DB2F-4567-BDF0-9521268A13AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista, nr random" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="25">
   <si>
     <t>n</t>
   </si>
@@ -97,6 +97,9 @@
   <si>
     <t>stack overflow</t>
   </si>
+  <si>
+    <t>Bubble</t>
+  </si>
 </sst>
 </file>
 
@@ -111,7 +114,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0000"/>
     <numFmt numFmtId="170" formatCode="#,##0.00000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -143,6 +146,14 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="&quot;gg sans&quot;"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="29">
@@ -480,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -609,6 +620,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="6" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4831,13 +4843,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1">
       <c r="A1" s="122" t="s">
         <v>22</v>
       </c>
@@ -4865,158 +4877,161 @@
       <c r="I1" s="64" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1">
+      <c r="K1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1">
       <c r="A2" s="1">
         <v>10</v>
       </c>
-      <c r="B2" s="77">
-        <v>0</v>
-      </c>
-      <c r="C2" s="78">
-        <v>0</v>
+      <c r="B2" s="93">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C2" s="94">
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="D2" s="79">
-        <v>0</v>
-      </c>
-      <c r="E2" s="80">
-        <v>0</v>
-      </c>
-      <c r="F2" s="81">
-        <v>0</v>
-      </c>
-      <c r="G2" s="82">
-        <v>0</v>
-      </c>
-      <c r="H2" s="83">
-        <v>0</v>
-      </c>
-      <c r="I2" s="84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="E2" s="96">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="F2" s="97">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G2" s="98">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H2" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I2" s="100">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" customHeight="1">
       <c r="A3" s="1">
         <v>20</v>
       </c>
-      <c r="B3" s="77">
-        <v>0</v>
-      </c>
-      <c r="C3" s="78">
-        <v>0</v>
+      <c r="B3" s="93">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C3" s="94">
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="D3" s="79">
-        <v>0</v>
-      </c>
-      <c r="E3" s="80">
-        <v>0</v>
-      </c>
-      <c r="F3" s="81">
-        <v>0</v>
-      </c>
-      <c r="G3" s="82">
-        <v>0</v>
-      </c>
-      <c r="H3" s="83">
-        <v>0</v>
-      </c>
-      <c r="I3" s="84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="E3" s="96">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="F3" s="97">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G3" s="98">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H3" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I3" s="100">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1">
       <c r="A4" s="1">
         <v>50</v>
       </c>
-      <c r="B4" s="77">
-        <v>0</v>
-      </c>
-      <c r="C4" s="78">
-        <v>0</v>
+      <c r="B4" s="93">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C4" s="94">
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="D4" s="79">
-        <v>0</v>
-      </c>
-      <c r="E4" s="80">
-        <v>0</v>
-      </c>
-      <c r="F4" s="81">
-        <v>0</v>
-      </c>
-      <c r="G4" s="82">
-        <v>0</v>
-      </c>
-      <c r="H4" s="83">
-        <v>0</v>
-      </c>
-      <c r="I4" s="84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="E4" s="96">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="F4" s="97">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G4" s="98">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H4" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I4" s="100">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" customHeight="1">
       <c r="A5" s="1">
         <v>100</v>
       </c>
-      <c r="B5" s="77">
-        <v>0</v>
-      </c>
-      <c r="C5" s="78">
-        <v>0</v>
-      </c>
-      <c r="D5" s="79">
-        <v>0</v>
-      </c>
-      <c r="E5" s="80">
-        <v>0</v>
-      </c>
-      <c r="F5" s="81">
-        <v>0</v>
-      </c>
-      <c r="G5" s="82">
-        <v>0</v>
-      </c>
-      <c r="H5" s="83">
-        <v>0</v>
-      </c>
-      <c r="I5" s="84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1">
+      <c r="B5" s="93">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C5" s="94">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="D5" s="95">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="E5" s="96">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="F5" s="97">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G5" s="98">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H5" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I5" s="100">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" customHeight="1">
       <c r="A6" s="1">
         <v>1000</v>
       </c>
-      <c r="B6" s="77">
-        <v>0</v>
-      </c>
-      <c r="C6" s="78">
-        <v>0</v>
-      </c>
-      <c r="D6" s="79">
-        <v>0</v>
-      </c>
-      <c r="E6" s="80">
-        <v>1E-3</v>
-      </c>
-      <c r="F6" s="81">
-        <v>0</v>
-      </c>
-      <c r="G6" s="82">
-        <v>0</v>
-      </c>
-      <c r="H6" s="83">
-        <v>0</v>
-      </c>
-      <c r="I6" s="84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1">
+      <c r="B6" s="93">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C6" s="94">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="D6" s="95">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="E6" s="47">
+        <v>1E-3</v>
+      </c>
+      <c r="F6" s="97">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G6" s="98">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H6" s="99">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I6" s="100">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" customHeight="1">
       <c r="A7" s="1">
         <v>10000</v>
       </c>
-      <c r="B7" s="44">
-        <v>0</v>
+      <c r="B7" s="77">
+        <v>1E-4</v>
       </c>
       <c r="C7" s="45">
         <v>0.03</v>
@@ -5040,12 +5055,12 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1">
       <c r="A8" s="1">
         <v>100000</v>
       </c>
-      <c r="B8" s="44">
-        <v>0</v>
+      <c r="B8" s="124">
+        <v>1E-4</v>
       </c>
       <c r="C8" s="45">
         <v>3.49</v>
@@ -5068,8 +5083,11 @@
       <c r="I8" s="51">
         <v>3.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1">
+      <c r="K8">
+        <v>3.6030000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" customHeight="1">
       <c r="A9" s="1">
         <v>1000000</v>
       </c>
@@ -5097,8 +5115,11 @@
       <c r="I9" s="51">
         <v>9.6000000000000002E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1">
+      <c r="K9">
+        <v>1324.7629999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="1">
         <v>10000000</v>
       </c>
@@ -5123,7 +5144,7 @@
         <v>0.499</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1">
       <c r="A11" s="1">
         <v>100000000</v>
       </c>
@@ -5158,13 +5179,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1">
       <c r="A1" s="122" t="s">
         <v>22</v>
       </c>
@@ -5192,8 +5213,11 @@
       <c r="I1" s="64" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1">
+      <c r="K1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1">
       <c r="A2" s="1">
         <v>10</v>
       </c>
@@ -5222,7 +5246,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1">
+    <row r="3" spans="1:11" ht="15.75" customHeight="1">
       <c r="A3" s="1">
         <v>20</v>
       </c>
@@ -5251,7 +5275,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1">
+    <row r="4" spans="1:11" ht="15.75" customHeight="1">
       <c r="A4" s="1">
         <v>50</v>
       </c>
@@ -5280,7 +5304,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1">
+    <row r="5" spans="1:11" ht="15.75" customHeight="1">
       <c r="A5" s="1">
         <v>100</v>
       </c>
@@ -5309,7 +5333,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1">
+    <row r="6" spans="1:11" ht="15.75" customHeight="1">
       <c r="A6" s="1">
         <v>1000</v>
       </c>
@@ -5338,7 +5362,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1">
+    <row r="7" spans="1:11" ht="15.75" customHeight="1">
       <c r="A7" s="1">
         <v>10000</v>
       </c>
@@ -5367,7 +5391,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1">
+    <row r="8" spans="1:11" ht="15.75" customHeight="1">
       <c r="A8" s="1">
         <v>100000</v>
       </c>
@@ -5395,8 +5419,11 @@
       <c r="I8" s="51">
         <v>4.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1">
+      <c r="K8">
+        <v>3.6190000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" customHeight="1">
       <c r="A9" s="1">
         <v>1000000</v>
       </c>
@@ -5425,7 +5452,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="1">
         <v>10000000</v>
       </c>
@@ -5450,7 +5477,7 @@
         <v>0.55900000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1">
       <c r="A11" s="1">
         <v>100000000</v>
       </c>

--- a/sortari.xlsx
+++ b/sortari.xlsx
@@ -1,16 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anton\uni\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44033721-C4AA-4F34-A0C4-71D016A63C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Lista, nr random" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="N Liste, nr random" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Lista sortata" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Lista aproape sortata (~98%)" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Lista invers sortata" sheetId="5" r:id="rId9"/>
+    <sheet name="Lista, nr random" sheetId="1" r:id="rId1"/>
+    <sheet name="N Liste, nr random" sheetId="2" r:id="rId2"/>
+    <sheet name="Lista sortata" sheetId="3" r:id="rId3"/>
+    <sheet name="Lista aproape sortata (~98%)" sheetId="4" r:id="rId4"/>
+    <sheet name="Lista invers sortata" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -89,8 +98,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="0.00000000000"/>
     <numFmt numFmtId="165" formatCode="0.000000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
@@ -99,33 +108,37 @@
     <numFmt numFmtId="169" formatCode="#,##0.0000000"/>
     <numFmt numFmtId="170" formatCode="#,##0.000000"/>
     <numFmt numFmtId="171" formatCode="#,##0.00000000"/>
-    <numFmt numFmtId="172" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="177" formatCode="0.0000000"/>
+    <numFmt numFmtId="183" formatCode="0.0000000000"/>
   </numFmts>
   <fonts count="6">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font/>
-    <font>
-      <sz val="12.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="&quot;gg sans&quot;"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -135,7 +148,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -295,25 +308,24 @@
     </fill>
   </fills>
   <borders count="16">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -321,8 +333,21 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -332,6 +357,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -346,6 +372,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -356,6 +383,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -368,6 +396,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -380,6 +409,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -392,6 +422,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -404,6 +435,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -414,6 +446,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -422,6 +455,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -430,6 +464,7 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -440,6 +475,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -448,234 +484,166 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="6" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="7" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="9" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="10" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="134">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="6" fillId="11" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="7" fillId="11" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="12" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="7" fillId="13" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="7" fillId="14" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="7" fillId="15" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="7" fillId="16" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="7" fillId="17" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="7" fillId="18" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="13" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="14" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="15" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="16" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="17" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="18" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="13" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="14" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="15" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="16" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="17" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="18" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="8" fillId="19" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="19" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="20" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="21" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="22" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="23" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="24" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="25" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="26" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="5" fillId="19" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="20" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="21" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="22" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="23" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="24" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="25" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="8" fillId="11" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="13" fontId="1" numFmtId="165" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="24" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="5" fillId="19" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="20" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="21" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="22" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="23" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="24" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="25" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="26" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="14" fontId="1" numFmtId="167" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="22" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="25" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="22" fontId="1" numFmtId="168" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="24" fontId="1" numFmtId="168" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="166" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="6" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="7" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="8" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="9" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="10" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="11" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="12" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="13" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="14" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="15" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="16" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="17" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="18" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="27" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="21" fontId="1" numFmtId="4" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="22" fontId="1" numFmtId="4" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="23" fontId="1" numFmtId="4" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="19" fontId="1" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="20" fontId="1" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="21" fontId="1" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="22" fontId="1" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="23" fontId="1" numFmtId="171" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="24" fontId="1" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="25" fontId="1" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="26" fontId="1" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="23" fontId="1" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="25" fontId="1" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="22" fontId="1" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="23" fontId="1" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="24" fontId="1" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="26" fontId="1" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="9" fillId="20" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="9" fillId="21" fontId="1" numFmtId="3" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="10" fillId="19" fontId="1" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="11" fillId="27" fontId="1" numFmtId="169" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="12" fillId="27" fontId="1" numFmtId="169" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="8" fillId="23" fontId="1" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="13" fillId="27" fontId="1" numFmtId="169" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="27" fontId="1" numFmtId="169" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="25" fontId="1" numFmtId="169" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="26" fontId="1" numFmtId="169" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="21" fontId="1" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="26" fontId="1" numFmtId="172" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="19" fontId="1" numFmtId="172" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="20" fontId="1" numFmtId="172" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="21" fontId="1" numFmtId="172" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="22" fontId="1" numFmtId="172" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="23" fontId="1" numFmtId="172" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="24" fontId="1" numFmtId="172" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="25" fontId="1" numFmtId="172" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="26" fontId="1" numFmtId="172" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="5" fillId="19" fontId="1" numFmtId="4" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="9" fillId="19" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="9" fillId="21" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="12" fillId="27" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="14" fillId="27" fontId="1" numFmtId="166" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="15" fillId="27" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="22" fontId="1" numFmtId="172" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="23" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="24" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="25" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="5" fillId="26" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="166" fontId="1" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="24" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="26" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="24" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="1" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="1" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="24" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="1" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="26" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="1" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="1" fillId="24" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="1" fillId="26" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="27" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="27" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="23" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="27" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="1" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="1" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="1" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="1" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="1" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -683,7 +651,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -873,3199 +841,3201 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Q1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.63"/>
-    <col customWidth="1" min="2" max="17" width="13.5"/>
+    <col min="1" max="1" width="12.6328125" customWidth="1"/>
+    <col min="2" max="17" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="104"/>
+      <c r="D1" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="104"/>
+      <c r="F1" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="104"/>
+      <c r="H1" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="7" t="s">
+      <c r="I1" s="104"/>
+      <c r="J1" s="108" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="8" t="s">
+      <c r="K1" s="104"/>
+      <c r="L1" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="3"/>
-      <c r="N1" s="9" t="s">
+      <c r="M1" s="104"/>
+      <c r="N1" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="10"/>
-      <c r="P1" s="11" t="s">
+      <c r="O1" s="111"/>
+      <c r="P1" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="10"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="12">
-        <v>10.0</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="Q1" s="111"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A2" s="2">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="21" t="s">
+      <c r="P2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="Q2" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="22">
-        <v>2.0E-6</v>
-      </c>
-      <c r="C3" s="22">
-        <v>2.0E-6</v>
-      </c>
-      <c r="D3" s="23">
-        <v>1.0E-6</v>
-      </c>
-      <c r="E3" s="23">
-        <v>2.0E-6</v>
-      </c>
-      <c r="F3" s="24">
-        <v>1.0E-6</v>
-      </c>
-      <c r="G3" s="24">
-        <v>2.0E-6</v>
-      </c>
-      <c r="H3" s="25">
-        <v>1.0E-6</v>
-      </c>
-      <c r="I3" s="25">
-        <v>2.0E-6</v>
-      </c>
-      <c r="J3" s="26">
-        <v>3.0E-6</v>
-      </c>
-      <c r="K3" s="26">
-        <v>3.0E-6</v>
-      </c>
-      <c r="L3" s="27">
-        <v>4.0E-6</v>
-      </c>
-      <c r="M3" s="27">
-        <v>2.0E-6</v>
-      </c>
-      <c r="N3" s="28">
-        <v>1.0E-6</v>
-      </c>
-      <c r="O3" s="28">
-        <v>3.0E-6</v>
-      </c>
-      <c r="P3" s="29">
-        <v>1.0E-6</v>
-      </c>
-      <c r="Q3" s="29">
-        <v>1.1E-6</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
+      <c r="B3" s="12">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="D3" s="13">
+        <v>6.9999999999999997E-7</v>
+      </c>
+      <c r="E3" s="13">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="F3" s="14">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="G3" s="14">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="H3" s="15">
+        <v>1.1999999999999999E-6</v>
+      </c>
+      <c r="I3" s="15">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="J3" s="16">
+        <v>4.3000000000000003E-6</v>
+      </c>
+      <c r="K3" s="16">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="L3" s="17">
+        <v>7.1999999999999997E-6</v>
+      </c>
+      <c r="M3" s="17">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="N3" s="115">
+        <v>8.9999999999999996E-7</v>
+      </c>
+      <c r="O3" s="18">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="P3" s="19">
+        <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="Q3" s="19">
+        <v>1.1000000000000001E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="22">
-        <v>1.0E-6</v>
-      </c>
-      <c r="C4" s="22">
-        <v>1.0E-6</v>
-      </c>
-      <c r="D4" s="23">
-        <v>1.0E-6</v>
-      </c>
-      <c r="E4" s="23">
-        <v>2.0E-6</v>
-      </c>
-      <c r="F4" s="24">
-        <v>1.0E-6</v>
-      </c>
-      <c r="G4" s="24">
-        <v>1.0E-6</v>
-      </c>
-      <c r="H4" s="25">
-        <v>1.0E-6</v>
-      </c>
-      <c r="I4" s="25">
-        <v>1.0E-6</v>
-      </c>
-      <c r="J4" s="26">
-        <v>3.0E-6</v>
-      </c>
-      <c r="K4" s="26">
-        <v>3.0E-6</v>
-      </c>
-      <c r="L4" s="27">
-        <v>2.0E-6</v>
-      </c>
-      <c r="M4" s="27">
-        <v>3.0E-6</v>
-      </c>
-      <c r="N4" s="28">
-        <v>2.0E-6</v>
-      </c>
-      <c r="O4" s="28">
-        <v>3.0E-6</v>
-      </c>
-      <c r="P4" s="29">
-        <v>1.0E-6</v>
-      </c>
-      <c r="Q4" s="29">
-        <v>2.0E-6</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
+      <c r="B4" s="12">
+        <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="C4" s="12">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="D4" s="13">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="E4" s="13">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="F4" s="14">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="G4" s="14">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="H4" s="15">
+        <v>1.1000000000000001E-6</v>
+      </c>
+      <c r="I4" s="15">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="J4" s="16">
+        <v>4.0999999999999997E-6</v>
+      </c>
+      <c r="K4" s="16">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="L4" s="17">
+        <v>4.6999999999999999E-6</v>
+      </c>
+      <c r="M4" s="17">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="N4" s="18">
+        <v>6.9999999999999997E-7</v>
+      </c>
+      <c r="O4" s="18">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="P4" s="19">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="Q4" s="19">
+        <v>1.9999999999999999E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="22">
-        <v>2.0E-6</v>
-      </c>
-      <c r="C5" s="22">
-        <v>2.0E-6</v>
-      </c>
-      <c r="D5" s="23">
-        <v>1.0E-6</v>
-      </c>
-      <c r="E5" s="23">
-        <v>2.0E-6</v>
-      </c>
-      <c r="F5" s="24">
-        <v>1.0E-6</v>
-      </c>
-      <c r="G5" s="24">
-        <v>1.0E-6</v>
-      </c>
-      <c r="H5" s="25">
-        <v>1.0E-6</v>
-      </c>
-      <c r="I5" s="25">
-        <v>1.0E-6</v>
-      </c>
-      <c r="J5" s="26">
-        <v>2.0E-6</v>
-      </c>
-      <c r="K5" s="26">
-        <v>3.0E-6</v>
-      </c>
-      <c r="L5" s="27">
-        <v>4.0E-6</v>
-      </c>
-      <c r="M5" s="27">
-        <v>2.0E-6</v>
-      </c>
-      <c r="N5" s="28">
-        <v>2.0E-6</v>
-      </c>
-      <c r="O5" s="28">
-        <v>3.0E-6</v>
-      </c>
-      <c r="P5" s="29">
-        <v>1.0E-6</v>
-      </c>
-      <c r="Q5" s="29">
-        <v>1.0E-6</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
+      <c r="B5" s="12">
+        <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="C5" s="12">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="D5" s="13">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="E5" s="13">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="F5" s="14">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="G5" s="14">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="H5" s="15">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="I5" s="15">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="J5" s="16">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="K5" s="16">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="L5" s="17">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="M5" s="17">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="N5" s="18">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="O5" s="18">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="P5" s="19">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="Q5" s="19">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="30">
-        <f t="shared" ref="B6:Q6" si="1">AVERAGE(B3:B5)</f>
-        <v>0.000001666666667</v>
-      </c>
-      <c r="C6" s="30">
-        <f t="shared" si="1"/>
-        <v>0.000001666666667</v>
-      </c>
-      <c r="D6" s="23">
-        <f t="shared" si="1"/>
-        <v>0.000001</v>
-      </c>
-      <c r="E6" s="23">
-        <f t="shared" si="1"/>
-        <v>0.000002</v>
-      </c>
-      <c r="F6" s="24">
-        <f t="shared" si="1"/>
-        <v>0.000001</v>
-      </c>
-      <c r="G6" s="31">
-        <f t="shared" si="1"/>
-        <v>0.000001333333333</v>
-      </c>
-      <c r="H6" s="25">
-        <f t="shared" si="1"/>
-        <v>0.000001</v>
-      </c>
-      <c r="I6" s="32">
-        <f t="shared" si="1"/>
-        <v>0.000001333333333</v>
-      </c>
-      <c r="J6" s="33">
-        <f t="shared" si="1"/>
-        <v>0.000002666666667</v>
-      </c>
-      <c r="K6" s="26">
-        <f t="shared" si="1"/>
-        <v>0.000003</v>
-      </c>
-      <c r="L6" s="34">
-        <f t="shared" si="1"/>
-        <v>0.000003333333333</v>
-      </c>
-      <c r="M6" s="34">
-        <f t="shared" si="1"/>
-        <v>0.000002333333333</v>
-      </c>
-      <c r="N6" s="35">
-        <f t="shared" si="1"/>
-        <v>0.000001666666667</v>
-      </c>
-      <c r="O6" s="28">
-        <f t="shared" si="1"/>
-        <v>0.000003</v>
-      </c>
-      <c r="P6" s="29">
-        <f t="shared" si="1"/>
-        <v>0.000001</v>
-      </c>
-      <c r="Q6" s="36">
-        <f t="shared" si="1"/>
-        <v>0.000001366666667</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="12">
-        <v>20.0</v>
-      </c>
-      <c r="B7" s="37" t="s">
+      <c r="B6" s="117">
+        <f t="shared" ref="B6:Q6" si="0">AVERAGE(B3:B5)</f>
+        <v>4.333333333333333E-7</v>
+      </c>
+      <c r="C6" s="20">
+        <f t="shared" si="0"/>
+        <v>1.6666666666666665E-6</v>
+      </c>
+      <c r="D6" s="116">
+        <f t="shared" si="0"/>
+        <v>5.6666666666666661E-7</v>
+      </c>
+      <c r="E6" s="13">
+        <f t="shared" si="0"/>
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="F6" s="119">
+        <f t="shared" si="0"/>
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="G6" s="118">
+        <f t="shared" si="0"/>
+        <v>1.3333333333333332E-6</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="0"/>
+        <v>1.0999999999999998E-6</v>
+      </c>
+      <c r="I6" s="22">
+        <f t="shared" si="0"/>
+        <v>1.3333333333333332E-6</v>
+      </c>
+      <c r="J6" s="23">
+        <f t="shared" si="0"/>
+        <v>3.4666666666666668E-6</v>
+      </c>
+      <c r="K6" s="16">
+        <f t="shared" si="0"/>
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="L6" s="24">
+        <f t="shared" si="0"/>
+        <v>5.3000000000000001E-6</v>
+      </c>
+      <c r="M6" s="24">
+        <f t="shared" si="0"/>
+        <v>2.3333333333333332E-6</v>
+      </c>
+      <c r="N6" s="25">
+        <f t="shared" si="0"/>
+        <v>1.1999999999999999E-6</v>
+      </c>
+      <c r="O6" s="18">
+        <f t="shared" si="0"/>
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="P6" s="19">
+        <f t="shared" si="0"/>
+        <v>6.3333333333333334E-7</v>
+      </c>
+      <c r="Q6" s="26">
+        <f t="shared" si="0"/>
+        <v>1.3666666666666666E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A7" s="2">
+        <v>20</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="40" t="s">
+      <c r="G7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="42" t="s">
+      <c r="J7" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="42" t="s">
+      <c r="K7" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="43" t="s">
+      <c r="L7" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="M7" s="43" t="s">
+      <c r="M7" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="N7" s="44" t="s">
+      <c r="N7" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="44" t="s">
+      <c r="O7" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="P7" s="45" t="s">
+      <c r="P7" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="Q7" s="45" t="s">
+      <c r="Q7" s="35" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="38">
-        <v>1.0E-6</v>
-      </c>
-      <c r="C8" s="38">
-        <v>2.0E-6</v>
-      </c>
-      <c r="D8" s="39">
-        <v>2.0E-6</v>
-      </c>
-      <c r="E8" s="39">
-        <v>2.0E-6</v>
-      </c>
-      <c r="F8" s="40">
-        <v>2.0E-6</v>
-      </c>
-      <c r="G8" s="40">
-        <v>2.0E-6</v>
-      </c>
-      <c r="H8" s="41">
-        <v>2.0E-6</v>
-      </c>
-      <c r="I8" s="41">
-        <v>2.0E-6</v>
-      </c>
-      <c r="J8" s="42">
-        <v>3.0E-6</v>
-      </c>
-      <c r="K8" s="42">
-        <v>5.0E-6</v>
-      </c>
-      <c r="L8" s="43">
-        <v>6.0E-6</v>
-      </c>
-      <c r="M8" s="43">
-        <v>2.0E-6</v>
-      </c>
-      <c r="N8" s="44">
-        <v>3.0E-6</v>
-      </c>
-      <c r="O8" s="44">
-        <v>2.0E-6</v>
-      </c>
-      <c r="P8" s="45">
-        <v>1.0E-6</v>
-      </c>
-      <c r="Q8" s="45">
-        <v>1.0E-6</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
+      <c r="B8" s="28">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C8" s="28">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="D8" s="29">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="E8" s="29">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="F8" s="30">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="G8" s="30">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="H8" s="31">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="I8" s="31">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="J8" s="32">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="K8" s="32">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="L8" s="33">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="M8" s="33">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="N8" s="34">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="O8" s="34">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="P8" s="35">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="Q8" s="35">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="38">
-        <v>2.0E-6</v>
-      </c>
-      <c r="C9" s="38">
-        <v>1.0E-6</v>
-      </c>
-      <c r="D9" s="39">
-        <v>2.0E-6</v>
-      </c>
-      <c r="E9" s="39">
-        <v>1.0E-6</v>
-      </c>
-      <c r="F9" s="40">
-        <v>2.0E-6</v>
-      </c>
-      <c r="G9" s="40">
-        <v>1.0E-6</v>
-      </c>
-      <c r="H9" s="41">
-        <v>2.0E-6</v>
-      </c>
-      <c r="I9" s="41">
-        <v>1.0E-6</v>
-      </c>
-      <c r="J9" s="42">
-        <v>4.0E-6</v>
-      </c>
-      <c r="K9" s="42">
-        <v>3.0E-6</v>
-      </c>
-      <c r="L9" s="43">
-        <v>6.0E-6</v>
-      </c>
-      <c r="M9" s="43">
-        <v>2.0E-6</v>
-      </c>
-      <c r="N9" s="44">
-        <v>3.0E-6</v>
-      </c>
-      <c r="O9" s="44">
-        <v>2.0E-6</v>
-      </c>
-      <c r="P9" s="45">
-        <v>1.0E-6</v>
-      </c>
-      <c r="Q9" s="45">
-        <v>1.0E-6</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
+      <c r="B9" s="28">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="C9" s="28">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="D9" s="29">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="E9" s="29">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="F9" s="30">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="G9" s="30">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="H9" s="31">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="I9" s="31">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="J9" s="32">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="K9" s="32">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="L9" s="33">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="M9" s="33">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="N9" s="34">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="O9" s="34">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="P9" s="35">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="Q9" s="35">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="38">
-        <v>2.0E-6</v>
-      </c>
-      <c r="C10" s="38">
-        <v>2.0E-6</v>
-      </c>
-      <c r="D10" s="39">
-        <v>2.0E-6</v>
-      </c>
-      <c r="E10" s="39">
-        <v>2.0E-6</v>
-      </c>
-      <c r="F10" s="40">
-        <v>1.0E-6</v>
-      </c>
-      <c r="G10" s="40">
-        <v>2.0E-6</v>
-      </c>
-      <c r="H10" s="41">
-        <v>1.0E-6</v>
-      </c>
-      <c r="I10" s="41">
-        <v>1.0E-6</v>
-      </c>
-      <c r="J10" s="42">
-        <v>4.0E-6</v>
-      </c>
-      <c r="K10" s="42">
-        <v>3.0E-6</v>
-      </c>
-      <c r="L10" s="43">
-        <v>6.0E-6</v>
-      </c>
-      <c r="M10" s="43">
-        <v>3.0E-6</v>
-      </c>
-      <c r="N10" s="44">
-        <v>3.0E-6</v>
-      </c>
-      <c r="O10" s="44">
-        <v>3.0E-6</v>
-      </c>
-      <c r="P10" s="45">
-        <v>1.0E-6</v>
-      </c>
-      <c r="Q10" s="45">
-        <v>1.0E-6</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
+      <c r="B10" s="28">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="C10" s="28">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="D10" s="29">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="E10" s="29">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="F10" s="30">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G10" s="30">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="H10" s="31">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="I10" s="31">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="J10" s="32">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="K10" s="32">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="L10" s="33">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="M10" s="33">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="N10" s="34">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="O10" s="34">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="P10" s="35">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="Q10" s="35">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="46">
-        <f t="shared" ref="B11:Q11" si="2">AVERAGE(B8:B10)</f>
-        <v>0.000001666666667</v>
-      </c>
-      <c r="C11" s="46">
-        <f t="shared" si="2"/>
-        <v>0.000001666666667</v>
-      </c>
-      <c r="D11" s="39">
-        <f t="shared" si="2"/>
-        <v>0.000002</v>
-      </c>
-      <c r="E11" s="47">
-        <f t="shared" si="2"/>
-        <v>0.000001666666667</v>
-      </c>
-      <c r="F11" s="48">
-        <f t="shared" si="2"/>
-        <v>0.000001666666667</v>
-      </c>
-      <c r="G11" s="48">
-        <f t="shared" si="2"/>
-        <v>0.000001666666667</v>
-      </c>
-      <c r="H11" s="49">
-        <f t="shared" si="2"/>
-        <v>0.000001666666667</v>
-      </c>
-      <c r="I11" s="49">
-        <f t="shared" si="2"/>
-        <v>0.000001333333333</v>
-      </c>
-      <c r="J11" s="50">
-        <f t="shared" si="2"/>
-        <v>0.000003666666667</v>
-      </c>
-      <c r="K11" s="50">
-        <f t="shared" si="2"/>
-        <v>0.000003666666667</v>
-      </c>
-      <c r="L11" s="43">
-        <f t="shared" si="2"/>
-        <v>0.000006</v>
-      </c>
-      <c r="M11" s="51">
-        <f t="shared" si="2"/>
-        <v>0.000002333333333</v>
-      </c>
-      <c r="N11" s="44">
-        <f t="shared" si="2"/>
-        <v>0.000003</v>
-      </c>
-      <c r="O11" s="52">
-        <f t="shared" si="2"/>
-        <v>0.000002333333333</v>
-      </c>
-      <c r="P11" s="45">
-        <f t="shared" si="2"/>
-        <v>0.000001</v>
-      </c>
-      <c r="Q11" s="45">
-        <f t="shared" si="2"/>
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="12">
-        <v>50.0</v>
-      </c>
-      <c r="B12" s="53" t="s">
+      <c r="B11" s="36">
+        <f t="shared" ref="B11:Q11" si="1">AVERAGE(B8:B10)</f>
+        <v>1.6666666666666665E-6</v>
+      </c>
+      <c r="C11" s="36">
+        <f t="shared" si="1"/>
+        <v>1.6666666666666665E-6</v>
+      </c>
+      <c r="D11" s="29">
+        <f t="shared" si="1"/>
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="E11" s="37">
+        <f t="shared" si="1"/>
+        <v>1.6666666666666665E-6</v>
+      </c>
+      <c r="F11" s="38">
+        <f t="shared" si="1"/>
+        <v>1.6666666666666665E-6</v>
+      </c>
+      <c r="G11" s="38">
+        <f t="shared" si="1"/>
+        <v>1.6666666666666665E-6</v>
+      </c>
+      <c r="H11" s="39">
+        <f t="shared" si="1"/>
+        <v>1.6666666666666665E-6</v>
+      </c>
+      <c r="I11" s="39">
+        <f t="shared" si="1"/>
+        <v>1.3333333333333332E-6</v>
+      </c>
+      <c r="J11" s="40">
+        <f t="shared" si="1"/>
+        <v>3.6666666666666666E-6</v>
+      </c>
+      <c r="K11" s="40">
+        <f t="shared" si="1"/>
+        <v>3.666666666666667E-6</v>
+      </c>
+      <c r="L11" s="33">
+        <f t="shared" si="1"/>
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="M11" s="41">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333332E-6</v>
+      </c>
+      <c r="N11" s="34">
+        <f t="shared" si="1"/>
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="O11" s="42">
+        <f t="shared" si="1"/>
+        <v>2.3333333333333332E-6</v>
+      </c>
+      <c r="P11" s="35">
+        <f t="shared" si="1"/>
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="Q11" s="35">
+        <f t="shared" si="1"/>
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A12" s="2">
+        <v>50</v>
+      </c>
+      <c r="B12" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="I12" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="26" t="s">
+      <c r="J12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="26" t="s">
+      <c r="K12" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="L12" s="27" t="s">
+      <c r="L12" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="M12" s="27" t="s">
+      <c r="M12" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="N12" s="28" t="s">
+      <c r="N12" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="O12" s="28" t="s">
+      <c r="O12" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="P12" s="29" t="s">
+      <c r="P12" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="Q12" s="29" t="s">
+      <c r="Q12" s="19" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="22">
-        <v>3.0E-6</v>
-      </c>
-      <c r="C13" s="22">
-        <v>4.0E-6</v>
-      </c>
-      <c r="D13" s="23">
-        <v>7.0E-6</v>
-      </c>
-      <c r="E13" s="23">
-        <v>6.0E-6</v>
-      </c>
-      <c r="F13" s="24">
-        <v>5.0E-6</v>
-      </c>
-      <c r="G13" s="24">
-        <v>4.0E-6</v>
-      </c>
-      <c r="H13" s="25">
-        <v>4.0E-6</v>
-      </c>
-      <c r="I13" s="25">
-        <v>4.0E-6</v>
-      </c>
-      <c r="J13" s="26">
-        <v>7.0E-6</v>
-      </c>
-      <c r="K13" s="26">
-        <v>5.0E-6</v>
-      </c>
-      <c r="L13" s="27">
+      <c r="B13" s="12">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="C13" s="12">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="D13" s="13">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="E13" s="13">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="F13" s="14">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="G13" s="14">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="H13" s="15">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="I13" s="15">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="J13" s="16">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="K13" s="16">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="L13" s="17">
         <v>1.1E-5</v>
       </c>
-      <c r="M13" s="27">
-        <v>4.0E-6</v>
-      </c>
-      <c r="N13" s="28">
-        <v>7.0E-6</v>
-      </c>
-      <c r="O13" s="28">
-        <v>6.0E-6</v>
-      </c>
-      <c r="P13" s="29">
-        <v>4.0E-6</v>
-      </c>
-      <c r="Q13" s="29">
-        <v>3.0E-6</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
+      <c r="M13" s="17">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="N13" s="18">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="O13" s="18">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="P13" s="19">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="Q13" s="19">
+        <v>3.0000000000000001E-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="22">
-        <v>4.0E-6</v>
-      </c>
-      <c r="C14" s="22">
-        <v>3.0E-6</v>
-      </c>
-      <c r="D14" s="23">
-        <v>1.3E-5</v>
-      </c>
-      <c r="E14" s="23">
-        <v>6.0E-6</v>
-      </c>
-      <c r="F14" s="24">
-        <v>5.0E-6</v>
-      </c>
-      <c r="G14" s="24">
-        <v>6.0E-6</v>
-      </c>
-      <c r="H14" s="25">
-        <v>3.0E-6</v>
-      </c>
-      <c r="I14" s="25">
-        <v>3.0E-6</v>
-      </c>
-      <c r="J14" s="26">
-        <v>7.0E-6</v>
-      </c>
-      <c r="K14" s="26">
-        <v>7.0E-6</v>
-      </c>
-      <c r="L14" s="27">
+      <c r="B14" s="12">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="C14" s="12">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="D14" s="13">
+        <v>1.2999999999999999E-5</v>
+      </c>
+      <c r="E14" s="13">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="F14" s="14">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="G14" s="14">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="H14" s="15">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="I14" s="15">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="J14" s="16">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="K14" s="16">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="L14" s="17">
         <v>1.1E-5</v>
       </c>
-      <c r="M14" s="27">
-        <v>3.0E-6</v>
-      </c>
-      <c r="N14" s="28">
-        <v>6.0E-6</v>
-      </c>
-      <c r="O14" s="28">
-        <v>6.0E-6</v>
-      </c>
-      <c r="P14" s="29">
-        <v>3.0E-6</v>
-      </c>
-      <c r="Q14" s="29">
-        <v>3.0E-6</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
+      <c r="M14" s="17">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="N14" s="18">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="O14" s="18">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="P14" s="19">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="Q14" s="19">
+        <v>3.0000000000000001E-6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="22">
-        <v>4.0E-6</v>
-      </c>
-      <c r="C15" s="22">
-        <v>3.0E-6</v>
-      </c>
-      <c r="D15" s="23">
-        <v>7.0E-6</v>
-      </c>
-      <c r="E15" s="23">
-        <v>6.0E-6</v>
-      </c>
-      <c r="F15" s="24">
-        <v>5.0E-6</v>
-      </c>
-      <c r="G15" s="24">
-        <v>5.0E-6</v>
-      </c>
-      <c r="H15" s="25">
-        <v>4.0E-6</v>
-      </c>
-      <c r="I15" s="25">
-        <v>4.0E-6</v>
-      </c>
-      <c r="J15" s="26">
-        <v>6.0E-6</v>
-      </c>
-      <c r="K15" s="26">
-        <v>8.0E-6</v>
-      </c>
-      <c r="L15" s="27">
+      <c r="B15" s="12">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="C15" s="12">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="D15" s="13">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="E15" s="13">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="F15" s="14">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="H15" s="15">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="I15" s="15">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="J15" s="16">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="K15" s="16">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="L15" s="17">
         <v>1.2E-5</v>
       </c>
-      <c r="M15" s="27">
-        <v>4.0E-6</v>
-      </c>
-      <c r="N15" s="28">
-        <v>7.0E-6</v>
-      </c>
-      <c r="O15" s="28">
-        <v>6.0E-6</v>
-      </c>
-      <c r="P15" s="29">
-        <v>3.0E-6</v>
-      </c>
-      <c r="Q15" s="29">
-        <v>3.0E-6</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
+      <c r="M15" s="17">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="N15" s="18">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="O15" s="18">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="P15" s="19">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="Q15" s="19">
+        <v>3.0000000000000001E-6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="30">
-        <f t="shared" ref="B16:Q16" si="3">AVERAGE(B13:B15)</f>
-        <v>0.000003666666667</v>
-      </c>
-      <c r="C16" s="30">
-        <f t="shared" si="3"/>
-        <v>0.000003333333333</v>
-      </c>
-      <c r="D16" s="23">
-        <f t="shared" si="3"/>
-        <v>0.000009</v>
-      </c>
-      <c r="E16" s="23">
-        <f t="shared" si="3"/>
-        <v>0.000006</v>
-      </c>
-      <c r="F16" s="24">
-        <f t="shared" si="3"/>
-        <v>0.000005</v>
-      </c>
-      <c r="G16" s="24">
-        <f t="shared" si="3"/>
-        <v>0.000005</v>
-      </c>
-      <c r="H16" s="32">
-        <f t="shared" si="3"/>
-        <v>0.000003666666667</v>
-      </c>
-      <c r="I16" s="32">
-        <f t="shared" si="3"/>
-        <v>0.000003666666667</v>
-      </c>
-      <c r="J16" s="33">
-        <f t="shared" si="3"/>
-        <v>0.000006666666667</v>
-      </c>
-      <c r="K16" s="33">
-        <f t="shared" si="3"/>
-        <v>0.000006666666667</v>
-      </c>
-      <c r="L16" s="34">
-        <f t="shared" si="3"/>
-        <v>0.00001133333333</v>
-      </c>
-      <c r="M16" s="34">
-        <f t="shared" si="3"/>
-        <v>0.000003666666667</v>
-      </c>
-      <c r="N16" s="35">
-        <f t="shared" si="3"/>
-        <v>0.000006666666667</v>
-      </c>
-      <c r="O16" s="28">
-        <f t="shared" si="3"/>
-        <v>0.000006</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" si="3"/>
-        <v>0.000003333333333</v>
-      </c>
-      <c r="Q16" s="29">
-        <f t="shared" si="3"/>
-        <v>0.000003</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="12">
-        <v>100.0</v>
-      </c>
-      <c r="B17" s="37" t="s">
+      <c r="B16" s="20">
+        <f t="shared" ref="B16:Q16" si="2">AVERAGE(B13:B15)</f>
+        <v>3.6666666666666666E-6</v>
+      </c>
+      <c r="C16" s="20">
+        <f t="shared" si="2"/>
+        <v>3.3333333333333329E-6</v>
+      </c>
+      <c r="D16" s="13">
+        <f t="shared" si="2"/>
+        <v>9.0000000000000002E-6</v>
+      </c>
+      <c r="E16" s="13">
+        <f t="shared" si="2"/>
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="F16" s="14">
+        <f t="shared" si="2"/>
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="G16" s="14">
+        <f t="shared" si="2"/>
+        <v>4.9999999999999996E-6</v>
+      </c>
+      <c r="H16" s="22">
+        <f t="shared" si="2"/>
+        <v>3.6666666666666666E-6</v>
+      </c>
+      <c r="I16" s="22">
+        <f t="shared" si="2"/>
+        <v>3.6666666666666666E-6</v>
+      </c>
+      <c r="J16" s="23">
+        <f t="shared" si="2"/>
+        <v>6.6666666666666658E-6</v>
+      </c>
+      <c r="K16" s="23">
+        <f t="shared" si="2"/>
+        <v>6.6666666666666658E-6</v>
+      </c>
+      <c r="L16" s="24">
+        <f t="shared" si="2"/>
+        <v>1.1333333333333334E-5</v>
+      </c>
+      <c r="M16" s="24">
+        <f t="shared" si="2"/>
+        <v>3.6666666666666666E-6</v>
+      </c>
+      <c r="N16" s="25">
+        <f t="shared" si="2"/>
+        <v>6.6666666666666675E-6</v>
+      </c>
+      <c r="O16" s="18">
+        <f t="shared" si="2"/>
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="P16" s="26">
+        <f t="shared" si="2"/>
+        <v>3.3333333333333329E-6</v>
+      </c>
+      <c r="Q16" s="19">
+        <f t="shared" si="2"/>
+        <v>3.0000000000000001E-6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A17" s="2">
+        <v>100</v>
+      </c>
+      <c r="B17" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="41" t="s">
+      <c r="H17" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="41" t="s">
+      <c r="I17" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="J17" s="42" t="s">
+      <c r="J17" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="K17" s="42" t="s">
+      <c r="K17" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="43" t="s">
+      <c r="L17" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="M17" s="43" t="s">
+      <c r="M17" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="N17" s="44" t="s">
+      <c r="N17" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="O17" s="44" t="s">
+      <c r="O17" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="P17" s="45" t="s">
+      <c r="P17" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="Q17" s="45" t="s">
+      <c r="Q17" s="35" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="28">
         <v>1.1E-5</v>
       </c>
-      <c r="C18" s="38">
-        <v>8.0E-6</v>
-      </c>
-      <c r="D18" s="39">
-        <v>1.9E-5</v>
-      </c>
-      <c r="E18" s="39">
-        <v>2.0E-5</v>
-      </c>
-      <c r="F18" s="40">
+      <c r="C18" s="28">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="D18" s="29">
+        <v>1.9000000000000001E-5</v>
+      </c>
+      <c r="E18" s="29">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="F18" s="30">
         <v>1.4E-5</v>
       </c>
-      <c r="G18" s="40">
-        <v>1.6E-5</v>
-      </c>
-      <c r="H18" s="41">
-        <v>8.0E-6</v>
-      </c>
-      <c r="I18" s="41">
-        <v>6.0E-6</v>
-      </c>
-      <c r="J18" s="42">
-        <v>9.0E-6</v>
-      </c>
-      <c r="K18" s="42">
-        <v>8.0E-6</v>
-      </c>
-      <c r="L18" s="43">
-        <v>2.2E-5</v>
-      </c>
-      <c r="M18" s="43">
-        <v>4.0E-6</v>
-      </c>
-      <c r="N18" s="44">
-        <v>1.3E-5</v>
-      </c>
-      <c r="O18" s="44">
+      <c r="G18" s="30">
+        <v>1.5999999999999999E-5</v>
+      </c>
+      <c r="H18" s="31">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="I18" s="31">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="J18" s="32">
+        <v>9.0000000000000002E-6</v>
+      </c>
+      <c r="K18" s="32">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="L18" s="33">
+        <v>2.1999999999999999E-5</v>
+      </c>
+      <c r="M18" s="33">
+        <v>3.9999999999999998E-6</v>
+      </c>
+      <c r="N18" s="34">
+        <v>1.2999999999999999E-5</v>
+      </c>
+      <c r="O18" s="34">
         <v>1.1E-5</v>
       </c>
-      <c r="P18" s="45">
-        <v>8.0E-6</v>
-      </c>
-      <c r="Q18" s="45">
-        <v>6.0E-6</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
+      <c r="P18" s="35">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="Q18" s="35">
+        <v>6.0000000000000002E-6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="38">
-        <v>9.0E-6</v>
-      </c>
-      <c r="C19" s="38">
-        <v>8.0E-6</v>
-      </c>
-      <c r="D19" s="39">
-        <v>2.4E-5</v>
-      </c>
-      <c r="E19" s="39">
+      <c r="B19" s="28">
+        <v>9.0000000000000002E-6</v>
+      </c>
+      <c r="C19" s="28">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="D19" s="29">
+        <v>2.4000000000000001E-5</v>
+      </c>
+      <c r="E19" s="29">
         <v>1.8E-5</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="30">
         <v>1.4E-5</v>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="30">
         <v>1.5E-5</v>
       </c>
-      <c r="H19" s="41">
-        <v>7.0E-6</v>
-      </c>
-      <c r="I19" s="41">
-        <v>7.0E-6</v>
-      </c>
-      <c r="J19" s="42">
+      <c r="H19" s="31">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="I19" s="31">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="J19" s="32">
         <v>1.2E-5</v>
       </c>
-      <c r="K19" s="42">
+      <c r="K19" s="32">
         <v>1.1E-5</v>
       </c>
-      <c r="L19" s="43">
-        <v>2.1E-5</v>
-      </c>
-      <c r="M19" s="43">
-        <v>6.0E-6</v>
-      </c>
-      <c r="N19" s="44">
-        <v>1.0E-5</v>
-      </c>
-      <c r="O19" s="44">
+      <c r="L19" s="33">
+        <v>2.0999999999999999E-5</v>
+      </c>
+      <c r="M19" s="33">
+        <v>6.0000000000000002E-6</v>
+      </c>
+      <c r="N19" s="34">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O19" s="34">
         <v>1.4E-5</v>
       </c>
-      <c r="P19" s="45">
-        <v>8.0E-6</v>
-      </c>
-      <c r="Q19" s="45">
-        <v>8.0E-6</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
+      <c r="P19" s="35">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="Q19" s="35">
+        <v>7.9999999999999996E-6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="38">
-        <v>9.0E-6</v>
-      </c>
-      <c r="C20" s="38">
-        <v>9.0E-6</v>
-      </c>
-      <c r="D20" s="39">
+      <c r="B20" s="28">
+        <v>9.0000000000000002E-6</v>
+      </c>
+      <c r="C20" s="28">
+        <v>9.0000000000000002E-6</v>
+      </c>
+      <c r="D20" s="29">
         <v>1.7E-5</v>
       </c>
-      <c r="E20" s="39">
+      <c r="E20" s="29">
         <v>1.7E-5</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="30">
         <v>1.4E-5</v>
       </c>
-      <c r="G20" s="40">
-        <v>1.6E-5</v>
-      </c>
-      <c r="H20" s="41">
-        <v>7.0E-6</v>
-      </c>
-      <c r="I20" s="41">
-        <v>7.0E-6</v>
-      </c>
-      <c r="J20" s="42">
+      <c r="G20" s="30">
+        <v>1.5999999999999999E-5</v>
+      </c>
+      <c r="H20" s="31">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="I20" s="31">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="J20" s="32">
         <v>1.1E-5</v>
       </c>
-      <c r="K20" s="42">
+      <c r="K20" s="32">
         <v>1.7E-5</v>
       </c>
-      <c r="L20" s="43">
-        <v>2.1E-5</v>
-      </c>
-      <c r="M20" s="43">
-        <v>5.0E-6</v>
-      </c>
-      <c r="N20" s="44">
+      <c r="L20" s="33">
+        <v>2.0999999999999999E-5</v>
+      </c>
+      <c r="M20" s="33">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="N20" s="34">
         <v>1.1E-5</v>
       </c>
-      <c r="O20" s="44">
+      <c r="O20" s="34">
         <v>1.2E-5</v>
       </c>
-      <c r="P20" s="45">
-        <v>7.0E-6</v>
-      </c>
-      <c r="Q20" s="45">
-        <v>6.0E-6</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
+      <c r="P20" s="35">
+        <v>6.9999999999999999E-6</v>
+      </c>
+      <c r="Q20" s="35">
+        <v>6.0000000000000002E-6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="46">
-        <f t="shared" ref="B21:Q21" si="4">AVERAGE(B18:B20)</f>
-        <v>0.000009666666667</v>
-      </c>
-      <c r="C21" s="46">
-        <f t="shared" si="4"/>
-        <v>0.000008333333333</v>
-      </c>
-      <c r="D21" s="39">
-        <f t="shared" si="4"/>
-        <v>0.00002</v>
-      </c>
-      <c r="E21" s="47">
-        <f t="shared" si="4"/>
-        <v>0.00001833333333</v>
-      </c>
-      <c r="F21" s="40">
-        <f t="shared" si="4"/>
-        <v>0.000014</v>
-      </c>
-      <c r="G21" s="48">
-        <f t="shared" si="4"/>
-        <v>0.00001566666667</v>
-      </c>
-      <c r="H21" s="49">
-        <f t="shared" si="4"/>
-        <v>0.000007333333333</v>
-      </c>
-      <c r="I21" s="49">
-        <f t="shared" si="4"/>
-        <v>0.000006666666667</v>
-      </c>
-      <c r="J21" s="42">
-        <f t="shared" si="4"/>
-        <v>0.00001066666667</v>
-      </c>
-      <c r="K21" s="42">
-        <f t="shared" si="4"/>
-        <v>0.000012</v>
-      </c>
-      <c r="L21" s="43">
-        <f t="shared" si="4"/>
-        <v>0.00002133333333</v>
-      </c>
-      <c r="M21" s="43">
-        <f t="shared" si="4"/>
-        <v>0.000005</v>
-      </c>
-      <c r="N21" s="44">
-        <f t="shared" si="4"/>
-        <v>0.00001133333333</v>
-      </c>
-      <c r="O21" s="44">
-        <f t="shared" si="4"/>
-        <v>0.00001233333333</v>
-      </c>
-      <c r="P21" s="45">
-        <f t="shared" si="4"/>
-        <v>0.000007666666667</v>
-      </c>
-      <c r="Q21" s="45">
-        <f t="shared" si="4"/>
-        <v>0.000006666666667</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12">
-        <v>1000.0</v>
-      </c>
-      <c r="B22" s="53" t="s">
+      <c r="B21" s="36">
+        <f t="shared" ref="B21:Q21" si="3">AVERAGE(B18:B20)</f>
+        <v>9.6666666666666667E-6</v>
+      </c>
+      <c r="C21" s="36">
+        <f t="shared" si="3"/>
+        <v>8.333333333333332E-6</v>
+      </c>
+      <c r="D21" s="29">
+        <f t="shared" si="3"/>
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="E21" s="37">
+        <f t="shared" si="3"/>
+        <v>1.8333333333333333E-5</v>
+      </c>
+      <c r="F21" s="30">
+        <f t="shared" si="3"/>
+        <v>1.4E-5</v>
+      </c>
+      <c r="G21" s="38">
+        <f t="shared" si="3"/>
+        <v>1.5666666666666667E-5</v>
+      </c>
+      <c r="H21" s="39">
+        <f t="shared" si="3"/>
+        <v>7.3333333333333331E-6</v>
+      </c>
+      <c r="I21" s="39">
+        <f t="shared" si="3"/>
+        <v>6.6666666666666675E-6</v>
+      </c>
+      <c r="J21" s="32">
+        <f t="shared" si="3"/>
+        <v>1.0666666666666669E-5</v>
+      </c>
+      <c r="K21" s="32">
+        <f t="shared" si="3"/>
+        <v>1.2E-5</v>
+      </c>
+      <c r="L21" s="33">
+        <f t="shared" si="3"/>
+        <v>2.1333333333333331E-5</v>
+      </c>
+      <c r="M21" s="33">
+        <f t="shared" si="3"/>
+        <v>4.9999999999999996E-6</v>
+      </c>
+      <c r="N21" s="34">
+        <f t="shared" si="3"/>
+        <v>1.1333333333333334E-5</v>
+      </c>
+      <c r="O21" s="34">
+        <f t="shared" si="3"/>
+        <v>1.2333333333333333E-5</v>
+      </c>
+      <c r="P21" s="35">
+        <f t="shared" si="3"/>
+        <v>7.6666666666666672E-6</v>
+      </c>
+      <c r="Q21" s="35">
+        <f t="shared" si="3"/>
+        <v>6.6666666666666658E-6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A22" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B22" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="24" t="s">
+      <c r="G22" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="25" t="s">
+      <c r="H22" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="25" t="s">
+      <c r="I22" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J22" s="26" t="s">
+      <c r="J22" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="K22" s="26" t="s">
+      <c r="K22" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="L22" s="27" t="s">
+      <c r="L22" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="M22" s="27" t="s">
+      <c r="M22" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="28" t="s">
+      <c r="N22" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="O22" s="28" t="s">
+      <c r="O22" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="29" t="s">
+      <c r="P22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="Q22" s="29" t="s">
+      <c r="Q22" s="19" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="22">
-        <v>6.53E-4</v>
-      </c>
-      <c r="C23" s="22">
-        <v>7.82E-4</v>
-      </c>
-      <c r="D23" s="23">
-        <v>0.001336</v>
-      </c>
-      <c r="E23" s="23">
-        <v>0.001403</v>
-      </c>
-      <c r="F23" s="24">
-        <v>7.88E-4</v>
-      </c>
-      <c r="G23" s="24">
-        <v>7.89E-4</v>
-      </c>
-      <c r="H23" s="25">
-        <v>8.8E-5</v>
-      </c>
-      <c r="I23" s="25">
-        <v>8.7E-5</v>
-      </c>
-      <c r="J23" s="26">
-        <v>8.0E-5</v>
-      </c>
-      <c r="K23" s="26">
-        <v>7.9E-5</v>
-      </c>
-      <c r="L23" s="27">
+      <c r="B23" s="12">
+        <v>6.5300000000000004E-4</v>
+      </c>
+      <c r="C23" s="12">
+        <v>7.8200000000000003E-4</v>
+      </c>
+      <c r="D23" s="13">
+        <v>1.3359999999999999E-3</v>
+      </c>
+      <c r="E23" s="13">
+        <v>1.403E-3</v>
+      </c>
+      <c r="F23" s="14">
+        <v>7.8799999999999996E-4</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7.8899999999999999E-4</v>
+      </c>
+      <c r="H23" s="15">
+        <v>8.7999999999999998E-5</v>
+      </c>
+      <c r="I23" s="15">
+        <v>8.7000000000000001E-5</v>
+      </c>
+      <c r="J23" s="16">
+        <v>8.0000000000000007E-5</v>
+      </c>
+      <c r="K23" s="16">
+        <v>7.8999999999999996E-5</v>
+      </c>
+      <c r="L23" s="17">
         <v>1.35E-4</v>
       </c>
-      <c r="M23" s="27">
-        <v>5.9E-5</v>
-      </c>
-      <c r="N23" s="28">
+      <c r="M23" s="17">
+        <v>5.8999999999999998E-5</v>
+      </c>
+      <c r="N23" s="18">
         <v>1.46E-4</v>
       </c>
-      <c r="O23" s="28">
-        <v>1.5E-4</v>
-      </c>
-      <c r="P23" s="29">
-        <v>9.6E-5</v>
-      </c>
-      <c r="Q23" s="29">
-        <v>9.9E-5</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
+      <c r="O23" s="18">
+        <v>1.4999999999999999E-4</v>
+      </c>
+      <c r="P23" s="19">
+        <v>9.6000000000000002E-5</v>
+      </c>
+      <c r="Q23" s="19">
+        <v>9.8999999999999994E-5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="22">
-        <v>9.07E-4</v>
-      </c>
-      <c r="C24" s="22">
-        <v>6.94E-4</v>
-      </c>
-      <c r="D24" s="23">
-        <v>0.001543</v>
-      </c>
-      <c r="E24" s="23">
-        <v>0.001336</v>
-      </c>
-      <c r="F24" s="24">
-        <v>0.001389</v>
-      </c>
-      <c r="G24" s="24">
-        <v>7.82E-4</v>
-      </c>
-      <c r="H24" s="25">
+      <c r="B24" s="12">
+        <v>9.0700000000000004E-4</v>
+      </c>
+      <c r="C24" s="12">
+        <v>6.9399999999999996E-4</v>
+      </c>
+      <c r="D24" s="13">
+        <v>1.5430000000000001E-3</v>
+      </c>
+      <c r="E24" s="13">
+        <v>1.3359999999999999E-3</v>
+      </c>
+      <c r="F24" s="14">
+        <v>1.389E-3</v>
+      </c>
+      <c r="G24" s="14">
+        <v>7.8200000000000003E-4</v>
+      </c>
+      <c r="H24" s="15">
         <v>1.01E-4</v>
       </c>
-      <c r="I24" s="25">
-        <v>8.3E-5</v>
-      </c>
-      <c r="J24" s="26">
-        <v>1.51E-4</v>
-      </c>
-      <c r="K24" s="26">
-        <v>7.9E-5</v>
-      </c>
-      <c r="L24" s="27">
-        <v>2.07E-4</v>
-      </c>
-      <c r="M24" s="27">
+      <c r="I24" s="15">
+        <v>8.2999999999999998E-5</v>
+      </c>
+      <c r="J24" s="16">
+        <v>1.5100000000000001E-4</v>
+      </c>
+      <c r="K24" s="16">
+        <v>7.8999999999999996E-5</v>
+      </c>
+      <c r="L24" s="17">
+        <v>2.0699999999999999E-4</v>
+      </c>
+      <c r="M24" s="17">
         <v>5.8E-5</v>
       </c>
-      <c r="N24" s="28">
-        <v>1.91E-4</v>
-      </c>
-      <c r="O24" s="28">
+      <c r="N24" s="18">
+        <v>1.9100000000000001E-4</v>
+      </c>
+      <c r="O24" s="18">
         <v>1.47E-4</v>
       </c>
-      <c r="P24" s="29">
+      <c r="P24" s="19">
         <v>1.08E-4</v>
       </c>
-      <c r="Q24" s="29">
-        <v>8.9E-5</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
+      <c r="Q24" s="19">
+        <v>8.8999999999999995E-5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="22">
-        <v>7.06E-4</v>
-      </c>
-      <c r="C25" s="22">
-        <v>6.88E-4</v>
-      </c>
-      <c r="D25" s="23">
-        <v>0.001337</v>
-      </c>
-      <c r="E25" s="23">
-        <v>0.001571</v>
-      </c>
-      <c r="F25" s="24">
-        <v>0.001094</v>
-      </c>
-      <c r="G25" s="24">
-        <v>0.001023</v>
-      </c>
-      <c r="H25" s="25">
-        <v>9.6E-5</v>
-      </c>
-      <c r="I25" s="25">
+      <c r="B25" s="12">
+        <v>7.0600000000000003E-4</v>
+      </c>
+      <c r="C25" s="12">
+        <v>6.8800000000000003E-4</v>
+      </c>
+      <c r="D25" s="13">
+        <v>1.3370000000000001E-3</v>
+      </c>
+      <c r="E25" s="13">
+        <v>1.5709999999999999E-3</v>
+      </c>
+      <c r="F25" s="14">
+        <v>1.0939999999999999E-3</v>
+      </c>
+      <c r="G25" s="14">
+        <v>1.023E-3</v>
+      </c>
+      <c r="H25" s="15">
+        <v>9.6000000000000002E-5</v>
+      </c>
+      <c r="I25" s="15">
         <v>9.7E-5</v>
       </c>
-      <c r="J25" s="26">
-        <v>7.6E-5</v>
-      </c>
-      <c r="K25" s="26">
+      <c r="J25" s="16">
+        <v>7.6000000000000004E-5</v>
+      </c>
+      <c r="K25" s="16">
         <v>1.03E-4</v>
       </c>
-      <c r="L25" s="27">
+      <c r="L25" s="17">
         <v>1.34E-4</v>
       </c>
-      <c r="M25" s="27">
-        <v>8.1E-5</v>
-      </c>
-      <c r="N25" s="28">
+      <c r="M25" s="17">
+        <v>8.1000000000000004E-5</v>
+      </c>
+      <c r="N25" s="18">
         <v>1.66E-4</v>
       </c>
-      <c r="O25" s="28">
+      <c r="O25" s="18">
         <v>1.45E-4</v>
       </c>
-      <c r="P25" s="29">
-        <v>8.8E-5</v>
-      </c>
-      <c r="Q25" s="29">
+      <c r="P25" s="19">
+        <v>8.7999999999999998E-5</v>
+      </c>
+      <c r="Q25" s="19">
         <v>1.1E-4</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="30">
-        <f t="shared" ref="B26:Q26" si="5">AVERAGE(B23:B25)</f>
-        <v>0.0007553333333</v>
-      </c>
-      <c r="C26" s="22">
-        <f t="shared" si="5"/>
-        <v>0.0007213333333</v>
-      </c>
-      <c r="D26" s="54">
-        <f t="shared" si="5"/>
-        <v>0.001405333333</v>
-      </c>
-      <c r="E26" s="23">
-        <f t="shared" si="5"/>
-        <v>0.001436666667</v>
-      </c>
-      <c r="F26" s="31">
-        <f t="shared" si="5"/>
-        <v>0.001090333333</v>
-      </c>
-      <c r="G26" s="24">
-        <f t="shared" si="5"/>
-        <v>0.0008646666667</v>
-      </c>
-      <c r="H26" s="25">
-        <f t="shared" si="5"/>
-        <v>0.000095</v>
-      </c>
-      <c r="I26" s="25">
-        <f t="shared" si="5"/>
-        <v>0.000089</v>
-      </c>
-      <c r="J26" s="33">
-        <f t="shared" si="5"/>
-        <v>0.0001023333333</v>
-      </c>
-      <c r="K26" s="26">
-        <f t="shared" si="5"/>
-        <v>0.000087</v>
-      </c>
-      <c r="L26" s="34">
-        <f t="shared" si="5"/>
-        <v>0.0001586666667</v>
-      </c>
-      <c r="M26" s="27">
-        <f t="shared" si="5"/>
-        <v>0.000066</v>
-      </c>
-      <c r="N26" s="35">
-        <f t="shared" si="5"/>
-        <v>0.0001676666667</v>
-      </c>
-      <c r="O26" s="28">
-        <f t="shared" si="5"/>
-        <v>0.0001473333333</v>
-      </c>
-      <c r="P26" s="36">
-        <f t="shared" si="5"/>
-        <v>0.00009733333333</v>
-      </c>
-      <c r="Q26" s="29">
-        <f t="shared" si="5"/>
-        <v>0.00009933333333</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="12">
-        <v>10000.0</v>
-      </c>
-      <c r="B27" s="37" t="s">
+      <c r="B26" s="20">
+        <f t="shared" ref="B26:Q26" si="4">AVERAGE(B23:B25)</f>
+        <v>7.5533333333333344E-4</v>
+      </c>
+      <c r="C26" s="12">
+        <f t="shared" si="4"/>
+        <v>7.2133333333333337E-4</v>
+      </c>
+      <c r="D26" s="44">
+        <f t="shared" si="4"/>
+        <v>1.4053333333333333E-3</v>
+      </c>
+      <c r="E26" s="13">
+        <f t="shared" si="4"/>
+        <v>1.4366666666666666E-3</v>
+      </c>
+      <c r="F26" s="21">
+        <f t="shared" si="4"/>
+        <v>1.0903333333333333E-3</v>
+      </c>
+      <c r="G26" s="14">
+        <f t="shared" si="4"/>
+        <v>8.6466666666666669E-4</v>
+      </c>
+      <c r="H26" s="15">
+        <f t="shared" si="4"/>
+        <v>9.4999999999999992E-5</v>
+      </c>
+      <c r="I26" s="15">
+        <f t="shared" si="4"/>
+        <v>8.8999999999999995E-5</v>
+      </c>
+      <c r="J26" s="23">
+        <f t="shared" si="4"/>
+        <v>1.0233333333333335E-4</v>
+      </c>
+      <c r="K26" s="16">
+        <f t="shared" si="4"/>
+        <v>8.7000000000000001E-5</v>
+      </c>
+      <c r="L26" s="24">
+        <f t="shared" si="4"/>
+        <v>1.5866666666666666E-4</v>
+      </c>
+      <c r="M26" s="17">
+        <f t="shared" si="4"/>
+        <v>6.5999999999999992E-5</v>
+      </c>
+      <c r="N26" s="25">
+        <f t="shared" si="4"/>
+        <v>1.6766666666666666E-4</v>
+      </c>
+      <c r="O26" s="18">
+        <f t="shared" si="4"/>
+        <v>1.4733333333333333E-4</v>
+      </c>
+      <c r="P26" s="26">
+        <f t="shared" si="4"/>
+        <v>9.7333333333333332E-5</v>
+      </c>
+      <c r="Q26" s="19">
+        <f t="shared" si="4"/>
+        <v>9.9333333333333326E-5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A27" s="2">
+        <v>10000</v>
+      </c>
+      <c r="B27" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="39" t="s">
+      <c r="D27" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="39" t="s">
+      <c r="E27" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="F27" s="40" t="s">
+      <c r="F27" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="G27" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H27" s="41" t="s">
+      <c r="H27" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="I27" s="41" t="s">
+      <c r="I27" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="J27" s="42" t="s">
+      <c r="J27" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="K27" s="42" t="s">
+      <c r="K27" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="L27" s="43" t="s">
+      <c r="L27" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="M27" s="43" t="s">
+      <c r="M27" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="N27" s="44" t="s">
+      <c r="N27" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="O27" s="44" t="s">
+      <c r="O27" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="P27" s="45" t="s">
+      <c r="P27" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="Q27" s="45" t="s">
+      <c r="Q27" s="35" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="38">
-        <v>0.021</v>
-      </c>
-      <c r="C28" s="38">
-        <v>0.021</v>
-      </c>
-      <c r="D28" s="39">
-        <v>0.031</v>
-      </c>
-      <c r="E28" s="39">
-        <v>0.032</v>
-      </c>
-      <c r="F28" s="40">
-        <v>0.026</v>
-      </c>
-      <c r="G28" s="40">
-        <v>0.026</v>
-      </c>
-      <c r="H28" s="41">
-        <v>0.001</v>
-      </c>
-      <c r="I28" s="41">
-        <v>0.001</v>
-      </c>
-      <c r="J28" s="42">
-        <v>0.001</v>
-      </c>
-      <c r="K28" s="42">
-        <v>0.001</v>
-      </c>
-      <c r="L28" s="43">
-        <v>0.001</v>
-      </c>
-      <c r="M28" s="43">
-        <v>0.001</v>
-      </c>
-      <c r="N28" s="44">
-        <v>0.001</v>
-      </c>
-      <c r="O28" s="44">
-        <v>0.001</v>
-      </c>
-      <c r="P28" s="45">
-        <v>0.001</v>
-      </c>
-      <c r="Q28" s="45">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
+      <c r="B28" s="28">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="C28" s="28">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D28" s="29">
+        <v>3.1E-2</v>
+      </c>
+      <c r="E28" s="29">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F28" s="30">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="G28" s="30">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="H28" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="I28" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="J28" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="K28" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="L28" s="33">
+        <v>1E-3</v>
+      </c>
+      <c r="M28" s="33">
+        <v>1E-3</v>
+      </c>
+      <c r="N28" s="34">
+        <v>1E-3</v>
+      </c>
+      <c r="O28" s="34">
+        <v>1E-3</v>
+      </c>
+      <c r="P28" s="35">
+        <v>1E-3</v>
+      </c>
+      <c r="Q28" s="35">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="38">
+      <c r="B29" s="28">
         <v>0.02</v>
       </c>
-      <c r="C29" s="38">
+      <c r="C29" s="28">
         <v>0.02</v>
       </c>
-      <c r="D29" s="39">
-        <v>0.032</v>
-      </c>
-      <c r="E29" s="39">
-        <v>0.032</v>
-      </c>
-      <c r="F29" s="40">
-        <v>0.025</v>
-      </c>
-      <c r="G29" s="40">
-        <v>0.025</v>
-      </c>
-      <c r="H29" s="41">
-        <v>0.001</v>
-      </c>
-      <c r="I29" s="41">
-        <v>0.001</v>
-      </c>
-      <c r="J29" s="42">
-        <v>0.001</v>
-      </c>
-      <c r="K29" s="42">
-        <v>0.001</v>
-      </c>
-      <c r="L29" s="43">
-        <v>0.001</v>
-      </c>
-      <c r="M29" s="43">
-        <v>0.001</v>
-      </c>
-      <c r="N29" s="44">
-        <v>0.001</v>
-      </c>
-      <c r="O29" s="44">
-        <v>0.001</v>
-      </c>
-      <c r="P29" s="45">
-        <v>0.001</v>
-      </c>
-      <c r="Q29" s="45">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
+      <c r="D29" s="29">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="E29" s="29">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F29" s="30">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G29" s="30">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="H29" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="I29" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="J29" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="K29" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="L29" s="33">
+        <v>1E-3</v>
+      </c>
+      <c r="M29" s="33">
+        <v>1E-3</v>
+      </c>
+      <c r="N29" s="34">
+        <v>1E-3</v>
+      </c>
+      <c r="O29" s="34">
+        <v>1E-3</v>
+      </c>
+      <c r="P29" s="35">
+        <v>1E-3</v>
+      </c>
+      <c r="Q29" s="35">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B30" s="38">
-        <v>0.021</v>
-      </c>
-      <c r="C30" s="38">
+      <c r="B30" s="28">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="C30" s="28">
         <v>0.02</v>
       </c>
-      <c r="D30" s="39">
-        <v>0.033</v>
-      </c>
-      <c r="E30" s="39">
-        <v>0.032</v>
-      </c>
-      <c r="F30" s="40">
+      <c r="D30" s="29">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="E30" s="29">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F30" s="30">
         <v>0.25</v>
       </c>
-      <c r="G30" s="40">
+      <c r="G30" s="30">
         <v>0.25</v>
       </c>
-      <c r="H30" s="41">
-        <v>0.001</v>
-      </c>
-      <c r="I30" s="41">
-        <v>0.001</v>
-      </c>
-      <c r="J30" s="42">
-        <v>0.001</v>
-      </c>
-      <c r="K30" s="42">
-        <v>0.001</v>
-      </c>
-      <c r="L30" s="43">
-        <v>0.001</v>
-      </c>
-      <c r="M30" s="43">
-        <v>0.001</v>
-      </c>
-      <c r="N30" s="44">
-        <v>0.001</v>
-      </c>
-      <c r="O30" s="44">
-        <v>0.001</v>
-      </c>
-      <c r="P30" s="45">
-        <v>0.001</v>
-      </c>
-      <c r="Q30" s="45">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
+      <c r="H30" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="I30" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="J30" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="K30" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="L30" s="33">
+        <v>1E-3</v>
+      </c>
+      <c r="M30" s="33">
+        <v>1E-3</v>
+      </c>
+      <c r="N30" s="34">
+        <v>1E-3</v>
+      </c>
+      <c r="O30" s="34">
+        <v>1E-3</v>
+      </c>
+      <c r="P30" s="35">
+        <v>1E-3</v>
+      </c>
+      <c r="Q30" s="35">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B31" s="38">
-        <f t="shared" ref="B31:G31" si="6">AVERAGE(B28:B30)</f>
-        <v>0.02066666667</v>
-      </c>
-      <c r="C31" s="38">
-        <f t="shared" si="6"/>
-        <v>0.02033333333</v>
-      </c>
-      <c r="D31" s="39">
-        <f t="shared" si="6"/>
-        <v>0.032</v>
-      </c>
-      <c r="E31" s="39">
-        <f t="shared" si="6"/>
-        <v>0.032</v>
-      </c>
-      <c r="F31" s="40">
-        <f t="shared" si="6"/>
-        <v>0.1003333333</v>
-      </c>
-      <c r="G31" s="40">
-        <f t="shared" si="6"/>
-        <v>0.1003333333</v>
-      </c>
-      <c r="H31" s="41">
-        <v>0.001</v>
-      </c>
-      <c r="I31" s="41">
-        <v>0.001</v>
-      </c>
-      <c r="J31" s="42">
-        <v>0.001</v>
-      </c>
-      <c r="K31" s="42">
-        <v>0.001</v>
-      </c>
-      <c r="L31" s="43">
-        <v>0.001</v>
-      </c>
-      <c r="M31" s="43">
-        <v>0.001</v>
-      </c>
-      <c r="N31" s="44">
-        <v>0.001</v>
-      </c>
-      <c r="O31" s="44">
-        <v>0.001</v>
-      </c>
-      <c r="P31" s="45">
-        <v>0.001</v>
-      </c>
-      <c r="Q31" s="45">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="12">
-        <v>100000.0</v>
-      </c>
-      <c r="B32" s="53" t="s">
+      <c r="B31" s="28">
+        <f t="shared" ref="B31:G31" si="5">AVERAGE(B28:B30)</f>
+        <v>2.0666666666666667E-2</v>
+      </c>
+      <c r="C31" s="28">
+        <f t="shared" si="5"/>
+        <v>2.0333333333333332E-2</v>
+      </c>
+      <c r="D31" s="29">
+        <f t="shared" si="5"/>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="E31" s="29">
+        <f t="shared" si="5"/>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="F31" s="30">
+        <f t="shared" si="5"/>
+        <v>0.10033333333333333</v>
+      </c>
+      <c r="G31" s="30">
+        <f t="shared" si="5"/>
+        <v>0.10033333333333333</v>
+      </c>
+      <c r="H31" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="I31" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="J31" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="K31" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="L31" s="33">
+        <v>1E-3</v>
+      </c>
+      <c r="M31" s="33">
+        <v>1E-3</v>
+      </c>
+      <c r="N31" s="34">
+        <v>1E-3</v>
+      </c>
+      <c r="O31" s="34">
+        <v>1E-3</v>
+      </c>
+      <c r="P31" s="35">
+        <v>1E-3</v>
+      </c>
+      <c r="Q31" s="35">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A32" s="2">
+        <v>100000</v>
+      </c>
+      <c r="B32" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="24" t="s">
+      <c r="G32" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H32" s="25" t="s">
+      <c r="H32" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I32" s="25" t="s">
+      <c r="I32" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J32" s="26" t="s">
+      <c r="J32" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="K32" s="26" t="s">
+      <c r="K32" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="L32" s="27" t="s">
+      <c r="L32" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="M32" s="27" t="s">
+      <c r="M32" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="N32" s="28" t="s">
+      <c r="N32" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="O32" s="28" t="s">
+      <c r="O32" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="P32" s="29" t="s">
+      <c r="P32" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="Q32" s="29" t="s">
+      <c r="Q32" s="19" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="22">
-        <v>2.094</v>
-      </c>
-      <c r="C33" s="22">
-        <v>2.082</v>
-      </c>
-      <c r="D33" s="23">
+      <c r="B33" s="12">
+        <v>2.0939999999999999</v>
+      </c>
+      <c r="C33" s="12">
+        <v>2.0819999999999999</v>
+      </c>
+      <c r="D33" s="13">
         <v>3.22</v>
       </c>
-      <c r="E33" s="23">
-        <v>3.675</v>
-      </c>
-      <c r="F33" s="24">
-        <v>3.942</v>
-      </c>
-      <c r="G33" s="24">
+      <c r="E33" s="13">
+        <v>3.6749999999999998</v>
+      </c>
+      <c r="F33" s="14">
+        <v>3.9420000000000002</v>
+      </c>
+      <c r="G33" s="14">
         <v>3.202</v>
       </c>
-      <c r="H33" s="25">
-        <v>0.015</v>
-      </c>
-      <c r="I33" s="25">
-        <v>0.006</v>
-      </c>
-      <c r="J33" s="26">
-        <v>0.015</v>
-      </c>
-      <c r="K33" s="26">
-        <v>0.007</v>
-      </c>
-      <c r="L33" s="27">
-        <v>0.024</v>
-      </c>
-      <c r="M33" s="27">
-        <v>0.003</v>
-      </c>
-      <c r="N33" s="28">
-        <v>0.024</v>
-      </c>
-      <c r="O33" s="28">
-        <v>0.019</v>
-      </c>
-      <c r="P33" s="29">
-        <v>0.019</v>
-      </c>
-      <c r="Q33" s="29">
-        <v>0.013</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
+      <c r="H33" s="15">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I33" s="15">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="J33" s="16">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K33" s="16">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="L33" s="17">
+        <v>2.4E-2</v>
+      </c>
+      <c r="M33" s="17">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="N33" s="18">
+        <v>2.4E-2</v>
+      </c>
+      <c r="O33" s="18">
+        <v>1.9E-2</v>
+      </c>
+      <c r="P33" s="19">
+        <v>1.9E-2</v>
+      </c>
+      <c r="Q33" s="19">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B34" s="22">
+      <c r="B34" s="12">
         <v>2.06</v>
       </c>
-      <c r="C34" s="22">
-        <v>2.057</v>
-      </c>
-      <c r="D34" s="23">
+      <c r="C34" s="12">
+        <v>2.0569999999999999</v>
+      </c>
+      <c r="D34" s="13">
         <v>3.11</v>
       </c>
-      <c r="E34" s="23">
-        <v>4.788</v>
-      </c>
-      <c r="F34" s="24">
-        <v>2.498</v>
-      </c>
-      <c r="G34" s="24">
+      <c r="E34" s="13">
+        <v>4.7880000000000003</v>
+      </c>
+      <c r="F34" s="14">
+        <v>2.4980000000000002</v>
+      </c>
+      <c r="G34" s="14">
         <v>3.758</v>
       </c>
-      <c r="H34" s="25">
-        <v>0.007</v>
-      </c>
-      <c r="I34" s="25">
-        <v>0.006</v>
-      </c>
-      <c r="J34" s="26">
+      <c r="H34" s="15">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="I34" s="15">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="J34" s="16">
         <v>0.01</v>
       </c>
-      <c r="K34" s="26">
-        <v>0.008</v>
-      </c>
-      <c r="L34" s="27">
-        <v>0.007</v>
-      </c>
-      <c r="M34" s="27">
-        <v>0.004</v>
-      </c>
-      <c r="N34" s="28">
-        <v>0.013</v>
-      </c>
-      <c r="O34" s="28">
-        <v>0.019</v>
-      </c>
-      <c r="P34" s="29">
+      <c r="K34" s="16">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="L34" s="17">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="M34" s="17">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="N34" s="18">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="O34" s="18">
+        <v>1.9E-2</v>
+      </c>
+      <c r="P34" s="19">
         <v>0.01</v>
       </c>
-      <c r="Q34" s="29">
-        <v>0.012</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
+      <c r="Q34" s="19">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="22">
-        <v>2.078</v>
-      </c>
-      <c r="C35" s="22">
-        <v>2.062</v>
-      </c>
-      <c r="D35" s="23">
-        <v>3.126</v>
-      </c>
-      <c r="E35" s="23">
+      <c r="B35" s="12">
+        <v>2.0779999999999998</v>
+      </c>
+      <c r="C35" s="12">
+        <v>2.0619999999999998</v>
+      </c>
+      <c r="D35" s="13">
+        <v>3.1259999999999999</v>
+      </c>
+      <c r="E35" s="13">
         <v>4.758</v>
       </c>
-      <c r="F35" s="24">
-        <v>2.549</v>
-      </c>
-      <c r="G35" s="24">
-        <v>4.168</v>
-      </c>
-      <c r="H35" s="25">
-        <v>0.007</v>
-      </c>
-      <c r="I35" s="25">
-        <v>0.009</v>
-      </c>
-      <c r="J35" s="26">
+      <c r="F35" s="14">
+        <v>2.5489999999999999</v>
+      </c>
+      <c r="G35" s="14">
+        <v>4.1680000000000001</v>
+      </c>
+      <c r="H35" s="15">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="I35" s="15">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="J35" s="16">
         <v>0.01</v>
       </c>
-      <c r="K35" s="26">
-        <v>0.012</v>
-      </c>
-      <c r="L35" s="27">
-        <v>0.007</v>
-      </c>
-      <c r="M35" s="27">
-        <v>0.013</v>
-      </c>
-      <c r="N35" s="28">
-        <v>0.014</v>
-      </c>
-      <c r="O35" s="28">
-        <v>0.019</v>
-      </c>
-      <c r="P35" s="29">
-        <v>0.009</v>
-      </c>
-      <c r="Q35" s="29">
-        <v>0.014</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
+      <c r="K35" s="16">
+        <v>1.2E-2</v>
+      </c>
+      <c r="L35" s="17">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="M35" s="17">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="N35" s="18">
+        <v>1.4E-2</v>
+      </c>
+      <c r="O35" s="18">
+        <v>1.9E-2</v>
+      </c>
+      <c r="P35" s="19">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="Q35" s="19">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B36" s="22">
-        <f t="shared" ref="B36:Q36" si="7">AVERAGE(B33:B35)</f>
-        <v>2.077333333</v>
-      </c>
-      <c r="C36" s="22">
-        <f t="shared" si="7"/>
-        <v>2.067</v>
-      </c>
-      <c r="D36" s="23">
-        <f t="shared" si="7"/>
-        <v>3.152</v>
-      </c>
-      <c r="E36" s="23">
-        <f t="shared" si="7"/>
+      <c r="B36" s="12">
+        <f t="shared" ref="B36:Q36" si="6">AVERAGE(B33:B35)</f>
+        <v>2.0773333333333333</v>
+      </c>
+      <c r="C36" s="12">
+        <f t="shared" si="6"/>
+        <v>2.0669999999999997</v>
+      </c>
+      <c r="D36" s="13">
+        <f t="shared" si="6"/>
+        <v>3.1519999999999997</v>
+      </c>
+      <c r="E36" s="13">
+        <f t="shared" si="6"/>
         <v>4.407</v>
       </c>
-      <c r="F36" s="24">
-        <f t="shared" si="7"/>
-        <v>2.996333333</v>
-      </c>
-      <c r="G36" s="55">
-        <f t="shared" si="7"/>
-        <v>3.709333333</v>
-      </c>
-      <c r="H36" s="32">
-        <f t="shared" si="7"/>
-        <v>0.009666666667</v>
-      </c>
-      <c r="I36" s="25">
-        <f t="shared" si="7"/>
-        <v>0.007</v>
-      </c>
-      <c r="J36" s="26">
-        <f t="shared" si="7"/>
-        <v>0.01166666667</v>
-      </c>
-      <c r="K36" s="26">
-        <f t="shared" si="7"/>
-        <v>0.009</v>
-      </c>
-      <c r="L36" s="27">
-        <f t="shared" si="7"/>
-        <v>0.01266666667</v>
-      </c>
-      <c r="M36" s="34">
-        <f t="shared" si="7"/>
-        <v>0.006666666667</v>
-      </c>
-      <c r="N36" s="28">
-        <f t="shared" si="7"/>
-        <v>0.017</v>
-      </c>
-      <c r="O36" s="28">
-        <f t="shared" si="7"/>
-        <v>0.019</v>
-      </c>
-      <c r="P36" s="29">
-        <f t="shared" si="7"/>
-        <v>0.01266666667</v>
-      </c>
-      <c r="Q36" s="29">
-        <f t="shared" si="7"/>
-        <v>0.013</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="56">
-        <v>1000000.0</v>
-      </c>
-      <c r="B37" s="37" t="s">
+      <c r="F36" s="14">
+        <f t="shared" si="6"/>
+        <v>2.9963333333333337</v>
+      </c>
+      <c r="G36" s="45">
+        <f t="shared" si="6"/>
+        <v>3.7093333333333334</v>
+      </c>
+      <c r="H36" s="22">
+        <f t="shared" si="6"/>
+        <v>9.6666666666666654E-3</v>
+      </c>
+      <c r="I36" s="15">
+        <f t="shared" si="6"/>
+        <v>6.9999999999999993E-3</v>
+      </c>
+      <c r="J36" s="16">
+        <f t="shared" si="6"/>
+        <v>1.1666666666666667E-2</v>
+      </c>
+      <c r="K36" s="16">
+        <f t="shared" si="6"/>
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="L36" s="17">
+        <f t="shared" si="6"/>
+        <v>1.2666666666666666E-2</v>
+      </c>
+      <c r="M36" s="24">
+        <f t="shared" si="6"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="N36" s="18">
+        <f t="shared" si="6"/>
+        <v>1.6999999999999998E-2</v>
+      </c>
+      <c r="O36" s="18">
+        <f t="shared" si="6"/>
+        <v>1.9E-2</v>
+      </c>
+      <c r="P36" s="19">
+        <f t="shared" si="6"/>
+        <v>1.2666666666666666E-2</v>
+      </c>
+      <c r="Q36" s="19">
+        <f t="shared" si="6"/>
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A37" s="46">
+        <v>1000000</v>
+      </c>
+      <c r="B37" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="38" t="s">
+      <c r="C37" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D37" s="39" t="s">
+      <c r="D37" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="39" t="s">
+      <c r="E37" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="40" t="s">
+      <c r="F37" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="G37" s="40" t="s">
+      <c r="G37" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H37" s="41" t="s">
+      <c r="H37" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="I37" s="41" t="s">
+      <c r="I37" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="J37" s="42" t="s">
+      <c r="J37" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="K37" s="42" t="s">
+      <c r="K37" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="L37" s="43" t="s">
+      <c r="L37" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="M37" s="43" t="s">
+      <c r="M37" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="N37" s="44" t="s">
+      <c r="N37" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="O37" s="44" t="s">
+      <c r="O37" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="Q37" s="45" t="s">
+      <c r="Q37" s="35" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="57">
-        <v>454.467</v>
-      </c>
-      <c r="C38" s="57">
-        <v>423.588</v>
-      </c>
-      <c r="D38" s="58">
-        <v>985.989</v>
-      </c>
-      <c r="E38" s="58">
-        <v>409.025</v>
-      </c>
-      <c r="F38" s="59">
-        <v>716.035</v>
-      </c>
-      <c r="G38" s="59">
-        <v>249.567</v>
-      </c>
-      <c r="H38" s="60">
-        <v>0.176</v>
-      </c>
-      <c r="I38" s="60">
-        <v>0.082</v>
-      </c>
-      <c r="J38" s="61">
+      <c r="B38" s="47">
+        <v>454.46699999999998</v>
+      </c>
+      <c r="C38" s="47">
+        <v>423.58800000000002</v>
+      </c>
+      <c r="D38" s="48">
+        <v>985.98900000000003</v>
+      </c>
+      <c r="E38" s="48">
+        <v>409.02499999999998</v>
+      </c>
+      <c r="F38" s="49">
+        <v>716.03499999999997</v>
+      </c>
+      <c r="G38" s="49">
+        <v>249.56700000000001</v>
+      </c>
+      <c r="H38" s="50">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="I38" s="50">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="J38" s="51">
         <v>0.26</v>
       </c>
-      <c r="K38" s="61">
-        <v>0.032</v>
-      </c>
-      <c r="L38" s="62">
-        <v>0.306</v>
-      </c>
-      <c r="M38" s="62">
+      <c r="K38" s="51">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="L38" s="52">
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="M38" s="52">
         <v>0.03</v>
       </c>
-      <c r="N38" s="63">
-        <v>0.456</v>
-      </c>
-      <c r="O38" s="63">
-        <v>0.178</v>
-      </c>
-      <c r="P38" s="64">
+      <c r="N38" s="53">
+        <v>0.45600000000000002</v>
+      </c>
+      <c r="O38" s="53">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="P38" s="54">
         <v>0.24</v>
       </c>
-      <c r="Q38" s="45">
+      <c r="Q38" s="35">
         <v>0.1</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="57">
-        <v>212.859</v>
-      </c>
-      <c r="C39" s="57">
-        <v>204.568</v>
-      </c>
-      <c r="D39" s="58">
-        <v>355.172</v>
-      </c>
-      <c r="E39" s="58">
-        <v>322.324</v>
-      </c>
-      <c r="F39" s="59">
+      <c r="B39" s="47">
+        <v>212.85900000000001</v>
+      </c>
+      <c r="C39" s="47">
+        <v>204.56800000000001</v>
+      </c>
+      <c r="D39" s="48">
+        <v>355.17200000000003</v>
+      </c>
+      <c r="E39" s="48">
+        <v>322.32400000000001</v>
+      </c>
+      <c r="F39" s="49">
         <v>420.529</v>
       </c>
-      <c r="G39" s="59">
-        <v>279.074</v>
-      </c>
-      <c r="H39" s="60">
-        <v>0.088</v>
-      </c>
-      <c r="I39" s="60">
-        <v>0.083</v>
-      </c>
-      <c r="J39" s="61">
-        <v>0.175</v>
-      </c>
-      <c r="K39" s="61">
-        <v>0.031</v>
-      </c>
-      <c r="L39" s="62">
-        <v>0.162</v>
-      </c>
-      <c r="M39" s="62">
-        <v>0.032</v>
-      </c>
-      <c r="N39" s="63">
-        <v>0.256</v>
-      </c>
-      <c r="O39" s="63">
-        <v>0.171</v>
-      </c>
-      <c r="P39" s="64">
+      <c r="G39" s="49">
+        <v>279.07400000000001</v>
+      </c>
+      <c r="H39" s="50">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="I39" s="50">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="J39" s="51">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="K39" s="51">
+        <v>3.1E-2</v>
+      </c>
+      <c r="L39" s="52">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="M39" s="52">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="N39" s="53">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="O39" s="53">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="P39" s="54">
         <v>0.15</v>
       </c>
-      <c r="Q39" s="45">
+      <c r="Q39" s="35">
         <v>0.1</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="57">
-        <v>288.719</v>
-      </c>
-      <c r="C40" s="57">
-        <v>266.578</v>
-      </c>
-      <c r="D40" s="58">
-        <v>727.388</v>
-      </c>
-      <c r="E40" s="58">
-        <v>303.662</v>
-      </c>
-      <c r="F40" s="59">
+      <c r="B40" s="47">
+        <v>288.71899999999999</v>
+      </c>
+      <c r="C40" s="47">
+        <v>266.57799999999997</v>
+      </c>
+      <c r="D40" s="48">
+        <v>727.38800000000003</v>
+      </c>
+      <c r="E40" s="48">
+        <v>303.66199999999998</v>
+      </c>
+      <c r="F40" s="49">
         <v>560.25</v>
       </c>
-      <c r="G40" s="59">
-        <v>242.676</v>
-      </c>
-      <c r="H40" s="60">
-        <v>0.118</v>
-      </c>
-      <c r="I40" s="60">
-        <v>0.081</v>
-      </c>
-      <c r="J40" s="61">
+      <c r="G40" s="49">
+        <v>242.67599999999999</v>
+      </c>
+      <c r="H40" s="50">
+        <v>0.11799999999999999</v>
+      </c>
+      <c r="I40" s="50">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="J40" s="51">
         <v>0.189</v>
       </c>
-      <c r="K40" s="61">
-        <v>0.036</v>
-      </c>
-      <c r="L40" s="62">
+      <c r="K40" s="51">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="L40" s="52">
         <v>0.188</v>
       </c>
-      <c r="M40" s="62">
-        <v>0.032</v>
-      </c>
-      <c r="N40" s="63">
-        <v>0.298</v>
-      </c>
-      <c r="O40" s="63">
-        <v>0.169</v>
-      </c>
-      <c r="P40" s="64">
-        <v>0.163</v>
-      </c>
-      <c r="Q40" s="45">
+      <c r="M40" s="52">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="N40" s="53">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="O40" s="53">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="P40" s="54">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="Q40" s="35">
         <v>0.1</v>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="57">
-        <f t="shared" ref="B41:Q41" si="8">AVERAGE(B38:B40)</f>
-        <v>318.6816667</v>
-      </c>
-      <c r="C41" s="57">
-        <f t="shared" si="8"/>
-        <v>298.2446667</v>
-      </c>
-      <c r="D41" s="58">
-        <f t="shared" si="8"/>
-        <v>689.5163333</v>
-      </c>
-      <c r="E41" s="58">
-        <f t="shared" si="8"/>
-        <v>345.0036667</v>
-      </c>
-      <c r="F41" s="59">
-        <f t="shared" si="8"/>
-        <v>565.6046667</v>
-      </c>
-      <c r="G41" s="59">
-        <f t="shared" si="8"/>
-        <v>257.1056667</v>
-      </c>
-      <c r="H41" s="60">
-        <f t="shared" si="8"/>
-        <v>0.1273333333</v>
-      </c>
-      <c r="I41" s="60">
-        <f t="shared" si="8"/>
-        <v>0.082</v>
-      </c>
-      <c r="J41" s="61">
-        <f t="shared" si="8"/>
-        <v>0.208</v>
-      </c>
-      <c r="K41" s="61">
-        <f t="shared" si="8"/>
-        <v>0.033</v>
-      </c>
-      <c r="L41" s="62">
-        <f t="shared" si="8"/>
-        <v>0.2186666667</v>
-      </c>
-      <c r="M41" s="62">
-        <f t="shared" si="8"/>
-        <v>0.03133333333</v>
-      </c>
-      <c r="N41" s="63">
-        <f t="shared" si="8"/>
-        <v>0.3366666667</v>
-      </c>
-      <c r="O41" s="63">
-        <f t="shared" si="8"/>
-        <v>0.1726666667</v>
-      </c>
-      <c r="P41" s="64">
-        <f t="shared" si="8"/>
-        <v>0.1843333333</v>
-      </c>
-      <c r="Q41" s="45">
-        <f t="shared" si="8"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="12">
-        <v>1.0E7</v>
-      </c>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
-      <c r="E42" s="65"/>
-      <c r="F42" s="65"/>
-      <c r="H42" s="25" t="s">
+      <c r="B41" s="47">
+        <f t="shared" ref="B41:Q41" si="7">AVERAGE(B38:B40)</f>
+        <v>318.68166666666667</v>
+      </c>
+      <c r="C41" s="47">
+        <f t="shared" si="7"/>
+        <v>298.24466666666666</v>
+      </c>
+      <c r="D41" s="48">
+        <f t="shared" si="7"/>
+        <v>689.51633333333336</v>
+      </c>
+      <c r="E41" s="48">
+        <f t="shared" si="7"/>
+        <v>345.00366666666667</v>
+      </c>
+      <c r="F41" s="49">
+        <f t="shared" si="7"/>
+        <v>565.60466666666662</v>
+      </c>
+      <c r="G41" s="49">
+        <f t="shared" si="7"/>
+        <v>257.10566666666665</v>
+      </c>
+      <c r="H41" s="50">
+        <f t="shared" si="7"/>
+        <v>0.12733333333333333</v>
+      </c>
+      <c r="I41" s="50">
+        <f t="shared" si="7"/>
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="J41" s="51">
+        <f t="shared" si="7"/>
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="K41" s="51">
+        <f t="shared" si="7"/>
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="L41" s="52">
+        <f t="shared" si="7"/>
+        <v>0.21866666666666665</v>
+      </c>
+      <c r="M41" s="52">
+        <f t="shared" si="7"/>
+        <v>3.1333333333333331E-2</v>
+      </c>
+      <c r="N41" s="53">
+        <f t="shared" si="7"/>
+        <v>0.33666666666666667</v>
+      </c>
+      <c r="O41" s="53">
+        <f t="shared" si="7"/>
+        <v>0.17266666666666666</v>
+      </c>
+      <c r="P41" s="54">
+        <f t="shared" si="7"/>
+        <v>0.18433333333333335</v>
+      </c>
+      <c r="Q41" s="35">
+        <f t="shared" si="7"/>
+        <v>0.10000000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A42" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="B42" s="55"/>
+      <c r="C42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="H42" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I42" s="25" t="s">
+      <c r="I42" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J42" s="26" t="s">
+      <c r="J42" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="K42" s="26" t="s">
+      <c r="K42" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="L42" s="27" t="s">
+      <c r="L42" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="M42" s="27" t="s">
+      <c r="M42" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="N42" s="28" t="s">
+      <c r="N42" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="O42" s="28" t="s">
+      <c r="O42" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="P42" s="29" t="s">
+      <c r="P42" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="Q42" s="29" t="s">
+      <c r="Q42" s="19" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H43" s="25">
+      <c r="H43" s="15">
         <v>1.02</v>
       </c>
-      <c r="I43" s="25">
-        <v>3.018</v>
-      </c>
-      <c r="J43" s="26">
-        <v>1.132</v>
-      </c>
-      <c r="K43" s="26">
-        <v>0.553</v>
-      </c>
-      <c r="L43" s="27">
+      <c r="I43" s="15">
+        <v>3.0179999999999998</v>
+      </c>
+      <c r="J43" s="16">
+        <v>1.1319999999999999</v>
+      </c>
+      <c r="K43" s="16">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="L43" s="17">
         <v>1.784</v>
       </c>
-      <c r="M43" s="27">
-        <v>1.027</v>
-      </c>
-      <c r="N43" s="28">
-        <v>4.828</v>
-      </c>
-      <c r="O43" s="28">
-        <v>3.291</v>
-      </c>
-      <c r="P43" s="29">
-        <v>2.155</v>
-      </c>
-      <c r="Q43" s="29">
-        <v>1.965</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
+      <c r="M43" s="17">
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="N43" s="18">
+        <v>4.8280000000000003</v>
+      </c>
+      <c r="O43" s="18">
+        <v>3.2909999999999999</v>
+      </c>
+      <c r="P43" s="19">
+        <v>2.1549999999999998</v>
+      </c>
+      <c r="Q43" s="19">
+        <v>1.9650000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="25">
+      <c r="H44" s="15">
         <v>1.403</v>
       </c>
-      <c r="I44" s="25">
-        <v>3.132</v>
-      </c>
-      <c r="J44" s="26">
+      <c r="I44" s="15">
+        <v>3.1320000000000001</v>
+      </c>
+      <c r="J44" s="16">
         <v>2.41</v>
       </c>
-      <c r="K44" s="26">
-        <v>0.585</v>
-      </c>
-      <c r="L44" s="27">
-        <v>2.022</v>
-      </c>
-      <c r="M44" s="27">
-        <v>0.386</v>
-      </c>
-      <c r="N44" s="28">
-        <v>4.691</v>
-      </c>
-      <c r="O44" s="28">
-        <v>2.401</v>
-      </c>
-      <c r="P44" s="29">
-        <v>2.273</v>
-      </c>
-      <c r="Q44" s="29">
-        <v>1.146</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
+      <c r="K44" s="16">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="L44" s="17">
+        <v>2.0219999999999998</v>
+      </c>
+      <c r="M44" s="17">
+        <v>0.38600000000000001</v>
+      </c>
+      <c r="N44" s="18">
+        <v>4.6909999999999998</v>
+      </c>
+      <c r="O44" s="18">
+        <v>2.4009999999999998</v>
+      </c>
+      <c r="P44" s="19">
+        <v>2.2730000000000001</v>
+      </c>
+      <c r="Q44" s="19">
+        <v>1.1459999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H45" s="25">
-        <v>1.007</v>
-      </c>
-      <c r="I45" s="25">
-        <v>2.792</v>
-      </c>
-      <c r="J45" s="26">
-        <v>2.313</v>
-      </c>
-      <c r="K45" s="26">
-        <v>0.55</v>
-      </c>
-      <c r="L45" s="27">
-        <v>0.822</v>
-      </c>
-      <c r="M45" s="27">
-        <v>0.721</v>
-      </c>
-      <c r="N45" s="28">
+      <c r="H45" s="15">
+        <v>1.0069999999999999</v>
+      </c>
+      <c r="I45" s="15">
+        <v>2.7919999999999998</v>
+      </c>
+      <c r="J45" s="16">
+        <v>2.3130000000000002</v>
+      </c>
+      <c r="K45" s="16">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L45" s="17">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="M45" s="17">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="N45" s="18">
         <v>3.988</v>
       </c>
-      <c r="O45" s="28">
-        <v>3.916</v>
-      </c>
-      <c r="P45" s="29">
-        <v>2.204</v>
-      </c>
-      <c r="Q45" s="29">
+      <c r="O45" s="18">
+        <v>3.9159999999999999</v>
+      </c>
+      <c r="P45" s="19">
+        <v>2.2040000000000002</v>
+      </c>
+      <c r="Q45" s="19">
         <v>1.766</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H46" s="66">
-        <f t="shared" ref="H46:Q46" si="9">AVERAGE(H43:H45)</f>
-        <v>1.143333333</v>
-      </c>
-      <c r="I46" s="25">
-        <f t="shared" si="9"/>
-        <v>2.980666667</v>
-      </c>
-      <c r="J46" s="26">
-        <f t="shared" si="9"/>
-        <v>1.951666667</v>
-      </c>
-      <c r="K46" s="26">
-        <f t="shared" si="9"/>
-        <v>0.5626666667</v>
-      </c>
-      <c r="L46" s="27">
-        <f t="shared" si="9"/>
-        <v>1.542666667</v>
-      </c>
-      <c r="M46" s="27">
-        <f t="shared" si="9"/>
-        <v>0.7113333333</v>
-      </c>
-      <c r="N46" s="28">
-        <f t="shared" si="9"/>
-        <v>4.502333333</v>
-      </c>
-      <c r="O46" s="28">
-        <f t="shared" si="9"/>
-        <v>3.202666667</v>
-      </c>
-      <c r="P46" s="29">
-        <f t="shared" si="9"/>
-        <v>2.210666667</v>
-      </c>
-      <c r="Q46" s="29">
-        <f t="shared" si="9"/>
-        <v>1.625666667</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="12">
-        <v>1.0E8</v>
-      </c>
-      <c r="B47" s="65"/>
-      <c r="C47" s="65"/>
-      <c r="E47" s="65"/>
-      <c r="F47" s="65"/>
-      <c r="H47" s="41" t="s">
+      <c r="H46" s="56">
+        <f t="shared" ref="H46:Q46" si="8">AVERAGE(H43:H45)</f>
+        <v>1.1433333333333333</v>
+      </c>
+      <c r="I46" s="15">
+        <f t="shared" si="8"/>
+        <v>2.9806666666666666</v>
+      </c>
+      <c r="J46" s="16">
+        <f t="shared" si="8"/>
+        <v>1.9516666666666669</v>
+      </c>
+      <c r="K46" s="16">
+        <f t="shared" si="8"/>
+        <v>0.56266666666666665</v>
+      </c>
+      <c r="L46" s="17">
+        <f t="shared" si="8"/>
+        <v>1.5426666666666666</v>
+      </c>
+      <c r="M46" s="17">
+        <f t="shared" si="8"/>
+        <v>0.71133333333333326</v>
+      </c>
+      <c r="N46" s="18">
+        <f t="shared" si="8"/>
+        <v>4.5023333333333335</v>
+      </c>
+      <c r="O46" s="18">
+        <f t="shared" si="8"/>
+        <v>3.202666666666667</v>
+      </c>
+      <c r="P46" s="19">
+        <f t="shared" si="8"/>
+        <v>2.2106666666666666</v>
+      </c>
+      <c r="Q46" s="19">
+        <f t="shared" si="8"/>
+        <v>1.6256666666666666</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A47" s="2">
+        <v>100000000</v>
+      </c>
+      <c r="B47" s="55"/>
+      <c r="C47" s="55"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="H47" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="I47" s="41" t="s">
+      <c r="I47" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="J47" s="42" t="s">
+      <c r="J47" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="K47" s="42" t="s">
+      <c r="K47" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="L47" s="43" t="s">
+      <c r="L47" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="M47" s="43" t="s">
+      <c r="M47" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="N47" s="44" t="s">
+      <c r="N47" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="O47" s="44" t="s">
+      <c r="O47" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="P47" s="45" t="s">
+      <c r="P47" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="Q47" s="45" t="s">
+      <c r="Q47" s="35" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H48" s="41">
-        <v>16.479</v>
-      </c>
-      <c r="I48" s="67">
-        <v>176.722</v>
-      </c>
-      <c r="J48" s="42">
+      <c r="H48" s="31">
+        <v>16.478999999999999</v>
+      </c>
+      <c r="I48" s="31">
+        <v>176.72200000000001</v>
+      </c>
+      <c r="J48" s="32">
         <v>29.727</v>
       </c>
-      <c r="K48" s="42">
+      <c r="K48" s="32">
         <v>3.03</v>
       </c>
-      <c r="L48" s="43">
+      <c r="L48" s="33">
         <v>19.084</v>
       </c>
-      <c r="M48" s="43">
-        <v>3.251</v>
-      </c>
-      <c r="N48" s="44">
-        <v>74.926</v>
-      </c>
-      <c r="O48" s="68">
-        <v>62.819</v>
-      </c>
-      <c r="P48" s="45">
+      <c r="M48" s="33">
+        <v>3.2509999999999999</v>
+      </c>
+      <c r="N48" s="34">
+        <v>74.926000000000002</v>
+      </c>
+      <c r="O48" s="34">
+        <v>62.819000000000003</v>
+      </c>
+      <c r="P48" s="35">
         <v>20.898</v>
       </c>
-      <c r="Q48" s="45">
-        <v>20.178</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
+      <c r="Q48" s="35">
+        <v>20.178000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H49" s="41">
+      <c r="H49" s="31">
         <v>16.439</v>
       </c>
-      <c r="I49" s="41">
-        <v>178.551</v>
-      </c>
-      <c r="J49" s="42">
+      <c r="I49" s="31">
+        <v>178.55099999999999</v>
+      </c>
+      <c r="J49" s="32">
         <v>29.44</v>
       </c>
-      <c r="K49" s="42">
-        <v>4.275</v>
-      </c>
-      <c r="L49" s="43">
-        <v>18.824</v>
-      </c>
-      <c r="M49" s="43">
-        <v>6.989</v>
-      </c>
-      <c r="N49" s="44">
-        <v>68.433</v>
-      </c>
-      <c r="O49" s="44">
-        <v>38.602</v>
-      </c>
-      <c r="P49" s="45">
+      <c r="K49" s="32">
+        <v>4.2750000000000004</v>
+      </c>
+      <c r="L49" s="33">
+        <v>18.824000000000002</v>
+      </c>
+      <c r="M49" s="33">
+        <v>6.9889999999999999</v>
+      </c>
+      <c r="N49" s="34">
+        <v>68.433000000000007</v>
+      </c>
+      <c r="O49" s="34">
+        <v>38.601999999999997</v>
+      </c>
+      <c r="P49" s="35">
         <v>15.465</v>
       </c>
-      <c r="Q49" s="45">
-        <v>11.658</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
+      <c r="Q49" s="35">
+        <v>11.657999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H50" s="41">
-        <v>16.142</v>
-      </c>
-      <c r="I50" s="41">
+      <c r="H50" s="31">
+        <v>16.141999999999999</v>
+      </c>
+      <c r="I50" s="31">
         <v>199.815</v>
       </c>
-      <c r="J50" s="42">
-        <v>30.265</v>
-      </c>
-      <c r="K50" s="42">
-        <v>5.945</v>
-      </c>
-      <c r="L50" s="43">
+      <c r="J50" s="32">
+        <v>30.265000000000001</v>
+      </c>
+      <c r="K50" s="32">
+        <v>5.9450000000000003</v>
+      </c>
+      <c r="L50" s="33">
         <v>19.907</v>
       </c>
-      <c r="M50" s="43">
-        <v>7.406</v>
-      </c>
-      <c r="N50" s="44">
-        <v>58.996</v>
-      </c>
-      <c r="O50" s="44">
-        <v>55.581</v>
-      </c>
-      <c r="P50" s="45">
-        <v>24.764</v>
-      </c>
-      <c r="Q50" s="45">
-        <v>20.425</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
+      <c r="M50" s="33">
+        <v>7.4059999999999997</v>
+      </c>
+      <c r="N50" s="34">
+        <v>58.996000000000002</v>
+      </c>
+      <c r="O50" s="34">
+        <v>55.581000000000003</v>
+      </c>
+      <c r="P50" s="35">
+        <v>24.763999999999999</v>
+      </c>
+      <c r="Q50" s="35">
+        <v>20.425000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H51" s="41">
-        <f t="shared" ref="H51:Q51" si="10">AVERAGE(H48:H50)</f>
-        <v>16.35333333</v>
-      </c>
-      <c r="I51" s="69">
-        <f t="shared" si="10"/>
-        <v>185.0293333</v>
-      </c>
-      <c r="J51" s="42">
-        <f t="shared" si="10"/>
-        <v>29.81066667</v>
-      </c>
-      <c r="K51" s="42">
-        <f t="shared" si="10"/>
-        <v>4.416666667</v>
-      </c>
-      <c r="L51" s="43">
-        <f t="shared" si="10"/>
-        <v>19.27166667</v>
-      </c>
-      <c r="M51" s="70">
-        <f t="shared" si="10"/>
-        <v>5.882</v>
-      </c>
-      <c r="N51" s="44">
-        <f t="shared" si="10"/>
-        <v>67.45166667</v>
-      </c>
-      <c r="O51" s="63">
-        <f t="shared" si="10"/>
-        <v>52.334</v>
-      </c>
-      <c r="P51" s="45">
-        <f t="shared" si="10"/>
-        <v>20.37566667</v>
-      </c>
-      <c r="Q51" s="45">
-        <f t="shared" si="10"/>
-        <v>17.42033333</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="B52" s="71"/>
-      <c r="C52" s="71"/>
-      <c r="D52" s="71"/>
-      <c r="E52" s="71"/>
-      <c r="F52" s="71"/>
-      <c r="G52" s="71"/>
-      <c r="H52" s="71"/>
-      <c r="I52" s="71"/>
-      <c r="J52" s="71"/>
-      <c r="K52" s="71"/>
-      <c r="L52" s="71"/>
-      <c r="M52" s="71"/>
-      <c r="N52" s="71"/>
-      <c r="O52" s="71"/>
-      <c r="P52" s="71"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="B53" s="71"/>
-      <c r="C53" s="71"/>
-      <c r="D53" s="71"/>
-      <c r="E53" s="71"/>
-      <c r="F53" s="71"/>
-      <c r="G53" s="71"/>
-      <c r="H53" s="71"/>
-      <c r="I53" s="71"/>
-      <c r="J53" s="71"/>
-      <c r="K53" s="71"/>
-      <c r="L53" s="71"/>
-      <c r="M53" s="71"/>
-      <c r="N53" s="71"/>
-      <c r="O53" s="71"/>
-      <c r="P53" s="71"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="B54" s="71"/>
-      <c r="C54" s="71"/>
-      <c r="D54" s="71"/>
-      <c r="E54" s="71"/>
-      <c r="F54" s="71"/>
-      <c r="G54" s="71"/>
-      <c r="H54" s="71"/>
-      <c r="I54" s="71"/>
-      <c r="J54" s="71"/>
-      <c r="K54" s="71"/>
-      <c r="L54" s="71"/>
-      <c r="M54" s="71"/>
-      <c r="N54" s="71"/>
-      <c r="O54" s="71"/>
-      <c r="P54" s="71"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="B55" s="71"/>
-      <c r="C55" s="71"/>
-      <c r="D55" s="71"/>
-      <c r="E55" s="71"/>
-      <c r="F55" s="71"/>
-      <c r="G55" s="71"/>
-      <c r="H55" s="71"/>
-      <c r="I55" s="71"/>
-      <c r="J55" s="71"/>
-      <c r="K55" s="71"/>
-      <c r="L55" s="71"/>
-      <c r="M55" s="71"/>
-      <c r="N55" s="71"/>
-      <c r="O55" s="71"/>
-      <c r="P55" s="71"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="B56" s="71"/>
-      <c r="C56" s="71"/>
-      <c r="D56" s="71"/>
-      <c r="E56" s="71"/>
-      <c r="F56" s="71"/>
-      <c r="G56" s="71"/>
-      <c r="H56" s="71"/>
-      <c r="I56" s="71"/>
-      <c r="J56" s="71"/>
-      <c r="K56" s="71"/>
-      <c r="L56" s="71"/>
-      <c r="M56" s="71"/>
-      <c r="N56" s="71"/>
-      <c r="O56" s="71"/>
-      <c r="P56" s="71"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="B57" s="71"/>
-      <c r="C57" s="71"/>
-      <c r="D57" s="71"/>
-      <c r="E57" s="71"/>
-      <c r="F57" s="71"/>
-      <c r="G57" s="71"/>
-      <c r="H57" s="71"/>
-      <c r="I57" s="71"/>
-      <c r="J57" s="71"/>
-      <c r="K57" s="71"/>
-      <c r="L57" s="71"/>
-      <c r="M57" s="71"/>
-      <c r="N57" s="71"/>
-      <c r="O57" s="71"/>
-      <c r="P57" s="71"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="B58" s="71"/>
-      <c r="C58" s="71"/>
-      <c r="D58" s="71"/>
-      <c r="E58" s="71"/>
-      <c r="F58" s="71"/>
-      <c r="G58" s="71"/>
-      <c r="H58" s="71"/>
-      <c r="I58" s="71"/>
-      <c r="J58" s="71"/>
-      <c r="K58" s="71"/>
-      <c r="L58" s="71"/>
-      <c r="M58" s="71"/>
-      <c r="N58" s="71"/>
-      <c r="O58" s="71"/>
-      <c r="P58" s="71"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="B59" s="71"/>
-      <c r="C59" s="71"/>
-      <c r="D59" s="71"/>
-      <c r="E59" s="71"/>
-      <c r="F59" s="71"/>
-      <c r="G59" s="71"/>
-      <c r="H59" s="71"/>
-      <c r="I59" s="71"/>
-      <c r="J59" s="71"/>
-      <c r="K59" s="71"/>
-      <c r="L59" s="71"/>
-      <c r="M59" s="71"/>
-      <c r="N59" s="71"/>
-      <c r="O59" s="71"/>
-      <c r="P59" s="71"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="B60" s="71"/>
-      <c r="C60" s="71"/>
-      <c r="D60" s="71"/>
-      <c r="E60" s="71"/>
-      <c r="F60" s="71"/>
-      <c r="G60" s="71"/>
-      <c r="H60" s="71"/>
-      <c r="I60" s="71"/>
-      <c r="J60" s="71"/>
-      <c r="K60" s="71"/>
-      <c r="L60" s="71"/>
-      <c r="M60" s="71"/>
-      <c r="N60" s="71"/>
-      <c r="O60" s="71"/>
-      <c r="P60" s="71"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
-      <c r="D61" s="71"/>
-      <c r="E61" s="71"/>
-      <c r="F61" s="71"/>
-      <c r="G61" s="71"/>
-      <c r="H61" s="71"/>
-      <c r="I61" s="71"/>
-      <c r="J61" s="71"/>
-      <c r="K61" s="71"/>
-      <c r="L61" s="71"/>
-      <c r="M61" s="71"/>
-      <c r="N61" s="71"/>
-      <c r="O61" s="71"/>
-      <c r="P61" s="71"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="71"/>
-      <c r="C62" s="71"/>
-      <c r="D62" s="71"/>
-      <c r="E62" s="71"/>
-      <c r="F62" s="71"/>
-      <c r="G62" s="71"/>
-      <c r="H62" s="71"/>
-      <c r="I62" s="71"/>
-      <c r="J62" s="71"/>
-      <c r="K62" s="71"/>
-      <c r="L62" s="71"/>
-      <c r="M62" s="71"/>
-      <c r="N62" s="71"/>
-      <c r="O62" s="71"/>
-      <c r="P62" s="71"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="B63" s="71"/>
-      <c r="C63" s="71"/>
-      <c r="D63" s="71"/>
-      <c r="E63" s="71"/>
-      <c r="F63" s="71"/>
-      <c r="G63" s="71"/>
-      <c r="H63" s="71"/>
-      <c r="I63" s="71"/>
-      <c r="J63" s="71"/>
-      <c r="K63" s="71"/>
-      <c r="L63" s="71"/>
-      <c r="M63" s="71"/>
-      <c r="N63" s="71"/>
-      <c r="O63" s="71"/>
-      <c r="P63" s="71"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="B64" s="71"/>
-      <c r="C64" s="71"/>
-      <c r="D64" s="71"/>
-      <c r="E64" s="71"/>
-      <c r="F64" s="71"/>
-      <c r="G64" s="71"/>
-      <c r="H64" s="71"/>
-      <c r="I64" s="71"/>
-      <c r="J64" s="71"/>
-      <c r="K64" s="71"/>
-      <c r="L64" s="71"/>
-      <c r="M64" s="71"/>
-      <c r="N64" s="71"/>
-      <c r="O64" s="71"/>
-      <c r="P64" s="71"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="B65" s="71"/>
-      <c r="C65" s="71"/>
-      <c r="D65" s="71"/>
-      <c r="E65" s="71"/>
-      <c r="F65" s="71"/>
-      <c r="G65" s="71"/>
-      <c r="H65" s="71"/>
-      <c r="I65" s="71"/>
-      <c r="J65" s="71"/>
-      <c r="K65" s="71"/>
-      <c r="L65" s="71"/>
-      <c r="M65" s="71"/>
-      <c r="N65" s="71"/>
-      <c r="O65" s="71"/>
-      <c r="P65" s="71"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="B66" s="71"/>
-      <c r="C66" s="71"/>
-      <c r="D66" s="71"/>
-      <c r="E66" s="71"/>
-      <c r="F66" s="71"/>
-      <c r="G66" s="71"/>
-      <c r="H66" s="71"/>
-      <c r="I66" s="71"/>
-      <c r="J66" s="71"/>
-      <c r="K66" s="71"/>
-      <c r="L66" s="71"/>
-      <c r="M66" s="71"/>
-      <c r="N66" s="71"/>
-      <c r="O66" s="71"/>
-      <c r="P66" s="71"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="B67" s="71"/>
-      <c r="C67" s="71"/>
-      <c r="D67" s="71"/>
-      <c r="E67" s="71"/>
-      <c r="F67" s="71"/>
-      <c r="G67" s="71"/>
-      <c r="H67" s="71"/>
-      <c r="I67" s="71"/>
-      <c r="J67" s="71"/>
-      <c r="K67" s="71"/>
-      <c r="L67" s="71"/>
-      <c r="M67" s="71"/>
-      <c r="N67" s="71"/>
-      <c r="O67" s="71"/>
-      <c r="P67" s="71"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="B68" s="71"/>
-      <c r="C68" s="71"/>
-      <c r="D68" s="71"/>
-      <c r="E68" s="71"/>
-      <c r="F68" s="71"/>
-      <c r="G68" s="71"/>
-      <c r="H68" s="71"/>
-      <c r="I68" s="71"/>
-      <c r="J68" s="71"/>
-      <c r="K68" s="71"/>
-      <c r="L68" s="71"/>
-      <c r="M68" s="71"/>
-      <c r="N68" s="71"/>
-      <c r="O68" s="71"/>
-      <c r="P68" s="71"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="B74" s="71"/>
-      <c r="C74" s="71"/>
-      <c r="D74" s="71"/>
-      <c r="E74" s="71"/>
-      <c r="F74" s="71"/>
-      <c r="G74" s="71"/>
-      <c r="H74" s="71"/>
-      <c r="I74" s="71"/>
-      <c r="J74" s="71"/>
-      <c r="K74" s="71"/>
-      <c r="L74" s="71"/>
-      <c r="M74" s="71"/>
-      <c r="N74" s="71"/>
-      <c r="O74" s="71"/>
-      <c r="P74" s="71"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="B75" s="71"/>
-      <c r="C75" s="71"/>
-      <c r="D75" s="71"/>
-      <c r="E75" s="71"/>
-      <c r="F75" s="71"/>
-      <c r="G75" s="71"/>
-      <c r="H75" s="71"/>
-      <c r="I75" s="71"/>
-      <c r="J75" s="71"/>
-      <c r="K75" s="71"/>
-      <c r="L75" s="71"/>
-      <c r="M75" s="71"/>
-      <c r="N75" s="71"/>
-      <c r="O75" s="71"/>
-      <c r="P75" s="71"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="B76" s="71"/>
-      <c r="C76" s="71"/>
-      <c r="D76" s="71"/>
-      <c r="E76" s="71"/>
-      <c r="F76" s="71"/>
-      <c r="G76" s="71"/>
-      <c r="H76" s="71"/>
-      <c r="I76" s="71"/>
-      <c r="J76" s="71"/>
-      <c r="K76" s="71"/>
-      <c r="L76" s="71"/>
-      <c r="M76" s="71"/>
-      <c r="N76" s="71"/>
-      <c r="O76" s="71"/>
-      <c r="P76" s="71"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="B77" s="71"/>
-      <c r="C77" s="71"/>
-      <c r="D77" s="71"/>
-      <c r="E77" s="71"/>
-      <c r="F77" s="71"/>
-      <c r="G77" s="71"/>
-      <c r="H77" s="71"/>
-      <c r="I77" s="71"/>
-      <c r="J77" s="71"/>
-      <c r="K77" s="71"/>
-      <c r="L77" s="71"/>
-      <c r="M77" s="71"/>
-      <c r="N77" s="71"/>
-      <c r="O77" s="71"/>
-      <c r="P77" s="71"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="B78" s="71"/>
-      <c r="C78" s="71"/>
-      <c r="D78" s="71"/>
-      <c r="E78" s="71"/>
-      <c r="F78" s="71"/>
-      <c r="G78" s="71"/>
-      <c r="H78" s="71"/>
-      <c r="I78" s="71"/>
-      <c r="J78" s="71"/>
-      <c r="K78" s="71"/>
-      <c r="L78" s="71"/>
-      <c r="M78" s="71"/>
-      <c r="N78" s="71"/>
-      <c r="O78" s="71"/>
-      <c r="P78" s="71"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="B79" s="71"/>
-      <c r="C79" s="71"/>
-      <c r="D79" s="71"/>
-      <c r="E79" s="71"/>
-      <c r="F79" s="71"/>
-      <c r="G79" s="71"/>
-      <c r="H79" s="71"/>
-      <c r="I79" s="71"/>
-      <c r="J79" s="71"/>
-      <c r="K79" s="71"/>
-      <c r="L79" s="71"/>
-      <c r="M79" s="71"/>
-      <c r="N79" s="71"/>
-      <c r="O79" s="71"/>
-      <c r="P79" s="71"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="B80" s="71"/>
-      <c r="C80" s="71"/>
-      <c r="D80" s="71"/>
-      <c r="E80" s="71"/>
-      <c r="F80" s="71"/>
-      <c r="G80" s="71"/>
-      <c r="H80" s="71"/>
-      <c r="I80" s="71"/>
-      <c r="J80" s="71"/>
-      <c r="K80" s="71"/>
-      <c r="L80" s="71"/>
-      <c r="M80" s="71"/>
-      <c r="N80" s="71"/>
-      <c r="O80" s="71"/>
-      <c r="P80" s="71"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="B81" s="71"/>
-      <c r="C81" s="71"/>
-      <c r="D81" s="71"/>
-      <c r="E81" s="71"/>
-      <c r="F81" s="71"/>
-      <c r="G81" s="71"/>
-      <c r="H81" s="71"/>
-      <c r="I81" s="71"/>
-      <c r="J81" s="71"/>
-      <c r="K81" s="71"/>
-      <c r="L81" s="71"/>
-      <c r="M81" s="71"/>
-      <c r="N81" s="71"/>
-      <c r="O81" s="71"/>
-      <c r="P81" s="71"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="B82" s="71"/>
-      <c r="C82" s="71"/>
-      <c r="D82" s="71"/>
-      <c r="E82" s="71"/>
-      <c r="F82" s="71"/>
-      <c r="G82" s="71"/>
-      <c r="H82" s="71"/>
-      <c r="I82" s="71"/>
-      <c r="J82" s="71"/>
-      <c r="K82" s="71"/>
-      <c r="L82" s="71"/>
-      <c r="M82" s="71"/>
-      <c r="N82" s="71"/>
-      <c r="O82" s="71"/>
-      <c r="P82" s="71"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="B83" s="71"/>
-      <c r="C83" s="71"/>
-      <c r="D83" s="71"/>
-      <c r="E83" s="71"/>
-      <c r="F83" s="71"/>
-      <c r="G83" s="71"/>
-      <c r="H83" s="71"/>
-      <c r="I83" s="71"/>
-      <c r="J83" s="71"/>
-      <c r="K83" s="71"/>
-      <c r="L83" s="71"/>
-      <c r="M83" s="71"/>
-      <c r="N83" s="71"/>
-      <c r="O83" s="71"/>
-      <c r="P83" s="71"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="B84" s="71"/>
-      <c r="C84" s="71"/>
-      <c r="D84" s="71"/>
-      <c r="E84" s="71"/>
-      <c r="F84" s="71"/>
-      <c r="G84" s="71"/>
-      <c r="H84" s="71"/>
-      <c r="I84" s="71"/>
-      <c r="J84" s="71"/>
-      <c r="K84" s="71"/>
-      <c r="L84" s="71"/>
-      <c r="M84" s="71"/>
-      <c r="N84" s="71"/>
-      <c r="O84" s="71"/>
-      <c r="P84" s="71"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="B85" s="71"/>
-      <c r="C85" s="71"/>
-      <c r="D85" s="71"/>
-      <c r="E85" s="71"/>
-      <c r="F85" s="71"/>
-      <c r="G85" s="71"/>
-      <c r="H85" s="71"/>
-      <c r="I85" s="71"/>
-      <c r="J85" s="71"/>
-      <c r="K85" s="71"/>
-      <c r="L85" s="71"/>
-      <c r="M85" s="71"/>
-      <c r="N85" s="71"/>
-      <c r="O85" s="71"/>
-      <c r="P85" s="71"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="B86" s="71"/>
-      <c r="C86" s="71"/>
-      <c r="D86" s="71"/>
-      <c r="E86" s="71"/>
-      <c r="F86" s="71"/>
-      <c r="G86" s="71"/>
-      <c r="H86" s="71"/>
-      <c r="I86" s="71"/>
-      <c r="J86" s="71"/>
-      <c r="K86" s="71"/>
-      <c r="L86" s="71"/>
-      <c r="M86" s="71"/>
-      <c r="N86" s="71"/>
-      <c r="O86" s="71"/>
-      <c r="P86" s="71"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
+      <c r="H51" s="31">
+        <f t="shared" ref="H51:Q51" si="9">AVERAGE(H48:H50)</f>
+        <v>16.353333333333335</v>
+      </c>
+      <c r="I51" s="57">
+        <f t="shared" si="9"/>
+        <v>185.02933333333331</v>
+      </c>
+      <c r="J51" s="32">
+        <f t="shared" si="9"/>
+        <v>29.810666666666666</v>
+      </c>
+      <c r="K51" s="32">
+        <f t="shared" si="9"/>
+        <v>4.416666666666667</v>
+      </c>
+      <c r="L51" s="33">
+        <f t="shared" si="9"/>
+        <v>19.271666666666665</v>
+      </c>
+      <c r="M51" s="58">
+        <f t="shared" si="9"/>
+        <v>5.8820000000000006</v>
+      </c>
+      <c r="N51" s="34">
+        <f t="shared" si="9"/>
+        <v>67.451666666666668</v>
+      </c>
+      <c r="O51" s="53">
+        <f t="shared" si="9"/>
+        <v>52.334000000000003</v>
+      </c>
+      <c r="P51" s="35">
+        <f t="shared" si="9"/>
+        <v>20.375666666666664</v>
+      </c>
+      <c r="Q51" s="35">
+        <f t="shared" si="9"/>
+        <v>17.420333333333332</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B52" s="59"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="59"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="59"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="59"/>
+      <c r="O52" s="59"/>
+      <c r="P52" s="59"/>
+    </row>
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B53" s="59"/>
+      <c r="C53" s="59"/>
+      <c r="D53" s="59"/>
+      <c r="E53" s="59"/>
+      <c r="F53" s="59"/>
+      <c r="G53" s="59"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="59"/>
+      <c r="J53" s="59"/>
+      <c r="K53" s="59"/>
+      <c r="L53" s="59"/>
+      <c r="M53" s="59"/>
+      <c r="N53" s="59"/>
+      <c r="O53" s="59"/>
+      <c r="P53" s="59"/>
+    </row>
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B54" s="59"/>
+      <c r="C54" s="59"/>
+      <c r="D54" s="59"/>
+      <c r="E54" s="59"/>
+      <c r="F54" s="59"/>
+      <c r="G54" s="59"/>
+      <c r="H54" s="59"/>
+      <c r="I54" s="59"/>
+      <c r="J54" s="59"/>
+      <c r="K54" s="59"/>
+      <c r="L54" s="59"/>
+      <c r="M54" s="59"/>
+      <c r="N54" s="59"/>
+      <c r="O54" s="59"/>
+      <c r="P54" s="59"/>
+    </row>
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B55" s="59"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="59"/>
+      <c r="H55" s="59"/>
+      <c r="I55" s="59"/>
+      <c r="J55" s="59"/>
+      <c r="K55" s="59"/>
+      <c r="L55" s="59"/>
+      <c r="M55" s="59"/>
+      <c r="N55" s="59"/>
+      <c r="O55" s="59"/>
+      <c r="P55" s="59"/>
+    </row>
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B56" s="59"/>
+      <c r="C56" s="59"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="59"/>
+      <c r="F56" s="59"/>
+      <c r="G56" s="59"/>
+      <c r="H56" s="59"/>
+      <c r="I56" s="59"/>
+      <c r="J56" s="59"/>
+      <c r="K56" s="59"/>
+      <c r="L56" s="59"/>
+      <c r="M56" s="59"/>
+      <c r="N56" s="59"/>
+      <c r="O56" s="59"/>
+      <c r="P56" s="59"/>
+    </row>
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B57" s="59"/>
+      <c r="C57" s="59"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="59"/>
+      <c r="G57" s="59"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="59"/>
+      <c r="J57" s="59"/>
+      <c r="K57" s="59"/>
+      <c r="L57" s="59"/>
+      <c r="M57" s="59"/>
+      <c r="N57" s="59"/>
+      <c r="O57" s="59"/>
+      <c r="P57" s="59"/>
+    </row>
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B58" s="59"/>
+      <c r="C58" s="59"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="59"/>
+      <c r="G58" s="59"/>
+      <c r="H58" s="59"/>
+      <c r="I58" s="59"/>
+      <c r="J58" s="59"/>
+      <c r="K58" s="59"/>
+      <c r="L58" s="59"/>
+      <c r="M58" s="59"/>
+      <c r="N58" s="59"/>
+      <c r="O58" s="59"/>
+      <c r="P58" s="59"/>
+    </row>
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B59" s="59"/>
+      <c r="C59" s="59"/>
+      <c r="D59" s="59"/>
+      <c r="E59" s="59"/>
+      <c r="F59" s="59"/>
+      <c r="G59" s="59"/>
+      <c r="H59" s="59"/>
+      <c r="I59" s="59"/>
+      <c r="J59" s="59"/>
+      <c r="K59" s="59"/>
+      <c r="L59" s="59"/>
+      <c r="M59" s="59"/>
+      <c r="N59" s="59"/>
+      <c r="O59" s="59"/>
+      <c r="P59" s="59"/>
+    </row>
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B60" s="59"/>
+      <c r="C60" s="59"/>
+      <c r="D60" s="59"/>
+      <c r="E60" s="59"/>
+      <c r="F60" s="59"/>
+      <c r="G60" s="59"/>
+      <c r="H60" s="59"/>
+      <c r="I60" s="59"/>
+      <c r="J60" s="59"/>
+      <c r="K60" s="59"/>
+      <c r="L60" s="59"/>
+      <c r="M60" s="59"/>
+      <c r="N60" s="59"/>
+      <c r="O60" s="59"/>
+      <c r="P60" s="59"/>
+    </row>
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B61" s="59"/>
+      <c r="C61" s="59"/>
+      <c r="D61" s="59"/>
+      <c r="E61" s="59"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="59"/>
+      <c r="H61" s="59"/>
+      <c r="I61" s="59"/>
+      <c r="J61" s="59"/>
+      <c r="K61" s="59"/>
+      <c r="L61" s="59"/>
+      <c r="M61" s="59"/>
+      <c r="N61" s="59"/>
+      <c r="O61" s="59"/>
+      <c r="P61" s="59"/>
+    </row>
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B62" s="59"/>
+      <c r="C62" s="59"/>
+      <c r="D62" s="59"/>
+      <c r="E62" s="59"/>
+      <c r="F62" s="59"/>
+      <c r="G62" s="59"/>
+      <c r="H62" s="59"/>
+      <c r="I62" s="59"/>
+      <c r="J62" s="59"/>
+      <c r="K62" s="59"/>
+      <c r="L62" s="59"/>
+      <c r="M62" s="59"/>
+      <c r="N62" s="59"/>
+      <c r="O62" s="59"/>
+      <c r="P62" s="59"/>
+    </row>
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B63" s="59"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="59"/>
+      <c r="E63" s="59"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="59"/>
+      <c r="J63" s="59"/>
+      <c r="K63" s="59"/>
+      <c r="L63" s="59"/>
+      <c r="M63" s="59"/>
+      <c r="N63" s="59"/>
+      <c r="O63" s="59"/>
+      <c r="P63" s="59"/>
+    </row>
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B64" s="59"/>
+      <c r="C64" s="59"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="59"/>
+      <c r="F64" s="59"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="59"/>
+      <c r="K64" s="59"/>
+      <c r="L64" s="59"/>
+      <c r="M64" s="59"/>
+      <c r="N64" s="59"/>
+      <c r="O64" s="59"/>
+      <c r="P64" s="59"/>
+    </row>
+    <row r="65" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B65" s="59"/>
+      <c r="C65" s="59"/>
+      <c r="D65" s="59"/>
+      <c r="E65" s="59"/>
+      <c r="F65" s="59"/>
+      <c r="G65" s="59"/>
+      <c r="H65" s="59"/>
+      <c r="I65" s="59"/>
+      <c r="J65" s="59"/>
+      <c r="K65" s="59"/>
+      <c r="L65" s="59"/>
+      <c r="M65" s="59"/>
+      <c r="N65" s="59"/>
+      <c r="O65" s="59"/>
+      <c r="P65" s="59"/>
+    </row>
+    <row r="66" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B66" s="59"/>
+      <c r="C66" s="59"/>
+      <c r="D66" s="59"/>
+      <c r="E66" s="59"/>
+      <c r="F66" s="59"/>
+      <c r="G66" s="59"/>
+      <c r="H66" s="59"/>
+      <c r="I66" s="59"/>
+      <c r="J66" s="59"/>
+      <c r="K66" s="59"/>
+      <c r="L66" s="59"/>
+      <c r="M66" s="59"/>
+      <c r="N66" s="59"/>
+      <c r="O66" s="59"/>
+      <c r="P66" s="59"/>
+    </row>
+    <row r="67" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B67" s="59"/>
+      <c r="C67" s="59"/>
+      <c r="D67" s="59"/>
+      <c r="E67" s="59"/>
+      <c r="F67" s="59"/>
+      <c r="G67" s="59"/>
+      <c r="H67" s="59"/>
+      <c r="I67" s="59"/>
+      <c r="J67" s="59"/>
+      <c r="K67" s="59"/>
+      <c r="L67" s="59"/>
+      <c r="M67" s="59"/>
+      <c r="N67" s="59"/>
+      <c r="O67" s="59"/>
+      <c r="P67" s="59"/>
+    </row>
+    <row r="68" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B68" s="59"/>
+      <c r="C68" s="59"/>
+      <c r="D68" s="59"/>
+      <c r="E68" s="59"/>
+      <c r="F68" s="59"/>
+      <c r="G68" s="59"/>
+      <c r="H68" s="59"/>
+      <c r="I68" s="59"/>
+      <c r="J68" s="59"/>
+      <c r="K68" s="59"/>
+      <c r="L68" s="59"/>
+      <c r="M68" s="59"/>
+      <c r="N68" s="59"/>
+      <c r="O68" s="59"/>
+      <c r="P68" s="59"/>
+    </row>
+    <row r="69" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="70" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="71" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="72" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="73" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="74" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B74" s="59"/>
+      <c r="C74" s="59"/>
+      <c r="D74" s="59"/>
+      <c r="E74" s="59"/>
+      <c r="F74" s="59"/>
+      <c r="G74" s="59"/>
+      <c r="H74" s="59"/>
+      <c r="I74" s="59"/>
+      <c r="J74" s="59"/>
+      <c r="K74" s="59"/>
+      <c r="L74" s="59"/>
+      <c r="M74" s="59"/>
+      <c r="N74" s="59"/>
+      <c r="O74" s="59"/>
+      <c r="P74" s="59"/>
+    </row>
+    <row r="75" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B75" s="59"/>
+      <c r="C75" s="59"/>
+      <c r="D75" s="59"/>
+      <c r="E75" s="59"/>
+      <c r="F75" s="59"/>
+      <c r="G75" s="59"/>
+      <c r="H75" s="59"/>
+      <c r="I75" s="59"/>
+      <c r="J75" s="59"/>
+      <c r="K75" s="59"/>
+      <c r="L75" s="59"/>
+      <c r="M75" s="59"/>
+      <c r="N75" s="59"/>
+      <c r="O75" s="59"/>
+      <c r="P75" s="59"/>
+    </row>
+    <row r="76" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B76" s="59"/>
+      <c r="C76" s="59"/>
+      <c r="D76" s="59"/>
+      <c r="E76" s="59"/>
+      <c r="F76" s="59"/>
+      <c r="G76" s="59"/>
+      <c r="H76" s="59"/>
+      <c r="I76" s="59"/>
+      <c r="J76" s="59"/>
+      <c r="K76" s="59"/>
+      <c r="L76" s="59"/>
+      <c r="M76" s="59"/>
+      <c r="N76" s="59"/>
+      <c r="O76" s="59"/>
+      <c r="P76" s="59"/>
+    </row>
+    <row r="77" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B77" s="59"/>
+      <c r="C77" s="59"/>
+      <c r="D77" s="59"/>
+      <c r="E77" s="59"/>
+      <c r="F77" s="59"/>
+      <c r="G77" s="59"/>
+      <c r="H77" s="59"/>
+      <c r="I77" s="59"/>
+      <c r="J77" s="59"/>
+      <c r="K77" s="59"/>
+      <c r="L77" s="59"/>
+      <c r="M77" s="59"/>
+      <c r="N77" s="59"/>
+      <c r="O77" s="59"/>
+      <c r="P77" s="59"/>
+    </row>
+    <row r="78" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B78" s="59"/>
+      <c r="C78" s="59"/>
+      <c r="D78" s="59"/>
+      <c r="E78" s="59"/>
+      <c r="F78" s="59"/>
+      <c r="G78" s="59"/>
+      <c r="H78" s="59"/>
+      <c r="I78" s="59"/>
+      <c r="J78" s="59"/>
+      <c r="K78" s="59"/>
+      <c r="L78" s="59"/>
+      <c r="M78" s="59"/>
+      <c r="N78" s="59"/>
+      <c r="O78" s="59"/>
+      <c r="P78" s="59"/>
+    </row>
+    <row r="79" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B79" s="59"/>
+      <c r="C79" s="59"/>
+      <c r="D79" s="59"/>
+      <c r="E79" s="59"/>
+      <c r="F79" s="59"/>
+      <c r="G79" s="59"/>
+      <c r="H79" s="59"/>
+      <c r="I79" s="59"/>
+      <c r="J79" s="59"/>
+      <c r="K79" s="59"/>
+      <c r="L79" s="59"/>
+      <c r="M79" s="59"/>
+      <c r="N79" s="59"/>
+      <c r="O79" s="59"/>
+      <c r="P79" s="59"/>
+    </row>
+    <row r="80" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B80" s="59"/>
+      <c r="C80" s="59"/>
+      <c r="D80" s="59"/>
+      <c r="E80" s="59"/>
+      <c r="F80" s="59"/>
+      <c r="G80" s="59"/>
+      <c r="H80" s="59"/>
+      <c r="I80" s="59"/>
+      <c r="J80" s="59"/>
+      <c r="K80" s="59"/>
+      <c r="L80" s="59"/>
+      <c r="M80" s="59"/>
+      <c r="N80" s="59"/>
+      <c r="O80" s="59"/>
+      <c r="P80" s="59"/>
+    </row>
+    <row r="81" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B81" s="59"/>
+      <c r="C81" s="59"/>
+      <c r="D81" s="59"/>
+      <c r="E81" s="59"/>
+      <c r="F81" s="59"/>
+      <c r="G81" s="59"/>
+      <c r="H81" s="59"/>
+      <c r="I81" s="59"/>
+      <c r="J81" s="59"/>
+      <c r="K81" s="59"/>
+      <c r="L81" s="59"/>
+      <c r="M81" s="59"/>
+      <c r="N81" s="59"/>
+      <c r="O81" s="59"/>
+      <c r="P81" s="59"/>
+    </row>
+    <row r="82" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B82" s="59"/>
+      <c r="C82" s="59"/>
+      <c r="D82" s="59"/>
+      <c r="E82" s="59"/>
+      <c r="F82" s="59"/>
+      <c r="G82" s="59"/>
+      <c r="H82" s="59"/>
+      <c r="I82" s="59"/>
+      <c r="J82" s="59"/>
+      <c r="K82" s="59"/>
+      <c r="L82" s="59"/>
+      <c r="M82" s="59"/>
+      <c r="N82" s="59"/>
+      <c r="O82" s="59"/>
+      <c r="P82" s="59"/>
+    </row>
+    <row r="83" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B83" s="59"/>
+      <c r="C83" s="59"/>
+      <c r="D83" s="59"/>
+      <c r="E83" s="59"/>
+      <c r="F83" s="59"/>
+      <c r="G83" s="59"/>
+      <c r="H83" s="59"/>
+      <c r="I83" s="59"/>
+      <c r="J83" s="59"/>
+      <c r="K83" s="59"/>
+      <c r="L83" s="59"/>
+      <c r="M83" s="59"/>
+      <c r="N83" s="59"/>
+      <c r="O83" s="59"/>
+      <c r="P83" s="59"/>
+    </row>
+    <row r="84" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B84" s="59"/>
+      <c r="C84" s="59"/>
+      <c r="D84" s="59"/>
+      <c r="E84" s="59"/>
+      <c r="F84" s="59"/>
+      <c r="G84" s="59"/>
+      <c r="H84" s="59"/>
+      <c r="I84" s="59"/>
+      <c r="J84" s="59"/>
+      <c r="K84" s="59"/>
+      <c r="L84" s="59"/>
+      <c r="M84" s="59"/>
+      <c r="N84" s="59"/>
+      <c r="O84" s="59"/>
+      <c r="P84" s="59"/>
+    </row>
+    <row r="85" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B85" s="59"/>
+      <c r="C85" s="59"/>
+      <c r="D85" s="59"/>
+      <c r="E85" s="59"/>
+      <c r="F85" s="59"/>
+      <c r="G85" s="59"/>
+      <c r="H85" s="59"/>
+      <c r="I85" s="59"/>
+      <c r="J85" s="59"/>
+      <c r="K85" s="59"/>
+      <c r="L85" s="59"/>
+      <c r="M85" s="59"/>
+      <c r="N85" s="59"/>
+      <c r="O85" s="59"/>
+      <c r="P85" s="59"/>
+    </row>
+    <row r="86" spans="2:16" ht="15.75" customHeight="1">
+      <c r="B86" s="59"/>
+      <c r="C86" s="59"/>
+      <c r="D86" s="59"/>
+      <c r="E86" s="59"/>
+      <c r="F86" s="59"/>
+      <c r="G86" s="59"/>
+      <c r="H86" s="59"/>
+      <c r="I86" s="59"/>
+      <c r="J86" s="59"/>
+      <c r="K86" s="59"/>
+      <c r="L86" s="59"/>
+      <c r="M86" s="59"/>
+      <c r="N86" s="59"/>
+      <c r="O86" s="59"/>
+      <c r="P86" s="59"/>
+    </row>
+    <row r="87" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="88" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="89" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="90" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="91" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="92" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="93" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="94" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="95" spans="2:16" ht="15.75" customHeight="1"/>
+    <row r="96" spans="2:16" ht="15.75" customHeight="1"/>
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1"/>
     <row r="99" ht="15.75" customHeight="1"/>
@@ -4972,830 +4942,828 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:I1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.75"/>
-    <col customWidth="1" min="2" max="6" width="12.63"/>
+    <col min="1" max="1" width="14.7265625" customWidth="1"/>
+    <col min="2" max="6" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="73" t="s">
+      <c r="C1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="76" t="s">
+      <c r="F1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="78" t="s">
+      <c r="H1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="67" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="12">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A2" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="80">
-        <v>0.001</v>
-      </c>
-      <c r="C3" s="81">
-        <v>0.001</v>
-      </c>
-      <c r="D3" s="82">
-        <v>0.001</v>
-      </c>
-      <c r="E3" s="83">
-        <v>0.001</v>
-      </c>
-      <c r="F3" s="84">
-        <v>0.001</v>
-      </c>
-      <c r="G3" s="85">
-        <v>0.001</v>
-      </c>
-      <c r="H3" s="86">
-        <v>0.001</v>
-      </c>
-      <c r="I3" s="87">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
+      <c r="B3" s="68">
+        <v>1E-3</v>
+      </c>
+      <c r="C3" s="69">
+        <v>1E-3</v>
+      </c>
+      <c r="D3" s="70">
+        <v>1E-3</v>
+      </c>
+      <c r="E3" s="71">
+        <v>1E-3</v>
+      </c>
+      <c r="F3" s="72">
+        <v>1E-3</v>
+      </c>
+      <c r="G3" s="73">
+        <v>1E-3</v>
+      </c>
+      <c r="H3" s="74">
+        <v>1E-3</v>
+      </c>
+      <c r="I3" s="75">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="80">
-        <v>0.013</v>
-      </c>
-      <c r="C4" s="81">
-        <v>0.001</v>
-      </c>
-      <c r="D4" s="82">
-        <v>0.002</v>
-      </c>
-      <c r="E4" s="83">
-        <v>0.001</v>
-      </c>
-      <c r="F4" s="84">
-        <v>0.002</v>
-      </c>
-      <c r="G4" s="85">
-        <v>0.001</v>
-      </c>
-      <c r="H4" s="86">
-        <v>0.001</v>
-      </c>
-      <c r="I4" s="87">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
+      <c r="B4" s="68">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="C4" s="69">
+        <v>1E-3</v>
+      </c>
+      <c r="D4" s="70">
+        <v>2E-3</v>
+      </c>
+      <c r="E4" s="71">
+        <v>1E-3</v>
+      </c>
+      <c r="F4" s="72">
+        <v>2E-3</v>
+      </c>
+      <c r="G4" s="73">
+        <v>1E-3</v>
+      </c>
+      <c r="H4" s="74">
+        <v>1E-3</v>
+      </c>
+      <c r="I4" s="75">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="80">
-        <v>0.023</v>
-      </c>
-      <c r="C5" s="81">
-        <v>0.003</v>
-      </c>
-      <c r="D5" s="82">
-        <v>0.003</v>
-      </c>
-      <c r="E5" s="83">
-        <v>0.005</v>
-      </c>
-      <c r="F5" s="84">
-        <v>0.005</v>
-      </c>
-      <c r="G5" s="85">
-        <v>0.003</v>
-      </c>
-      <c r="H5" s="86">
-        <v>0.002</v>
-      </c>
-      <c r="I5" s="87">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
+      <c r="B5" s="68">
+        <v>2.3E-2</v>
+      </c>
+      <c r="C5" s="69">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D5" s="70">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E5" s="71">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="F5" s="72">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G5" s="73">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H5" s="74">
+        <v>2E-3</v>
+      </c>
+      <c r="I5" s="75">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="80">
+      <c r="B6" s="68">
         <v>0.214</v>
       </c>
-      <c r="C6" s="81">
-        <v>0.015</v>
-      </c>
-      <c r="D6" s="82">
-        <v>0.019</v>
-      </c>
-      <c r="E6" s="83">
-        <v>0.013</v>
-      </c>
-      <c r="F6" s="84">
-        <v>0.013</v>
-      </c>
-      <c r="G6" s="85">
-        <v>0.011</v>
-      </c>
-      <c r="H6" s="86">
-        <v>0.011</v>
-      </c>
-      <c r="I6" s="87">
-        <v>0.011</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="12">
-        <v>20.0</v>
-      </c>
-      <c r="B7" s="88"/>
-      <c r="C7" s="88"/>
-      <c r="D7" s="88"/>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
+      <c r="C6" s="69">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="D6" s="70">
+        <v>1.9E-2</v>
+      </c>
+      <c r="E6" s="71">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="F6" s="72">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="G6" s="73">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="H6" s="74">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="I6" s="75">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A7" s="2">
+        <v>20</v>
+      </c>
+      <c r="B7" s="76"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="57">
-        <v>0.022</v>
-      </c>
-      <c r="C8" s="58">
-        <v>0.002</v>
-      </c>
-      <c r="D8" s="59">
-        <v>0.002</v>
-      </c>
-      <c r="E8" s="60">
-        <v>0.003</v>
-      </c>
-      <c r="F8" s="61">
-        <v>0.002</v>
-      </c>
-      <c r="G8" s="62">
-        <v>0.003</v>
-      </c>
-      <c r="H8" s="63">
-        <v>0.002</v>
-      </c>
-      <c r="I8" s="64">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
+      <c r="B8" s="47">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="C8" s="48">
+        <v>2E-3</v>
+      </c>
+      <c r="D8" s="49">
+        <v>2E-3</v>
+      </c>
+      <c r="E8" s="50">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="F8" s="51">
+        <v>2E-3</v>
+      </c>
+      <c r="G8" s="52">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H8" s="53">
+        <v>2E-3</v>
+      </c>
+      <c r="I8" s="54">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="57">
-        <v>0.028</v>
-      </c>
-      <c r="C9" s="58">
-        <v>0.004</v>
-      </c>
-      <c r="D9" s="59">
-        <v>0.004</v>
-      </c>
-      <c r="E9" s="60">
-        <v>0.004</v>
-      </c>
-      <c r="F9" s="61">
-        <v>0.003</v>
-      </c>
-      <c r="G9" s="62">
-        <v>0.003</v>
-      </c>
-      <c r="H9" s="63">
-        <v>0.004</v>
-      </c>
-      <c r="I9" s="64">
-        <v>0.003</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
+      <c r="B9" s="47">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="C9" s="48">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D9" s="49">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E9" s="50">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="F9" s="51">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G9" s="52">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H9" s="53">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I9" s="54">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="57">
-        <v>0.032</v>
-      </c>
-      <c r="C10" s="58">
-        <v>0.004</v>
-      </c>
-      <c r="D10" s="59">
-        <v>0.007</v>
-      </c>
-      <c r="E10" s="60">
-        <v>0.004</v>
-      </c>
-      <c r="F10" s="61">
-        <v>0.004</v>
-      </c>
-      <c r="G10" s="62">
-        <v>0.005</v>
-      </c>
-      <c r="H10" s="63">
-        <v>0.004</v>
-      </c>
-      <c r="I10" s="64">
-        <v>0.004</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
+      <c r="B10" s="47">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="C10" s="48">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D10" s="49">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="E10" s="50">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="F10" s="51">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G10" s="52">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="H10" s="53">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I10" s="54">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="57">
-        <v>0.146</v>
-      </c>
-      <c r="C11" s="58">
-        <v>0.031</v>
-      </c>
-      <c r="D11" s="59">
-        <v>0.036</v>
-      </c>
-      <c r="E11" s="60">
-        <v>0.031</v>
-      </c>
-      <c r="F11" s="61">
-        <v>0.023</v>
-      </c>
-      <c r="G11" s="62">
+      <c r="B11" s="47">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="C11" s="48">
+        <v>3.1E-2</v>
+      </c>
+      <c r="D11" s="49">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="E11" s="50">
+        <v>3.1E-2</v>
+      </c>
+      <c r="F11" s="51">
+        <v>2.3E-2</v>
+      </c>
+      <c r="G11" s="52">
         <v>0.02</v>
       </c>
-      <c r="H11" s="63">
-        <v>0.021</v>
-      </c>
-      <c r="I11" s="64">
-        <v>0.022</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="12">
-        <v>50.0</v>
-      </c>
-      <c r="B12" s="88"/>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88"/>
-      <c r="E12" s="88"/>
-      <c r="F12" s="88"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="88"/>
-      <c r="I12" s="88"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
+      <c r="H11" s="53">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="I11" s="54">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A12" s="2">
+        <v>50</v>
+      </c>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="76"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="80">
-        <v>0.022</v>
-      </c>
-      <c r="C13" s="81">
-        <v>0.011</v>
-      </c>
-      <c r="D13" s="82">
-        <v>0.012</v>
-      </c>
-      <c r="E13" s="83">
-        <v>0.009</v>
-      </c>
-      <c r="F13" s="84">
-        <v>0.009</v>
-      </c>
-      <c r="G13" s="85">
-        <v>0.008</v>
-      </c>
-      <c r="H13" s="86">
-        <v>0.008</v>
-      </c>
-      <c r="I13" s="87">
-        <v>0.009</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
+      <c r="B13" s="68">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="C13" s="69">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D13" s="70">
+        <v>1.2E-2</v>
+      </c>
+      <c r="E13" s="71">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="F13" s="72">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="G13" s="73">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="H13" s="74">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I13" s="75">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="80">
-        <v>0.048</v>
-      </c>
-      <c r="C14" s="81">
-        <v>0.012</v>
-      </c>
-      <c r="D14" s="82">
+      <c r="B14" s="68">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="C14" s="69">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D14" s="70">
         <v>0.01</v>
       </c>
-      <c r="E14" s="83">
-        <v>0.008</v>
-      </c>
-      <c r="F14" s="84">
-        <v>0.007</v>
-      </c>
-      <c r="G14" s="85">
-        <v>0.007</v>
-      </c>
-      <c r="H14" s="86">
-        <v>0.006</v>
-      </c>
-      <c r="I14" s="87">
-        <v>0.006</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
+      <c r="E14" s="71">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F14" s="72">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="G14" s="73">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="H14" s="74">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I14" s="75">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="80">
-        <v>0.022</v>
-      </c>
-      <c r="C15" s="81">
-        <v>0.011</v>
-      </c>
-      <c r="D15" s="82">
-        <v>0.008</v>
-      </c>
-      <c r="E15" s="83">
-        <v>0.011</v>
-      </c>
-      <c r="F15" s="84">
-        <v>0.011</v>
-      </c>
-      <c r="G15" s="85">
+      <c r="B15" s="68">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="C15" s="69">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="D15" s="70">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="E15" s="71">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="F15" s="72">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="G15" s="73">
         <v>0.09</v>
       </c>
-      <c r="H15" s="86">
+      <c r="H15" s="74">
         <v>0.01</v>
       </c>
-      <c r="I15" s="87">
-        <v>0.008</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
+      <c r="I15" s="75">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="80">
+      <c r="B16" s="68">
         <v>0.128</v>
       </c>
-      <c r="C16" s="81">
-        <v>0.068</v>
-      </c>
-      <c r="D16" s="82">
-        <v>0.063</v>
-      </c>
-      <c r="E16" s="83">
+      <c r="C16" s="69">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="D16" s="70">
+        <v>6.3E-2</v>
+      </c>
+      <c r="E16" s="71">
         <v>0.05</v>
       </c>
-      <c r="F16" s="84">
-        <v>0.054</v>
-      </c>
-      <c r="G16" s="85">
-        <v>0.052</v>
-      </c>
-      <c r="H16" s="86">
-        <v>0.051</v>
-      </c>
-      <c r="I16" s="87">
+      <c r="F16" s="72">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G16" s="73">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="H16" s="74">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="I16" s="75">
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="12">
-        <v>100.0</v>
-      </c>
-      <c r="B17" s="88"/>
-      <c r="C17" s="88"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="88"/>
-      <c r="H17" s="88"/>
-      <c r="I17" s="88"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A17" s="2">
+        <v>100</v>
+      </c>
+      <c r="B17" s="76"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="76"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="76"/>
+      <c r="I17" s="76"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="57">
-        <v>0.035</v>
-      </c>
-      <c r="C18" s="58">
-        <v>0.027</v>
-      </c>
-      <c r="D18" s="59">
-        <v>0.015</v>
-      </c>
-      <c r="E18" s="60">
-        <v>0.016</v>
-      </c>
-      <c r="F18" s="61">
-        <v>0.015</v>
-      </c>
-      <c r="G18" s="62">
-        <v>0.019</v>
-      </c>
-      <c r="H18" s="63">
-        <v>0.016</v>
-      </c>
-      <c r="I18" s="64">
-        <v>0.016</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
+      <c r="B18" s="47">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="C18" s="48">
+        <v>2.7E-2</v>
+      </c>
+      <c r="D18" s="49">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="E18" s="50">
+        <v>1.6E-2</v>
+      </c>
+      <c r="F18" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G18" s="52">
+        <v>1.9E-2</v>
+      </c>
+      <c r="H18" s="53">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I18" s="54">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="57">
+      <c r="B19" s="47">
         <v>0.124</v>
       </c>
-      <c r="C19" s="58">
-        <v>0.014</v>
-      </c>
-      <c r="D19" s="59">
-        <v>0.014</v>
-      </c>
-      <c r="E19" s="60">
-        <v>0.016</v>
-      </c>
-      <c r="F19" s="61">
-        <v>0.015</v>
-      </c>
-      <c r="G19" s="62">
-        <v>0.014</v>
-      </c>
-      <c r="H19" s="63">
-        <v>0.013</v>
-      </c>
-      <c r="I19" s="64">
-        <v>0.013</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
+      <c r="C19" s="48">
+        <v>1.4E-2</v>
+      </c>
+      <c r="D19" s="49">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E19" s="50">
+        <v>1.6E-2</v>
+      </c>
+      <c r="F19" s="51">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="G19" s="52">
+        <v>1.4E-2</v>
+      </c>
+      <c r="H19" s="53">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="I19" s="54">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="57">
-        <v>0.084</v>
-      </c>
-      <c r="C20" s="58">
+      <c r="B20" s="47">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="C20" s="48">
         <v>0.02</v>
       </c>
-      <c r="D20" s="59">
-        <v>0.017</v>
-      </c>
-      <c r="E20" s="60">
-        <v>0.018</v>
-      </c>
-      <c r="F20" s="61">
-        <v>0.019</v>
-      </c>
-      <c r="G20" s="62">
-        <v>0.019</v>
-      </c>
-      <c r="H20" s="63">
+      <c r="D20" s="49">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="E20" s="50">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="F20" s="51">
+        <v>1.9E-2</v>
+      </c>
+      <c r="G20" s="52">
+        <v>1.9E-2</v>
+      </c>
+      <c r="H20" s="53">
         <v>0.02</v>
       </c>
-      <c r="I20" s="64">
-        <v>0.018</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
+      <c r="I20" s="54">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="57">
+      <c r="B21" s="47">
         <v>0.27</v>
       </c>
-      <c r="C21" s="58">
+      <c r="C21" s="48">
         <v>0.13</v>
       </c>
-      <c r="D21" s="59">
+      <c r="D21" s="49">
         <v>0.12</v>
       </c>
-      <c r="E21" s="60">
+      <c r="E21" s="50">
         <v>0.126</v>
       </c>
-      <c r="F21" s="61">
+      <c r="F21" s="51">
         <v>0.108</v>
       </c>
-      <c r="G21" s="62">
-        <v>0.096</v>
-      </c>
-      <c r="H21" s="63">
-        <v>0.102</v>
-      </c>
-      <c r="I21" s="64">
-        <v>0.096</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12">
-        <v>1000.0</v>
-      </c>
-      <c r="B22" s="88"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="88"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="88"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="88"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
+      <c r="G21" s="52">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="H21" s="53">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="I21" s="54">
+        <v>9.6000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A22" s="2">
+        <v>1000</v>
+      </c>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="57">
+      <c r="B23" s="47">
         <v>0.23</v>
       </c>
-      <c r="C23" s="58">
-        <v>0.404</v>
-      </c>
-      <c r="D23" s="59">
+      <c r="C23" s="48">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="D23" s="49">
         <v>0.25</v>
       </c>
-      <c r="E23" s="60">
-        <v>0.199</v>
-      </c>
-      <c r="F23" s="61">
+      <c r="E23" s="50">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="F23" s="51">
         <v>0.186</v>
       </c>
-      <c r="G23" s="62">
+      <c r="G23" s="52">
         <v>0.189</v>
       </c>
-      <c r="H23" s="63">
-        <v>0.181</v>
-      </c>
-      <c r="I23" s="64">
-        <v>0.173</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
+      <c r="H23" s="53">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="I23" s="54">
+        <v>0.17299999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="57">
+      <c r="B24" s="47">
         <v>0.877</v>
       </c>
-      <c r="C24" s="58">
-        <v>0.742</v>
-      </c>
-      <c r="D24" s="59">
-        <v>0.275</v>
-      </c>
-      <c r="E24" s="60">
-        <v>0.166</v>
-      </c>
-      <c r="F24" s="61">
+      <c r="C24" s="48">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="D24" s="49">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="E24" s="50">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="F24" s="51">
         <v>0.2</v>
       </c>
-      <c r="G24" s="62">
+      <c r="G24" s="52">
         <v>0.155</v>
       </c>
-      <c r="H24" s="63">
-        <v>0.172</v>
-      </c>
-      <c r="I24" s="64">
-        <v>0.179</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
+      <c r="H24" s="53">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="I24" s="54">
+        <v>0.17899999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="57">
-        <v>1.076</v>
-      </c>
-      <c r="C25" s="58">
-        <v>0.744</v>
-      </c>
-      <c r="D25" s="59">
-        <v>0.264</v>
-      </c>
-      <c r="E25" s="60">
-        <v>0.226</v>
-      </c>
-      <c r="F25" s="61">
-        <v>0.202</v>
-      </c>
-      <c r="G25" s="62">
-        <v>0.227</v>
-      </c>
-      <c r="H25" s="63">
-        <v>0.206</v>
-      </c>
-      <c r="I25" s="64">
+      <c r="B25" s="47">
+        <v>1.0760000000000001</v>
+      </c>
+      <c r="C25" s="48">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="D25" s="49">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="E25" s="50">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="F25" s="51">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="G25" s="52">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="H25" s="53">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="I25" s="54">
         <v>0.21</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:9" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="57">
+      <c r="B26" s="47">
         <v>1.752</v>
       </c>
-      <c r="C26" s="58">
-        <v>1.346</v>
-      </c>
-      <c r="D26" s="89">
+      <c r="C26" s="48">
+        <v>1.3460000000000001</v>
+      </c>
+      <c r="D26" s="77">
         <v>1.81</v>
       </c>
-      <c r="E26" s="90">
+      <c r="E26" s="78">
         <v>1.99</v>
       </c>
-      <c r="F26" s="61">
-        <v>1.886</v>
-      </c>
-      <c r="G26" s="62">
-        <v>1.886</v>
-      </c>
-      <c r="H26" s="63">
-        <v>1.991</v>
-      </c>
-      <c r="I26" s="64">
+      <c r="F26" s="51">
+        <v>1.8859999999999999</v>
+      </c>
+      <c r="G26" s="52">
+        <v>1.8859999999999999</v>
+      </c>
+      <c r="H26" s="53">
+        <v>1.9910000000000001</v>
+      </c>
+      <c r="I26" s="54">
         <v>1.841</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="12">
-        <v>10000.0</v>
-      </c>
-      <c r="B27" s="88"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="27" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A27" s="2">
+        <v>10000</v>
+      </c>
+      <c r="B27" s="76"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="76"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="76"/>
+      <c r="I27" s="76"/>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="57">
+      <c r="B28" s="47">
         <v>6.452</v>
       </c>
-      <c r="C28" s="58">
-        <v>5.999</v>
-      </c>
-      <c r="D28" s="59">
-        <v>5.567</v>
-      </c>
-      <c r="E28" s="60">
-        <v>5.269</v>
-      </c>
-      <c r="F28" s="91">
+      <c r="C28" s="48">
+        <v>5.9989999999999997</v>
+      </c>
+      <c r="D28" s="49">
+        <v>5.5670000000000002</v>
+      </c>
+      <c r="E28" s="50">
+        <v>5.2690000000000001</v>
+      </c>
+      <c r="F28" s="79">
         <v>5.89</v>
       </c>
-      <c r="G28" s="62">
-        <v>5.662</v>
-      </c>
-      <c r="H28" s="63">
-        <v>5.103</v>
-      </c>
-      <c r="I28" s="64">
-        <v>5.545</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
+      <c r="G28" s="52">
+        <v>5.6619999999999999</v>
+      </c>
+      <c r="H28" s="53">
+        <v>5.1029999999999998</v>
+      </c>
+      <c r="I28" s="54">
+        <v>5.5449999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="57">
-        <v>8.634</v>
-      </c>
-      <c r="C29" s="58">
-        <v>7.934</v>
-      </c>
-      <c r="D29" s="59">
-        <v>8.639</v>
-      </c>
-      <c r="E29" s="60">
-        <v>8.042</v>
-      </c>
-      <c r="F29" s="61">
-        <v>8.184</v>
-      </c>
-      <c r="G29" s="62">
-        <v>8.614</v>
-      </c>
-      <c r="H29" s="63">
-        <v>7.481</v>
-      </c>
-      <c r="I29" s="64">
-        <v>7.725</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
+      <c r="B29" s="47">
+        <v>8.6340000000000003</v>
+      </c>
+      <c r="C29" s="48">
+        <v>7.9340000000000002</v>
+      </c>
+      <c r="D29" s="49">
+        <v>8.6389999999999993</v>
+      </c>
+      <c r="E29" s="50">
+        <v>8.0419999999999998</v>
+      </c>
+      <c r="F29" s="51">
+        <v>8.1839999999999993</v>
+      </c>
+      <c r="G29" s="52">
+        <v>8.6140000000000008</v>
+      </c>
+      <c r="H29" s="53">
+        <v>7.4809999999999999</v>
+      </c>
+      <c r="I29" s="54">
+        <v>7.7249999999999996</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="57">
+      <c r="B30" s="47">
         <v>10.96</v>
       </c>
-      <c r="C30" s="58">
-        <v>9.955</v>
-      </c>
-      <c r="D30" s="59">
+      <c r="C30" s="48">
+        <v>9.9550000000000001</v>
+      </c>
+      <c r="D30" s="49">
         <v>10.315</v>
       </c>
-      <c r="E30" s="60">
-        <v>9.822</v>
-      </c>
-      <c r="F30" s="61">
+      <c r="E30" s="50">
+        <v>9.8219999999999992</v>
+      </c>
+      <c r="F30" s="51">
         <v>9.65</v>
       </c>
-      <c r="G30" s="62">
-        <v>9.247</v>
-      </c>
-      <c r="H30" s="63">
-        <v>9.434</v>
-      </c>
-      <c r="I30" s="64">
-        <v>9.821</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
+      <c r="G30" s="52">
+        <v>9.2469999999999999</v>
+      </c>
+      <c r="H30" s="53">
+        <v>9.4339999999999993</v>
+      </c>
+      <c r="I30" s="54">
+        <v>9.8209999999999997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="57">
-        <v>20.143</v>
-      </c>
-      <c r="C31" s="58">
-        <v>20.565</v>
-      </c>
-      <c r="D31" s="59">
+      <c r="B31" s="47">
+        <v>20.143000000000001</v>
+      </c>
+      <c r="C31" s="48">
+        <v>20.565000000000001</v>
+      </c>
+      <c r="D31" s="49">
         <v>19.506</v>
       </c>
-      <c r="E31" s="60">
-        <v>17.705</v>
-      </c>
-      <c r="F31" s="61">
-        <v>17.565</v>
-      </c>
-      <c r="G31" s="62">
-        <v>17.798</v>
-      </c>
-      <c r="H31" s="63">
+      <c r="E31" s="50">
+        <v>17.704999999999998</v>
+      </c>
+      <c r="F31" s="51">
+        <v>17.565000000000001</v>
+      </c>
+      <c r="G31" s="52">
+        <v>17.797999999999998</v>
+      </c>
+      <c r="H31" s="53">
         <v>17.509</v>
       </c>
-      <c r="I31" s="64">
+      <c r="I31" s="54">
         <v>17.762</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -6765,341 +6733,339 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:I1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.13"/>
-    <col customWidth="1" min="2" max="6" width="12.63"/>
+    <col min="1" max="1" width="16.08984375" customWidth="1"/>
+    <col min="2" max="6" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A1" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="73" t="s">
+      <c r="C1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="76" t="s">
+      <c r="F1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="78" t="s">
+      <c r="H1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="67" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1">
       <c r="A2" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B2" s="94">
-        <v>3.0E-7</v>
-      </c>
-      <c r="C2" s="95">
-        <v>3.0E-7</v>
-      </c>
-      <c r="D2" s="96">
-        <v>3.0E-7</v>
-      </c>
-      <c r="E2" s="97">
-        <v>1.0E-6</v>
-      </c>
-      <c r="F2" s="98">
-        <v>1.09E-6</v>
-      </c>
-      <c r="G2" s="99">
-        <v>5.9E-6</v>
-      </c>
-      <c r="H2" s="100">
-        <v>1.0E-6</v>
-      </c>
-      <c r="I2" s="101">
-        <v>2.0E-7</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
+        <v>10</v>
+      </c>
+      <c r="B2" s="82">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="C2" s="83">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="D2" s="84">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="E2" s="85">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="F2" s="86">
+        <v>1.0899999999999999E-6</v>
+      </c>
+      <c r="G2" s="87">
+        <v>5.9000000000000003E-6</v>
+      </c>
+      <c r="H2" s="88">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="I2" s="89">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1">
       <c r="A3" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="B3" s="94">
-        <v>3.0E-7</v>
-      </c>
-      <c r="C3" s="95">
-        <v>6.0E-7</v>
-      </c>
-      <c r="D3" s="96">
-        <v>5.0E-7</v>
-      </c>
-      <c r="E3" s="97">
-        <v>1.0E-6</v>
-      </c>
-      <c r="F3" s="102">
-        <v>8.8E-6</v>
-      </c>
-      <c r="G3" s="99">
-        <v>9.8E-6</v>
-      </c>
-      <c r="H3" s="103">
-        <v>1.4E-6</v>
-      </c>
-      <c r="I3" s="101">
-        <v>3.0E-7</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
+        <v>20</v>
+      </c>
+      <c r="B3" s="82">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="C3" s="83">
+        <v>5.9999999999999997E-7</v>
+      </c>
+      <c r="D3" s="84">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="E3" s="85">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="F3" s="90">
+        <v>8.8000000000000004E-6</v>
+      </c>
+      <c r="G3" s="87">
+        <v>9.7999999999999993E-6</v>
+      </c>
+      <c r="H3" s="91">
+        <v>1.3999999999999999E-6</v>
+      </c>
+      <c r="I3" s="89">
+        <v>2.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" customHeight="1">
       <c r="A4" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="B4" s="94">
-        <v>3.0E-7</v>
-      </c>
-      <c r="C4" s="95">
+        <v>50</v>
+      </c>
+      <c r="B4" s="82">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="C4" s="83">
         <v>2.7E-6</v>
       </c>
-      <c r="D4" s="96">
+      <c r="D4" s="84">
         <v>1.9E-6</v>
       </c>
-      <c r="E4" s="104">
-        <v>2.1E-6</v>
-      </c>
-      <c r="F4" s="105">
-        <v>1.6E-5</v>
-      </c>
-      <c r="G4" s="99">
-        <v>2.07E-5</v>
-      </c>
-      <c r="H4" s="103">
-        <v>4.7E-6</v>
-      </c>
-      <c r="I4" s="101">
-        <v>2.6E-6</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
+      <c r="E4" s="92">
+        <v>2.0999999999999998E-6</v>
+      </c>
+      <c r="F4" s="93">
+        <v>1.5999999999999999E-5</v>
+      </c>
+      <c r="G4" s="87">
+        <v>2.0699999999999998E-5</v>
+      </c>
+      <c r="H4" s="91">
+        <v>4.6999999999999999E-6</v>
+      </c>
+      <c r="I4" s="89">
+        <v>2.6000000000000001E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="A5" s="1">
-        <v>100.0</v>
-      </c>
-      <c r="B5" s="94">
-        <v>5.0E-7</v>
-      </c>
-      <c r="C5" s="95">
-        <v>9.4E-6</v>
-      </c>
-      <c r="D5" s="96">
-        <v>6.6E-6</v>
-      </c>
-      <c r="E5" s="104">
-        <v>3.5E-6</v>
-      </c>
-      <c r="F5" s="102">
-        <v>2.46E-5</v>
-      </c>
-      <c r="G5" s="106">
+        <v>100</v>
+      </c>
+      <c r="B5" s="82">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="C5" s="83">
+        <v>9.3999999999999998E-6</v>
+      </c>
+      <c r="D5" s="84">
+        <v>6.6000000000000003E-6</v>
+      </c>
+      <c r="E5" s="92">
+        <v>3.4999999999999999E-6</v>
+      </c>
+      <c r="F5" s="90">
+        <v>2.4600000000000002E-5</v>
+      </c>
+      <c r="G5" s="94">
         <v>3.4E-5</v>
       </c>
-      <c r="H5" s="103">
-        <v>8.5E-6</v>
-      </c>
-      <c r="I5" s="101">
-        <v>4.9E-6</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
+      <c r="H5" s="91">
+        <v>8.4999999999999999E-6</v>
+      </c>
+      <c r="I5" s="89">
+        <v>4.8999999999999997E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1">
       <c r="A6" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="B6" s="94">
-        <v>3.5E-6</v>
-      </c>
-      <c r="C6" s="95">
-        <v>0.0010503</v>
-      </c>
-      <c r="D6" s="96">
-        <v>8.345E-4</v>
-      </c>
-      <c r="E6" s="104">
-        <v>3.47E-5</v>
-      </c>
-      <c r="F6" s="102">
-        <v>4.542E-4</v>
-      </c>
-      <c r="G6" s="99">
-        <v>2.598E-4</v>
-      </c>
-      <c r="H6" s="103">
-        <v>2.271E-4</v>
-      </c>
-      <c r="I6" s="107">
-        <v>7.8E-5</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
+        <v>1000</v>
+      </c>
+      <c r="B6" s="82">
+        <v>3.4999999999999999E-6</v>
+      </c>
+      <c r="C6" s="83">
+        <v>1.0503000000000001E-3</v>
+      </c>
+      <c r="D6" s="84">
+        <v>8.3449999999999996E-4</v>
+      </c>
+      <c r="E6" s="92">
+        <v>3.4700000000000003E-5</v>
+      </c>
+      <c r="F6" s="90">
+        <v>4.5419999999999998E-4</v>
+      </c>
+      <c r="G6" s="87">
+        <v>2.5980000000000003E-4</v>
+      </c>
+      <c r="H6" s="91">
+        <v>2.2709999999999999E-4</v>
+      </c>
+      <c r="I6" s="95">
+        <v>7.7999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1">
       <c r="A7" s="1">
-        <v>10000.0</v>
-      </c>
-      <c r="B7" s="94">
+        <v>10000</v>
+      </c>
+      <c r="B7" s="82">
         <v>3.43E-5</v>
       </c>
-      <c r="C7" s="95">
-        <v>0.0897676</v>
-      </c>
-      <c r="D7" s="96">
-        <v>0.0780845</v>
-      </c>
-      <c r="E7" s="104">
-        <v>4.43E-4</v>
-      </c>
-      <c r="F7" s="102">
-        <v>0.0022143</v>
-      </c>
-      <c r="G7" s="106">
-        <v>0.001831</v>
-      </c>
-      <c r="H7" s="103">
-        <v>0.0022367</v>
-      </c>
-      <c r="I7" s="101">
-        <v>7.689E-4</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
+      <c r="C7" s="83">
+        <v>8.9767600000000003E-2</v>
+      </c>
+      <c r="D7" s="84">
+        <v>7.8084500000000001E-2</v>
+      </c>
+      <c r="E7" s="92">
+        <v>4.4299999999999998E-4</v>
+      </c>
+      <c r="F7" s="90">
+        <v>2.2143000000000002E-3</v>
+      </c>
+      <c r="G7" s="94">
+        <v>1.8309999999999999E-3</v>
+      </c>
+      <c r="H7" s="91">
+        <v>2.2366999999999999E-3</v>
+      </c>
+      <c r="I7" s="89">
+        <v>7.6889999999999999E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1">
       <c r="A8" s="1">
-        <v>100000.0</v>
-      </c>
-      <c r="B8" s="94">
+        <v>100000</v>
+      </c>
+      <c r="B8" s="82">
         <v>7.718E-4</v>
       </c>
-      <c r="C8" s="95">
-        <v>8.8455091</v>
-      </c>
-      <c r="D8" s="96">
-        <v>6.1233466</v>
-      </c>
-      <c r="E8" s="104">
-        <v>0.0047988</v>
-      </c>
-      <c r="F8" s="102">
-        <v>0.0211812</v>
-      </c>
-      <c r="G8" s="106">
-        <v>0.015377</v>
-      </c>
-      <c r="H8" s="103">
-        <v>0.0174025</v>
-      </c>
-      <c r="I8" s="101">
-        <v>0.0075601</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
+      <c r="C8" s="83">
+        <v>8.8455090999999992</v>
+      </c>
+      <c r="D8" s="84">
+        <v>6.1233465999999996</v>
+      </c>
+      <c r="E8" s="92">
+        <v>4.7987999999999998E-3</v>
+      </c>
+      <c r="F8" s="90">
+        <v>2.1181200000000001E-2</v>
+      </c>
+      <c r="G8" s="94">
+        <v>1.5377E-2</v>
+      </c>
+      <c r="H8" s="91">
+        <v>1.7402500000000001E-2</v>
+      </c>
+      <c r="I8" s="89">
+        <v>7.5601000000000002E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="A9" s="1">
-        <v>1000000.0</v>
-      </c>
-      <c r="B9" s="94">
-        <v>0.0032974</v>
-      </c>
-      <c r="C9" s="108">
-        <v>712.896</v>
-      </c>
-      <c r="D9" s="109">
-        <v>573.0</v>
-      </c>
-      <c r="E9" s="104">
-        <v>0.0545904</v>
-      </c>
-      <c r="F9" s="102">
-        <v>0.1694797</v>
-      </c>
-      <c r="G9" s="106">
-        <v>0.173863</v>
-      </c>
-      <c r="H9" s="103">
-        <v>0.2308553</v>
-      </c>
-      <c r="I9" s="101">
-        <v>0.0963435</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
+        <v>1000000</v>
+      </c>
+      <c r="B9" s="82">
+        <v>3.2973999999999998E-3</v>
+      </c>
+      <c r="C9" s="114">
+        <v>906.70960090000005</v>
+      </c>
+      <c r="D9" s="113">
+        <v>710.28378339999995</v>
+      </c>
+      <c r="E9" s="92">
+        <v>5.4590399999999997E-2</v>
+      </c>
+      <c r="F9" s="90">
+        <v>0.16947970000000001</v>
+      </c>
+      <c r="G9" s="94">
+        <v>0.17386299999999999</v>
+      </c>
+      <c r="H9" s="91">
+        <v>0.23085530000000001</v>
+      </c>
+      <c r="I9" s="89">
+        <v>9.6343499999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1">
       <c r="A10" s="1">
-        <v>1.0E7</v>
-      </c>
-      <c r="B10" s="110">
-        <v>0.0399872</v>
-      </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="104">
-        <v>0.6544425</v>
-      </c>
-      <c r="F10" s="113">
+        <v>10000000</v>
+      </c>
+      <c r="B10" s="96">
+        <v>3.9987200000000001E-2</v>
+      </c>
+      <c r="C10" s="97"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="92">
+        <v>0.65444250000000004</v>
+      </c>
+      <c r="F10" s="99">
         <v>1.8745352</v>
       </c>
-      <c r="G10" s="99">
-        <v>1.8603602</v>
-      </c>
-      <c r="H10" s="103">
-        <v>2.5100879</v>
-      </c>
-      <c r="I10" s="101">
+      <c r="G10" s="87">
+        <v>1.8603601999999999</v>
+      </c>
+      <c r="H10" s="91">
+        <v>2.5100878999999998</v>
+      </c>
+      <c r="I10" s="89">
         <v>1.1909049</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1">
       <c r="A11" s="1">
-        <v>1.0E8</v>
-      </c>
-      <c r="B11" s="110">
-        <v>0.3132697</v>
-      </c>
-      <c r="C11" s="114"/>
-      <c r="D11" s="115"/>
-      <c r="E11" s="104">
+        <v>100000000</v>
+      </c>
+      <c r="B11" s="96">
+        <v>0.31326969999999998</v>
+      </c>
+      <c r="C11" s="100"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="92">
         <v>7.4575182</v>
       </c>
-      <c r="F11" s="113">
-        <v>17.4806584</v>
-      </c>
-      <c r="G11" s="99">
+      <c r="F11" s="99">
+        <v>17.480658399999999</v>
+      </c>
+      <c r="G11" s="87">
         <v>19.6583179</v>
       </c>
-      <c r="H11" s="116">
-        <v>26.924</v>
-      </c>
-      <c r="I11" s="117">
-        <v>11.505</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
+      <c r="H11" s="91">
+        <v>26.923999999999999</v>
+      </c>
+      <c r="I11" s="89">
+        <v>11.505000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -8085,341 +8051,339 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:I1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.38"/>
-    <col customWidth="1" min="2" max="6" width="12.63"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="6" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A1" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="73" t="s">
+      <c r="C1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="76" t="s">
+      <c r="F1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="78" t="s">
+      <c r="H1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="67" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1">
       <c r="A2" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B2" s="94">
-        <v>2.0E-7</v>
-      </c>
-      <c r="C2" s="95">
-        <v>4.0E-7</v>
-      </c>
-      <c r="D2" s="96">
-        <v>5.0E-7</v>
-      </c>
-      <c r="E2" s="104">
-        <v>1.1E-6</v>
-      </c>
-      <c r="F2" s="102">
-        <v>1.07E-5</v>
-      </c>
-      <c r="G2" s="99">
+        <v>10</v>
+      </c>
+      <c r="B2" s="120">
+        <v>1.9999999999999999E-7</v>
+      </c>
+      <c r="C2" s="121">
+        <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="D2" s="122">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="E2" s="123">
+        <v>1.1000000000000001E-6</v>
+      </c>
+      <c r="F2" s="124">
+        <v>1.0699999999999999E-5</v>
+      </c>
+      <c r="G2" s="125">
         <v>2.7E-6</v>
       </c>
-      <c r="H2" s="100">
-        <v>1.0E-6</v>
-      </c>
-      <c r="I2" s="101">
-        <v>3.0E-7</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
+      <c r="H2" s="126">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="I2" s="127">
+        <v>2.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1">
       <c r="A3" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="B3" s="94">
-        <v>5.0E-7</v>
-      </c>
-      <c r="C3" s="95">
-        <v>7.0E-7</v>
-      </c>
-      <c r="D3" s="96">
-        <v>5.0E-7</v>
-      </c>
-      <c r="E3" s="104">
-        <v>1.2E-6</v>
-      </c>
-      <c r="F3" s="102">
+        <v>20</v>
+      </c>
+      <c r="B3" s="120">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="C3" s="121">
+        <v>6.9999999999999997E-7</v>
+      </c>
+      <c r="D3" s="122">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="E3" s="123">
+        <v>1.1999999999999999E-6</v>
+      </c>
+      <c r="F3" s="124">
         <v>1.19E-5</v>
       </c>
-      <c r="G3" s="99">
-        <v>7.6E-6</v>
-      </c>
-      <c r="H3" s="103">
+      <c r="G3" s="125">
+        <v>7.6000000000000001E-6</v>
+      </c>
+      <c r="H3" s="126">
         <v>1.5E-6</v>
       </c>
-      <c r="I3" s="101">
-        <v>4.0E-7</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
+      <c r="I3" s="127">
+        <v>3.9999999999999998E-7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" customHeight="1">
       <c r="A4" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="B4" s="94">
-        <v>5.0E-7</v>
-      </c>
-      <c r="C4" s="95">
-        <v>3.4E-6</v>
-      </c>
-      <c r="D4" s="96">
+        <v>50</v>
+      </c>
+      <c r="B4" s="120">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="C4" s="121">
+        <v>3.4000000000000001E-6</v>
+      </c>
+      <c r="D4" s="122">
         <v>2.7E-6</v>
       </c>
-      <c r="E4" s="104">
-        <v>2.8E-6</v>
-      </c>
-      <c r="F4" s="102">
-        <v>3.14E-5</v>
-      </c>
-      <c r="G4" s="99">
-        <v>6.6E-6</v>
-      </c>
-      <c r="H4" s="103">
-        <v>5.0E-6</v>
-      </c>
-      <c r="I4" s="101">
-        <v>4.1E-6</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
+      <c r="E4" s="123">
+        <v>2.7999999999999999E-6</v>
+      </c>
+      <c r="F4" s="124">
+        <v>3.1399999999999998E-5</v>
+      </c>
+      <c r="G4" s="125">
+        <v>6.6000000000000003E-6</v>
+      </c>
+      <c r="H4" s="126">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="I4" s="127">
+        <v>4.0999999999999997E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1">
       <c r="A5" s="1">
-        <v>100.0</v>
-      </c>
-      <c r="B5" s="94">
-        <v>5.0E-7</v>
-      </c>
-      <c r="C5" s="95">
+        <v>100</v>
+      </c>
+      <c r="B5" s="120">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="C5" s="121">
         <v>1.06E-5</v>
       </c>
-      <c r="D5" s="118">
-        <v>3.3E-5</v>
-      </c>
-      <c r="E5" s="104">
-        <v>6.4E-6</v>
-      </c>
-      <c r="F5" s="102">
-        <v>9.73E-5</v>
-      </c>
-      <c r="G5" s="99">
-        <v>1.07E-5</v>
-      </c>
-      <c r="H5" s="103">
-        <v>9.8E-6</v>
-      </c>
-      <c r="I5" s="101">
+      <c r="D5" s="122">
+        <v>3.3000000000000003E-5</v>
+      </c>
+      <c r="E5" s="123">
+        <v>6.3999999999999997E-6</v>
+      </c>
+      <c r="F5" s="124">
+        <v>9.7299999999999993E-5</v>
+      </c>
+      <c r="G5" s="125">
+        <v>1.0699999999999999E-5</v>
+      </c>
+      <c r="H5" s="126">
+        <v>9.7999999999999993E-6</v>
+      </c>
+      <c r="I5" s="127">
         <v>2.34E-5</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1">
       <c r="A6" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="B6" s="94">
-        <v>3.2E-6</v>
-      </c>
-      <c r="C6" s="95">
-        <v>0.0010343</v>
-      </c>
-      <c r="D6" s="96">
-        <v>7.169E-4</v>
-      </c>
-      <c r="E6" s="104">
-        <v>5.76E-5</v>
-      </c>
-      <c r="F6" s="102">
-        <v>4.97E-4</v>
-      </c>
-      <c r="G6" s="99">
+        <v>1000</v>
+      </c>
+      <c r="B6" s="120">
+        <v>3.1999999999999999E-6</v>
+      </c>
+      <c r="C6" s="121">
+        <v>1.0342999999999999E-3</v>
+      </c>
+      <c r="D6" s="122">
+        <v>7.1690000000000002E-4</v>
+      </c>
+      <c r="E6" s="123">
+        <v>5.7599999999999997E-5</v>
+      </c>
+      <c r="F6" s="124">
+        <v>4.9700000000000005E-4</v>
+      </c>
+      <c r="G6" s="125">
         <v>1.261E-4</v>
       </c>
-      <c r="H6" s="103">
-        <v>1.878E-4</v>
-      </c>
-      <c r="I6" s="101">
+      <c r="H6" s="126">
+        <v>1.8780000000000001E-4</v>
+      </c>
+      <c r="I6" s="127">
         <v>1.166E-4</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1">
       <c r="A7" s="1">
-        <v>10000.0</v>
-      </c>
-      <c r="B7" s="94">
+        <v>10000</v>
+      </c>
+      <c r="B7" s="120">
         <v>2.042E-4</v>
       </c>
-      <c r="C7" s="95">
+      <c r="C7" s="121">
         <v>0.1026591</v>
       </c>
-      <c r="D7" s="96">
-        <v>0.0698352</v>
-      </c>
-      <c r="E7" s="104">
-        <v>0.0061688</v>
-      </c>
-      <c r="F7" s="102">
-        <v>0.0030207</v>
-      </c>
-      <c r="G7" s="99">
-        <v>0.0013399</v>
-      </c>
-      <c r="H7" s="103">
-        <v>0.0017523</v>
-      </c>
-      <c r="I7" s="101">
-        <v>7.777E-4</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
+      <c r="D7" s="122">
+        <v>6.98352E-2</v>
+      </c>
+      <c r="E7" s="123">
+        <v>6.1688000000000003E-3</v>
+      </c>
+      <c r="F7" s="124">
+        <v>3.0206999999999999E-3</v>
+      </c>
+      <c r="G7" s="125">
+        <v>1.3399E-3</v>
+      </c>
+      <c r="H7" s="126">
+        <v>1.7523E-3</v>
+      </c>
+      <c r="I7" s="127">
+        <v>7.7769999999999998E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1">
       <c r="A8" s="1">
-        <v>100000.0</v>
-      </c>
-      <c r="B8" s="94">
-        <v>7.777E-4</v>
-      </c>
-      <c r="C8" s="95">
-        <v>10.3650639</v>
-      </c>
-      <c r="D8" s="96">
-        <v>6.6000804</v>
-      </c>
-      <c r="E8" s="104">
-        <v>0.0122101</v>
-      </c>
-      <c r="F8" s="102">
-        <v>0.027529</v>
-      </c>
-      <c r="G8" s="99">
-        <v>0.0082455</v>
-      </c>
-      <c r="H8" s="103">
-        <v>0.0177576</v>
-      </c>
-      <c r="I8" s="101">
-        <v>0.0113858</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
+        <v>100000</v>
+      </c>
+      <c r="B8" s="120">
+        <v>7.7769999999999998E-4</v>
+      </c>
+      <c r="C8" s="121">
+        <v>10.365063900000001</v>
+      </c>
+      <c r="D8" s="122">
+        <v>6.6000804000000004</v>
+      </c>
+      <c r="E8" s="123">
+        <v>1.22101E-2</v>
+      </c>
+      <c r="F8" s="124">
+        <v>2.7529000000000001E-2</v>
+      </c>
+      <c r="G8" s="125">
+        <v>8.2454999999999994E-3</v>
+      </c>
+      <c r="H8" s="126">
+        <v>1.7757599999999998E-2</v>
+      </c>
+      <c r="I8" s="127">
+        <v>1.13858E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1">
       <c r="A9" s="1">
-        <v>1000000.0</v>
-      </c>
-      <c r="B9" s="94">
-        <v>0.0564578</v>
-      </c>
-      <c r="C9" s="58">
-        <v>651.493</v>
-      </c>
-      <c r="D9" s="89">
-        <v>440.52</v>
-      </c>
-      <c r="E9" s="104">
-        <v>0.0621153</v>
-      </c>
-      <c r="F9" s="102">
-        <v>0.294938</v>
-      </c>
-      <c r="G9" s="99">
-        <v>0.1593559</v>
-      </c>
-      <c r="H9" s="103">
-        <v>0.2256703</v>
-      </c>
-      <c r="I9" s="119">
+        <v>1000000</v>
+      </c>
+      <c r="B9" s="120">
+        <v>5.6457800000000002E-2</v>
+      </c>
+      <c r="C9" s="121">
+        <v>905.99362759999997</v>
+      </c>
+      <c r="D9" s="122">
+        <v>726.23423349999996</v>
+      </c>
+      <c r="E9" s="123">
+        <v>6.2115299999999998E-2</v>
+      </c>
+      <c r="F9" s="124">
+        <v>0.29493799999999998</v>
+      </c>
+      <c r="G9" s="125">
+        <v>0.15935589999999999</v>
+      </c>
+      <c r="H9" s="126">
+        <v>0.22567029999999999</v>
+      </c>
+      <c r="I9" s="127">
         <v>0.11488</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:9" ht="15.75" customHeight="1">
       <c r="A10" s="1">
-        <v>1.0E7</v>
-      </c>
-      <c r="B10" s="94">
-        <v>0.5020571</v>
-      </c>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="104">
-        <v>0.7021202</v>
-      </c>
-      <c r="F10" s="105">
+        <v>10000000</v>
+      </c>
+      <c r="B10" s="120">
+        <v>0.50205710000000003</v>
+      </c>
+      <c r="C10" s="128"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="123">
+        <v>0.70212019999999997</v>
+      </c>
+      <c r="F10" s="124">
         <v>3.8146852</v>
       </c>
-      <c r="G10" s="106">
+      <c r="G10" s="125">
         <v>1.5697534</v>
       </c>
-      <c r="H10" s="100">
-        <v>3.218833</v>
-      </c>
-      <c r="I10" s="107">
+      <c r="H10" s="126">
+        <v>3.2188330000000001</v>
+      </c>
+      <c r="I10" s="127">
         <v>1.077704</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1">
       <c r="A11" s="1">
-        <v>1.0E8</v>
-      </c>
-      <c r="B11" s="94">
-        <v>1.0258674</v>
-      </c>
-      <c r="C11" s="115"/>
-      <c r="D11" s="115"/>
-      <c r="E11" s="104">
-        <v>8.5270953</v>
-      </c>
-      <c r="F11" s="102">
-        <v>44.2835098</v>
-      </c>
-      <c r="G11" s="99">
-        <v>15.0534627</v>
-      </c>
-      <c r="H11" s="103">
-        <v>31.2510781</v>
-      </c>
-      <c r="I11" s="101">
+        <v>100000000</v>
+      </c>
+      <c r="B11" s="120">
+        <v>1.0258674000000001</v>
+      </c>
+      <c r="C11" s="128"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="123">
+        <v>8.5270952999999992</v>
+      </c>
+      <c r="F11" s="124">
+        <v>44.283509799999997</v>
+      </c>
+      <c r="G11" s="125">
+        <v>15.053462700000001</v>
+      </c>
+      <c r="H11" s="126">
+        <v>31.251078100000001</v>
+      </c>
+      <c r="I11" s="127">
         <v>14.7631543</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -9405,338 +9369,336 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:K1000"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.88"/>
-    <col customWidth="1" min="2" max="6" width="12.63"/>
+    <col min="1" max="1" width="15.90625" customWidth="1"/>
+    <col min="2" max="6" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A1" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="73" t="s">
+      <c r="C1" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="76" t="s">
+      <c r="F1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="78" t="s">
+      <c r="H1" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="120"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
+      <c r="K1" s="102"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1">
       <c r="A2" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="B2" s="121">
-        <v>1.0E-5</v>
-      </c>
-      <c r="C2" s="122">
-        <v>1.0E-5</v>
-      </c>
-      <c r="D2" s="123">
-        <v>1.0E-5</v>
-      </c>
-      <c r="E2" s="124">
-        <v>1.0E-5</v>
-      </c>
-      <c r="F2" s="125">
-        <v>1.0E-5</v>
-      </c>
-      <c r="G2" s="126">
-        <v>1.0E-5</v>
-      </c>
-      <c r="H2" s="127">
-        <v>1.0E-5</v>
-      </c>
-      <c r="I2" s="128">
-        <v>1.0E-5</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
+        <v>10</v>
+      </c>
+      <c r="B2" s="120">
+        <v>6.9999999999999997E-7</v>
+      </c>
+      <c r="C2" s="121">
+        <v>5.9999999999999997E-7</v>
+      </c>
+      <c r="D2" s="122">
+        <v>2.9999999999999999E-7</v>
+      </c>
+      <c r="E2" s="123">
+        <v>1.1000000000000001E-6</v>
+      </c>
+      <c r="F2" s="124">
+        <v>5.0000000000000004E-6</v>
+      </c>
+      <c r="G2" s="125">
+        <v>4.4000000000000002E-6</v>
+      </c>
+      <c r="H2" s="126">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="I2" s="127">
+        <v>8.9999999999999996E-7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" customHeight="1">
       <c r="A3" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="B3" s="121">
-        <v>1.0E-5</v>
-      </c>
-      <c r="C3" s="122">
-        <v>1.0E-5</v>
-      </c>
-      <c r="D3" s="123">
-        <v>1.0E-5</v>
-      </c>
-      <c r="E3" s="124">
-        <v>1.0E-5</v>
-      </c>
-      <c r="F3" s="125">
-        <v>1.0E-5</v>
-      </c>
-      <c r="G3" s="126">
-        <v>1.0E-5</v>
-      </c>
-      <c r="H3" s="127">
-        <v>1.0E-5</v>
-      </c>
-      <c r="I3" s="128">
-        <v>1.0E-5</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
+        <v>20</v>
+      </c>
+      <c r="B3" s="120">
+        <v>6.9999999999999997E-7</v>
+      </c>
+      <c r="C3" s="121">
+        <v>8.9999999999999996E-7</v>
+      </c>
+      <c r="D3" s="122">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="E3" s="123">
+        <v>1.5E-6</v>
+      </c>
+      <c r="F3" s="124">
+        <v>6.6000000000000003E-6</v>
+      </c>
+      <c r="G3" s="125">
+        <v>7.1999999999999997E-6</v>
+      </c>
+      <c r="H3" s="126">
+        <v>1.3E-6</v>
+      </c>
+      <c r="I3" s="127">
+        <v>6.9999999999999997E-7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1">
       <c r="A4" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="B4" s="121">
-        <v>1.0E-5</v>
-      </c>
-      <c r="C4" s="122">
-        <v>1.0E-5</v>
-      </c>
-      <c r="D4" s="123">
-        <v>1.0E-5</v>
-      </c>
-      <c r="E4" s="124">
-        <v>1.0E-5</v>
-      </c>
-      <c r="F4" s="125">
-        <v>1.0E-5</v>
-      </c>
-      <c r="G4" s="126">
-        <v>1.0E-5</v>
-      </c>
-      <c r="H4" s="127">
-        <v>1.0E-5</v>
-      </c>
-      <c r="I4" s="128">
-        <v>1.0E-5</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
+        <v>50</v>
+      </c>
+      <c r="B4" s="120">
+        <v>2.6000000000000001E-6</v>
+      </c>
+      <c r="C4" s="121">
+        <v>2.9000000000000002E-6</v>
+      </c>
+      <c r="D4" s="122">
+        <v>1.7999999999999999E-6</v>
+      </c>
+      <c r="E4" s="123">
+        <v>2.7999999999999999E-6</v>
+      </c>
+      <c r="F4" s="124">
+        <v>1.1600000000000001E-5</v>
+      </c>
+      <c r="G4" s="125">
+        <v>9.7000000000000003E-6</v>
+      </c>
+      <c r="H4" s="126">
+        <v>3.4000000000000001E-6</v>
+      </c>
+      <c r="I4" s="127">
+        <v>4.6E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" customHeight="1">
       <c r="A5" s="1">
-        <v>100.0</v>
-      </c>
-      <c r="B5" s="121">
-        <v>1.0E-5</v>
-      </c>
-      <c r="C5" s="122">
-        <v>1.0E-5</v>
-      </c>
-      <c r="D5" s="123">
-        <v>1.0E-5</v>
-      </c>
-      <c r="E5" s="124">
-        <v>1.0E-5</v>
-      </c>
-      <c r="F5" s="125">
-        <v>1.0E-5</v>
-      </c>
-      <c r="G5" s="126">
-        <v>1.0E-5</v>
-      </c>
-      <c r="H5" s="127">
-        <v>1.0E-5</v>
-      </c>
-      <c r="I5" s="128">
-        <v>1.0E-5</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
+        <v>100</v>
+      </c>
+      <c r="B5" s="120">
+        <v>1.31E-5</v>
+      </c>
+      <c r="C5" s="121">
+        <v>1.2999999999999999E-5</v>
+      </c>
+      <c r="D5" s="122">
+        <v>4.6999999999999999E-6</v>
+      </c>
+      <c r="E5" s="123">
+        <v>5.4E-6</v>
+      </c>
+      <c r="F5" s="124">
+        <v>2.27E-5</v>
+      </c>
+      <c r="G5" s="125">
+        <v>1.49E-5</v>
+      </c>
+      <c r="H5" s="126">
+        <v>6.9E-6</v>
+      </c>
+      <c r="I5" s="127">
+        <v>8.3999999999999992E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" customHeight="1">
       <c r="A6" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="B6" s="121">
-        <v>1.0E-5</v>
-      </c>
-      <c r="C6" s="58">
-        <v>0.001</v>
-      </c>
-      <c r="D6" s="123">
-        <v>1.0E-5</v>
-      </c>
-      <c r="E6" s="60">
-        <v>0.001</v>
-      </c>
-      <c r="F6" s="125">
-        <v>1.0E-5</v>
-      </c>
-      <c r="G6" s="126">
-        <v>1.0E-5</v>
-      </c>
-      <c r="H6" s="127">
-        <v>1.0E-5</v>
-      </c>
-      <c r="I6" s="64">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
+        <v>1000</v>
+      </c>
+      <c r="B6" s="120">
+        <v>9.3400000000000004E-4</v>
+      </c>
+      <c r="C6" s="121">
+        <v>6.0030000000000001E-4</v>
+      </c>
+      <c r="D6" s="122">
+        <v>4.1530000000000001E-4</v>
+      </c>
+      <c r="E6" s="123">
+        <v>5.0300000000000003E-5</v>
+      </c>
+      <c r="F6" s="124">
+        <v>1.8770000000000001E-4</v>
+      </c>
+      <c r="G6" s="125">
+        <v>1.072E-4</v>
+      </c>
+      <c r="H6" s="126">
+        <v>9.5600000000000006E-5</v>
+      </c>
+      <c r="I6" s="127">
+        <v>8.6799999999999996E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" customHeight="1">
       <c r="A7" s="1">
-        <v>10000.0</v>
-      </c>
-      <c r="B7" s="129">
-        <v>0.04</v>
-      </c>
-      <c r="C7" s="58">
-        <v>0.033</v>
-      </c>
-      <c r="D7" s="59">
-        <v>0.026</v>
-      </c>
-      <c r="E7" s="124">
-        <v>1.0E-5</v>
-      </c>
-      <c r="F7" s="61">
-        <v>0.001</v>
-      </c>
-      <c r="G7" s="62">
-        <v>0.001</v>
-      </c>
-      <c r="H7" s="63">
-        <v>0.001</v>
-      </c>
-      <c r="I7" s="64">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
+        <v>10000</v>
+      </c>
+      <c r="B7" s="120">
+        <v>6.1255900000000002E-2</v>
+      </c>
+      <c r="C7" s="121">
+        <v>4.6721600000000002E-2</v>
+      </c>
+      <c r="D7" s="122">
+        <v>4.2513099999999998E-2</v>
+      </c>
+      <c r="E7" s="123">
+        <v>4.2630000000000001E-4</v>
+      </c>
+      <c r="F7" s="124">
+        <v>1.5177000000000001E-3</v>
+      </c>
+      <c r="G7" s="125">
+        <v>1.1662E-3</v>
+      </c>
+      <c r="H7" s="126">
+        <v>1.0918E-3</v>
+      </c>
+      <c r="I7" s="127">
+        <v>7.561E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" customHeight="1">
       <c r="A8" s="1">
-        <v>100000.0</v>
-      </c>
-      <c r="B8" s="57">
-        <v>4.884</v>
-      </c>
-      <c r="C8" s="58">
-        <v>4.509</v>
-      </c>
-      <c r="D8" s="59">
-        <v>4.309</v>
-      </c>
-      <c r="E8" s="124">
-        <v>1.0E-5</v>
-      </c>
-      <c r="F8" s="61">
-        <v>0.027</v>
-      </c>
-      <c r="G8" s="62">
-        <v>0.012</v>
-      </c>
-      <c r="H8" s="63">
-        <v>0.014</v>
-      </c>
-      <c r="I8" s="64">
-        <v>0.013</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
+        <v>100000</v>
+      </c>
+      <c r="B8" s="120">
+        <v>10.178934999999999</v>
+      </c>
+      <c r="C8" s="121">
+        <v>9.3647717000000004</v>
+      </c>
+      <c r="D8" s="122">
+        <v>4.5256723000000001</v>
+      </c>
+      <c r="E8" s="123">
+        <v>1.0396499999999999E-2</v>
+      </c>
+      <c r="F8" s="124">
+        <v>2.5751799999999998E-2</v>
+      </c>
+      <c r="G8" s="125">
+        <v>2.7412200000000001E-2</v>
+      </c>
+      <c r="H8" s="126">
+        <v>2.6284200000000001E-2</v>
+      </c>
+      <c r="I8" s="127">
+        <v>1.30028E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" customHeight="1">
       <c r="A9" s="1">
-        <v>1000000.0</v>
-      </c>
-      <c r="B9" s="130">
-        <v>524.329</v>
-      </c>
-      <c r="C9" s="108">
-        <v>366.404</v>
-      </c>
-      <c r="D9" s="131">
-        <v>265.765</v>
-      </c>
-      <c r="E9" s="124">
-        <v>1.0E-5</v>
-      </c>
-      <c r="F9" s="61">
-        <v>0.121</v>
-      </c>
-      <c r="G9" s="62">
-        <v>0.046</v>
-      </c>
-      <c r="H9" s="63">
-        <v>0.113</v>
-      </c>
-      <c r="I9" s="64">
-        <v>0.054</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
+        <v>1000000</v>
+      </c>
+      <c r="B9" s="129">
+        <v>966.60574859999997</v>
+      </c>
+      <c r="C9" s="130">
+        <v>947.85994579999999</v>
+      </c>
+      <c r="D9" s="122">
+        <v>735.89232749999996</v>
+      </c>
+      <c r="E9" s="123">
+        <v>0.1102291</v>
+      </c>
+      <c r="F9" s="124">
+        <v>0.20478660000000001</v>
+      </c>
+      <c r="G9" s="125">
+        <v>0.22128020000000001</v>
+      </c>
+      <c r="H9" s="126">
+        <v>0.20972399999999999</v>
+      </c>
+      <c r="I9" s="127">
+        <v>0.126634</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" customHeight="1">
       <c r="A10" s="1">
-        <v>1.0E7</v>
-      </c>
-      <c r="B10" s="132"/>
-      <c r="C10" s="132"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="124">
-        <v>1.0E-5</v>
-      </c>
-      <c r="F10" s="61">
-        <v>1.325</v>
-      </c>
-      <c r="G10" s="62">
-        <v>0.532</v>
-      </c>
-      <c r="H10" s="63">
-        <v>1.741</v>
-      </c>
-      <c r="I10" s="64">
-        <v>0.612</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
+        <v>10000000</v>
+      </c>
+      <c r="B10" s="131"/>
+      <c r="C10" s="131"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="123">
+        <v>1.4396855</v>
+      </c>
+      <c r="F10" s="124">
+        <v>2.0417931999999999</v>
+      </c>
+      <c r="G10" s="125">
+        <v>2.3545300999999998</v>
+      </c>
+      <c r="H10" s="126">
+        <v>2.5976821999999999</v>
+      </c>
+      <c r="I10" s="127">
+        <v>0.88302329999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.75" customHeight="1">
       <c r="A11" s="1">
-        <v>1.0E8</v>
-      </c>
-      <c r="B11" s="88"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="134"/>
-      <c r="E11" s="135">
-        <v>16.9785971</v>
-      </c>
-      <c r="F11" s="136">
-        <v>16.7007158</v>
-      </c>
-      <c r="G11" s="137">
-        <v>16.7845469</v>
-      </c>
-      <c r="H11" s="138">
+        <v>100000000</v>
+      </c>
+      <c r="B11" s="128"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="123">
+        <v>16.978597100000002</v>
+      </c>
+      <c r="F11" s="124">
+        <v>16.700715800000001</v>
+      </c>
+      <c r="G11" s="125">
+        <v>16.784546899999999</v>
+      </c>
+      <c r="H11" s="126">
         <v>26.990527</v>
       </c>
-      <c r="I11" s="139">
-        <v>18.6015907</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
+      <c r="I11" s="127">
+        <v>18.601590699999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="13" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="16" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -10722,9 +10684,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>